--- a/workspaces/nasdaq_hourly_24hrs/volume/volume_ratio_24.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/volume/volume_ratio_24.xlsx
@@ -618,1805 +618,1805 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ 0.5515</t>
+          <t>X ≈ 0.5574</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>21.18155859259109</v>
+        <v>12.93337199674036</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>45.69352487825454</v>
+        <v>29.15775559645451</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>19.43179008994602</v>
+        <v>11.18066230422256</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>18.72781539970648</v>
+        <v>10.47491063042425</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-6.494852090959938</v>
+        <v>-6.427565358763232</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-6.3100007749361</v>
+        <v>-6.242900911625284</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-31.96114487332168</v>
+        <v>-23.59343896310069</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-7.359662784665858</v>
+        <v>-7.290809153533317</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-7.321537422381894</v>
+        <v>-7.252756098363719</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>16.80684117048889</v>
+        <v>-8.023848504061945</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-7.820705236730788</v>
+        <v>-7.753608995003262</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-8.101256888215815</v>
+        <v>-8.033797015732979</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>15.69726670138396</v>
+        <v>7.458267737702108</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>15.48174983758189</v>
+        <v>7.237604223813733</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>14.82969038335262</v>
+        <v>6.583740207447939</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>15.42904409264252</v>
+        <v>7.179473784518024</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>15.2955061008762</v>
+        <v>7.048647056399503</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-9.761426611175494</v>
+        <v>-9.691823991199222</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-9.548665582281522</v>
+        <v>-9.479272872998266</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-9.365533743726928</v>
+        <v>-9.29631637409296</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-9.911618269995579</v>
+        <v>-9.838480236332472</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-9.990809876550976</v>
+        <v>-9.917478602985206</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-9.71938029815275</v>
+        <v>-9.646357807394686</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-9.795321637426902</v>
+        <v>-9.725467289719624</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ 0.6251</t>
+          <t>X ≈ 0.6317</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.3384489278478569</v>
+        <v>-11.45302187168954</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.6729645206626458</v>
+        <v>-1.336349201343197</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>11.14880950441011</v>
+        <v>7.694010985453936</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>17.0701002670229</v>
+        <v>12.21796669981947</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>16.71136583518367</v>
+        <v>17.11952536325725</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>10.27157104587683</v>
+        <v>12.07780216951566</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>9.50742158586872</v>
+        <v>11.31555736789682</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>9.233242788366184</v>
+        <v>5.804447653595837</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>9.277013124082629</v>
+        <v>5.84694684808651</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-11.41081659382635</v>
+        <v>-10.64434779946189</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>2.14190557921939</v>
+        <v>-5.131679102739533</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>15.15251418529076</v>
+        <v>5.079321333327222</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>7.389256938117207</v>
+        <v>-1.286845201800396</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>7.170936705380278</v>
+        <v>-1.507505161942944</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.1346226630479279</v>
+        <v>-2.164326428336999</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>7.112615121003394</v>
+        <v>-1.57157723492039</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-12.97985149554844</v>
+        <v>-17.46239390237149</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-6.433690196743811</v>
+        <v>-12.31875123698371</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-12.87734565555306</v>
+        <v>-12.10712930418224</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-12.69537962968722</v>
+        <v>-11.92510733519119</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-6.580526748190024</v>
+        <v>-7.209524796529223</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-6.658597478126481</v>
+        <v>-7.287648327754589</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-13.05271363149177</v>
+        <v>-12.27700555720472</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-13.12865497076024</v>
+        <v>-17.62020413182609</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ 0.6986</t>
+          <t>X ≈ 0.7061</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-10.46379046072239</v>
+        <v>-5.599232564223378</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.8853973328210998</v>
+        <v>2.008888565336406</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>3.353064453896735</v>
+        <v>4.555732274098013</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>10.44045793658214</v>
+        <v>11.79771282204568</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>13.97936175834523</v>
+        <v>11.4664165858777</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>12.22090086367299</v>
+        <v>9.668578863265893</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>13.40887772843035</v>
+        <v>12.88488178387323</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>7.2803726924393</v>
+        <v>10.62232204913236</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>9.2761218152922</v>
+        <v>12.65748038940346</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>2.649027307417896</v>
+        <v>7.910526342413348</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>6.829609672860073</v>
+        <v>12.17073851566555</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>10.4618190397572</v>
+        <v>15.88328342155209</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>9.343360243162785</v>
+        <v>14.76802761106098</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>7.170465509431615</v>
+        <v>12.55364512488394</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>14.33980527316132</v>
+        <v>17.88503436717404</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>5.155584633072145</v>
+        <v>10.50424222174891</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.8477819449391575</v>
+        <v>4.387418790256405</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>1.004565653368083</v>
+        <v>6.280857905364627</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>1.221033187518231</v>
+        <v>4.501654940089914</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.550935170431508</v>
+        <v>2.691449393109636</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-1.094060676921522</v>
+        <v>2.149262194643363</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>2.749934520986464</v>
+        <v>6.071558082153921</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-4.817419513844705</v>
+        <v>0.3502643128213805</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-4.893360853113172</v>
+        <v>0.2745327102812851</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ 0.7722</t>
+          <t>X ≈ 0.7803</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.6826509708343096</v>
+        <v>0.00285679536521144</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.4634915141815554</v>
+        <v>-0.3326075169243552</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-2.448605796607488</v>
+        <v>-1.759906642935874</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.9358088364216641</v>
+        <v>1.476500699710243</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-3.526711120098597</v>
+        <v>-0.174499036180606</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-1.113875812476131</v>
+        <v>1.987887936562949</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-4.108924443371201</v>
+        <v>-1.411925049939441</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-2.158944910652153</v>
+        <v>-1.029996275163789</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.1097265030315953</v>
+        <v>2.305421894404276</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>6.028248311940665</v>
+        <v>7.47297028483834</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>8.533015754344731</v>
+        <v>9.067311023211154</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>8.257892174671355</v>
+        <v>7.473130634665395</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>5.651401505157629</v>
+        <v>5.69530683985662</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>4.68875170859166</v>
+        <v>6.134864987457902</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.3112915011578394</v>
+        <v>1.518944788563587</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>1.650673182676535</v>
+        <v>1.452825842041719</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>5.985444676243077</v>
+        <v>3.963850231993234</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>2.158330979959999</v>
+        <v>1.21655497639226</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>2.375243659997864</v>
+        <v>1.43290493213604</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>1.07155058291815</v>
+        <v>0.2965376713848542</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>3.511913970935169</v>
+        <v>2.400456591935651</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>1.199365812120213</v>
+        <v>1.002127839025036</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>1.474649552587834</v>
+        <v>-0.04694767568885538</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.09382910011347434</v>
+        <v>-0.12281828309726</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ 0.8457</t>
+          <t>X ≈ 0.8547</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>291</v>
+        <v>331</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1.931136287919514</v>
+        <v>2.050558784696264</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.7929234729426398</v>
+        <v>-0.6830513365523032</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2.195548993059958</v>
+        <v>2.376422002693864</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-2.772104222934047</v>
+        <v>-3.13965322380168</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-3.139157743422295</v>
+        <v>-4.377980016947177</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-4.811653806435544</v>
+        <v>-7.196944804266138</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-4.02410665415912</v>
+        <v>-6.47354943387257</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-4.987791024480188</v>
+        <v>-5.378817151194291</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-1.18558418617571</v>
+        <v>-2.632331558813661</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1.120494943882278</v>
+        <v>0.3755136796280709</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1.737299452206514</v>
+        <v>2.324369791887868</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.5951058525204971</v>
+        <v>0.8447569124826444</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.007169701044773547</v>
+        <v>0.628379647283829</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.9136780657718049</v>
+        <v>-1.097031318769943</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>2.197379224821738</v>
+        <v>1.860636907133944</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>1.079375395655923</v>
+        <v>1.551636181419397</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.9448770514855482</v>
+        <v>2.022243881349652</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>1.869050727256003</v>
+        <v>2.823359062568379</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>1.399457493561776</v>
+        <v>2.437259182792133</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>0.5581830498732074</v>
+        <v>1.115737516477125</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>0.2187604793746516</v>
+        <v>0.5734694455857365</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>0.8301409674892923</v>
+        <v>2.007480610695062</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>0.418076746515105</v>
+        <v>1.075015395589872</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>3.434918912401272</v>
+        <v>3.4165266679843</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ 0.9192</t>
+          <t>X ≈ 0.9289</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-4.005455306677483</v>
+        <v>-4.226572237183106</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.217270881434409</v>
+        <v>-1.401496300353827</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.4838659376351444</v>
+        <v>0.08515553500557616</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.972439584737856</v>
+        <v>1.080185030405559</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.5940429944647008</v>
+        <v>-0.2278096350217496</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.4060990236487001</v>
+        <v>0.4475464788797012</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.512682960148112</v>
+        <v>0.8981063827061249</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.2449334533831617</v>
+        <v>-1.329498749768952</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.03231415804756921</v>
+        <v>0.4157419459734371</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2.15210873583932</v>
+        <v>1.839108880434871</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.460858826400589</v>
+        <v>-0.5713825393727561</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.7029981465423845</v>
+        <v>-1.580761347571894</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.1765724415553933</v>
+        <v>-1.726528058144027</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.08619854531725224</v>
+        <v>-1.214680715623658</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-1.295432976673361</v>
+        <v>-2.361022408200327</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.7482361179000137</v>
+        <v>-1.034302726520963</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>1.339552407142435</v>
+        <v>-0.1904361908450483</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>1.960822323995004</v>
+        <v>0.3386822274012431</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>2.419961829774756</v>
+        <v>0.3105671958795284</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>1.398279654585465</v>
+        <v>0.4970751248075018</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>1.822889756380732</v>
+        <v>0.9338147660758551</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>2.232155091644572</v>
+        <v>0.1241463010792145</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>1.055438103778613</v>
+        <v>-0.5807526914115755</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>0.4952352632994845</v>
+        <v>-1.392133956386232</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ 0.993</t>
+          <t>X ≈ 1.003</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.728848212369293</v>
+        <v>-0.846631652528572</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.330218097482728</v>
+        <v>0.9581225305094279</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.3966268435555875</v>
+        <v>0.1648100614963184</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>2.718864352125479</v>
+        <v>3.312440930127096</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.8344799973220631</v>
+        <v>1.262716752249268</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.021206317556107</v>
+        <v>1.66524974533597</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>2.633174588155775</v>
+        <v>4.330383223259737</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.3988949274535045</v>
+        <v>2.332705166512703</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.097026846937588</v>
+        <v>1.087823417484479</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.5395187844360905</v>
+        <v>0.5294311021688003</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.669040941072609</v>
+        <v>-1.345629848388157</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.6453236496775645</v>
+        <v>-0.7659893053637816</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.1860223545706106</v>
+        <v>0.04552254695447289</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.3441643103002434</v>
+        <v>-0.8223224669602587</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.520615136232955</v>
+        <v>-0.2785416225101827</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.189702578706175</v>
+        <v>0.1014490242686534</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.5472965759091437</v>
+        <v>0.8297077477124901</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.1349115079234977</v>
+        <v>0.7246316269295292</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.9568847206693576</v>
+        <v>0.5094337226010381</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.4491444178231347</v>
+        <v>1.129957267387539</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>0.1241321441930339</v>
+        <v>0.5870411619464093</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-2.133121025145776</v>
+        <v>-1.088356367812672</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-1.422437066717386</v>
+        <v>-1.031224205411462</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-1.498378405985854</v>
+        <v>-0.7621843523546659</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ 1.067</t>
+          <t>X ≈ 1.078</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>3.628434817253194</v>
+        <v>4.671557178839812</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.032506786361111</v>
+        <v>-0.7558127551425073</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.1482341831480767</v>
+        <v>-1.421165535509139</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.3888549902308469</v>
+        <v>-2.136977467860675</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.2835634090338885</v>
+        <v>-1.188452537097149</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.2215731196750781</v>
+        <v>-1.254516807782963</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.2058221550448991</v>
+        <v>-2.023824642001109</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2.193837180090703</v>
+        <v>0.2597781350638968</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.5342954943673064</v>
+        <v>-2.262873100511804</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.557652491124749</v>
+        <v>-3.034152474963854</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.534320445375641</v>
+        <v>-2.759274682009739</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.057327038243095</v>
+        <v>-0.2227907305734504</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-3.436725567015863</v>
+        <v>-4.158655900329599</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-3.907378494477285</v>
+        <v>-4.377096857566883</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-4.315884720353161</v>
+        <v>-3.497914186046657</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-2.212793900828878</v>
+        <v>-1.882583267139076</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-1.087320039063478</v>
+        <v>-0.7353698078444566</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-1.947297506908505</v>
+        <v>-2.121774099628311</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.03345505298995022</v>
+        <v>-0.6232091850628336</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-1.293265499640682</v>
+        <v>-2.2350889935841</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-2.088452984182993</v>
+        <v>-3.29119777449327</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.1460298438014647</v>
+        <v>-1.311731551453043</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>0.6341550553769153</v>
+        <v>0.7616760174882273</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-1.714513556618826</v>
+        <v>-0.8565726881772022</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ 1.14</t>
+          <t>X ≈ 1.152</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>248</v>
+        <v>223</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>3.88736879279903</v>
+        <v>-1.226829215721551</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-3.241197303836174</v>
+        <v>-3.541225489394229</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.089474418967477</v>
+        <v>-0.9907730287836003</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-3.800734574354038</v>
+        <v>-2.591918358940291</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-1.775823934122911</v>
+        <v>-1.155853050032206</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.7901529358822259</v>
+        <v>0.3635326600377766</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.3670642232401988</v>
+        <v>0.9244691438409234</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.179428491910393</v>
+        <v>2.869049773256883</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.632871902855271</v>
+        <v>3.369357078041602</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>2.461715801807642</v>
+        <v>3.486148345756412</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.129460682594825</v>
+        <v>2.419293907866525</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.5287060423986958</v>
+        <v>-1.17514849747198</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.020806291139543</v>
+        <v>-0.5203935313652366</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.364017617881494</v>
+        <v>1.488731206062567</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.9109950190603229</v>
+        <v>0.383650524509072</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>1.509034707391699</v>
+        <v>0.799681183459569</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.2338476635182545</v>
+        <v>-1.30683435023267</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>0.06241401754834186</v>
+        <v>-0.0687892868163047</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>2.695840240780903</v>
+        <v>2.832351904604181</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>1.272977070550951</v>
+        <v>1.67852257893145</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>0.3264845186100729</v>
+        <v>1.5843046525655</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>0.0856299258974218</v>
+        <v>0.1648619216797655</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>2.37739389539</v>
+        <v>2.682203528526074</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>2.704678362573055</v>
+        <v>1.261079795482168</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ 1.214</t>
+          <t>X ≈ 1.226</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.204200521269286</v>
+        <v>-1.511299542252551</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.1672453966251126</v>
+        <v>1.861613323235844</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.558400963608051</v>
+        <v>4.477085748776332</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-2.323574334355854</v>
+        <v>-1.188449415632519</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-2.101979830641582</v>
+        <v>0.3321033006752572</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.7236491626479804</v>
+        <v>2.383008324449854</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-2.693692810299453</v>
+        <v>-2.747297318209746</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.5924916861060794</v>
+        <v>-1.785221102846492</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-4.119686469183975</v>
+        <v>-4.224908919492748</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-4.29729775124634</v>
+        <v>-3.130057021969002</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-4.027950837759256</v>
+        <v>-2.86140952698748</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.718840378332303</v>
+        <v>-1.902196744302543</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-4.856363716252865</v>
+        <v>-1.172767202271963</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-3.888279682050097</v>
+        <v>-0.1504786881031492</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-7.17969582965943</v>
+        <v>-5.80309136942364</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-8.382043770592539</v>
+        <v>-7.068814398985431</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-10.90819130173151</v>
+        <v>-9.075194323513593</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-6.232084915390892</v>
+        <v>-5.44005058665168</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-9.251939139601504</v>
+        <v>-8.597611542637026</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-8.467024165841252</v>
+        <v>-9.045706496132844</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-7.215757353773775</v>
+        <v>-7.715338314821864</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-7.889156744233397</v>
+        <v>-9.044660360769214</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-7.024769519715392</v>
+        <v>-7.774635036496392</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-7.699513254193299</v>
+        <v>-7.225467289719589</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ 1.287</t>
+          <t>X ≈ 1.3</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.400701964157726</v>
+        <v>-1.782524029763508</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.2226590389426093</v>
+        <v>0.09981252688532294</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.1435823170899297</v>
+        <v>0.8772646969595783</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.6602113888967907</v>
+        <v>1.648912489715421</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>4.517656497054652</v>
+        <v>3.54107243836269</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>6.224268583707371</v>
+        <v>4.477601675263955</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>6.975230126788624</v>
+        <v>6.682603264261445</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2.140210289541884</v>
+        <v>1.939882283172025</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>2.180925978057694</v>
+        <v>4.638204914421379</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>3.689885261398587</v>
+        <v>6.840066143263755</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>6.249131097781301</v>
+        <v>8.603967185862565</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>7.495247323964236</v>
+        <v>10.55931089725246</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>5.615263416181556</v>
+        <v>6.47642132801186</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>5.395161730241377</v>
+        <v>5.510754628983335</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>6.260603870799223</v>
+        <v>7.834764945621764</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>3.05211324620236</v>
+        <v>4.702410430763678</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>1.394572260374609</v>
+        <v>1.589023672901867</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>3.575598968457861</v>
+        <v>4.46387625607629</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>1.505292413881058</v>
+        <v>2.444662172587151</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>1.691916616171305</v>
+        <v>2.634580887859464</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>2.673002685512451</v>
+        <v>3.584572033326261</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-1.212619582652493</v>
+        <v>2.762457415200664</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>2.876039549169818</v>
+        <v>5.275738097832047</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>1.273380652649436</v>
+        <v>2.961099874459443</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ 1.361</t>
+          <t>X ≈ 1.375</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2.511261604716154</v>
+        <v>4.597330791319983</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.667440288221613</v>
+        <v>4.263630581987854</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>3.615314687210912</v>
+        <v>1.559400358437799</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.90415711466084</v>
+        <v>2.121317903963849</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-4.238919734148134</v>
+        <v>-8.409476529282031</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-5.183586082308061</v>
+        <v>-6.248794296543217</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-3.691911711814214</v>
+        <v>1.9154974899945</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-5.092632936141477</v>
+        <v>-0.9114784465924828</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.5369599938006573</v>
+        <v>-2.155312104453962</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>3.216092035223795</v>
+        <v>-0.3769630386316933</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.09513878856400737</v>
+        <v>-1.378223236146006</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>2.083896622876814</v>
+        <v>-4.209487506465202</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>5.496284351402331</v>
+        <v>1.067298289592927</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>6.408853409261773</v>
+        <v>2.12677888587406</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>4.620110451361889</v>
+        <v>0.190585250384693</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>1.820900715504152</v>
+        <v>-3.054510752889144</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.5543170473047496</v>
+        <v>-0.6269953025585977</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.4478592268688502</v>
+        <v>-3.292954951835526</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>2.933385550923532</v>
+        <v>-1.796504098183327</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>1.985580325548462</v>
+        <v>-0.3313586452442294</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-1.960987622963572</v>
+        <v>-3.438007377312815</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>2.503043167112274</v>
+        <v>0.3323005074319312</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.6284712072492766</v>
+        <v>-4.521429908291296</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>1.568314726209465</v>
+        <v>-2.033159597412002</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ 1.434</t>
+          <t>X ≈ 1.449</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-4.155452495907085</v>
+        <v>-1.091420011274138</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.772059093950141</v>
+        <v>0.5662638928179078</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.7204190849222414</v>
+        <v>-0.8848332060143491</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.706203216567133</v>
+        <v>2.414600132933067</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.7390560366666961</v>
+        <v>4.111221321447836</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-4.735397440987825</v>
+        <v>-3.730199408167522</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.814419791552211</v>
+        <v>-1.492108713516359</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>2.593814757673947</v>
+        <v>-0.7552157340740777</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-2.610747611689575</v>
+        <v>-6.756675504197268</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-3.390385265440351</v>
+        <v>-5.524988039266965</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-4.159792797018149</v>
+        <v>-7.258180404357006</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.291837359178587</v>
+        <v>-2.505555458248878</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-4.503862175051978</v>
+        <v>-4.632071763414778</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-5.771472460342885</v>
+        <v>-4.852263942101139</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-1.186702950280022</v>
+        <v>-1.476783302353191</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-2.69196892490092</v>
+        <v>-1.889693992542057</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.32764875051015</v>
+        <v>-0.005912463095071985</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.8296815127279729</v>
+        <v>-0.1125265624366278</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-1.663408318037526</v>
+        <v>0.1042515162478637</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-2.5270467836257</v>
+        <v>-0.7198590337447399</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.9692988166900349</v>
+        <v>-0.2523041916097668</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>0.007509121293615806</v>
+        <v>-0.3281501530188109</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-2.877275035000594</v>
+        <v>-0.05367544053669349</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.8479532163742789</v>
+        <v>1.890694326442045</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 1.508</t>
+          <t>X ≈ 1.523</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>7.559678299698383</v>
+        <v>4.892560031086276</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>3.137610296099723</v>
+        <v>1.559077456252872</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.363578329296566</v>
+        <v>-1.889664436834231</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-3.102391581638386</v>
+        <v>-2.601690915724618</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.6212964785178059</v>
+        <v>-0.9129210328241442</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.8054278429569948</v>
+        <v>-0.7154159582281991</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.013433835970922</v>
+        <v>-2.496264490399398</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.276068288043547</v>
+        <v>-0.7523902767031529</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-6.364349145207576</v>
+        <v>-0.7193794669011595</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-7.126560646698252</v>
+        <v>-3.51296807270149</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.722337736673651</v>
+        <v>1.789463870559999</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.9751267998729816</v>
+        <v>0.5067352813146258</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-3.14751011872486</v>
+        <v>-0.5995339634641894</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-4.401814003908342</v>
+        <v>-2.833254094946199</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-6.088710641689588</v>
+        <v>-3.489977059032434</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-4.482910073027114</v>
+        <v>-1.887139009330305</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-3.595342699181131</v>
+        <v>-1.011894851801465</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-4.721987183271317</v>
+        <v>-3.1336378111409</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-4.510497403867873</v>
+        <v>-1.909295302457494</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-3.292525773195898</v>
+        <v>-1.729960043845693</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-4.864337325481237</v>
+        <v>-2.272506211811724</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-3.920948004893042</v>
+        <v>-2.348352173220825</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.9564937002202853</v>
+        <v>-0.05367544053675743</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-1.032435039488753</v>
+        <v>-0.1295076937600328</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 1.581</t>
+          <t>X ≈ 1.598</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2.964860641990377</v>
+        <v>2.925675311299436</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>3.976104539458881</v>
+        <v>2.59634833183226</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>5.280500021233919</v>
+        <v>5.606858544763355</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>4.558962574222157</v>
+        <v>-0.9954999800305657</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.436781149764926</v>
+        <v>-1.379823060218065</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.600713361315805</v>
+        <v>-2.718851586337216</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>3.546038199601789</v>
+        <v>-0.502819973209931</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.854179132182828</v>
+        <v>-0.8533968634627627</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2.691137907972745</v>
+        <v>-3.742710224289034</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>5.998538906025864</v>
+        <v>0.02530580478531874</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>6.269014979602829</v>
+        <v>0.2903197662597776</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>7.341272427479268</v>
+        <v>4.480136622422826</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>11.57170509839883</v>
+        <v>7.108292571730722</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>14.0375182159137</v>
+        <v>9.854141971834508</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>9.320649729283964</v>
+        <v>6.201850872230686</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>10.73118042196219</v>
+        <v>8.284238520027657</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>13.29978943051597</v>
+        <v>9.63378552132535</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>10.49210331171798</v>
+        <v>8.045480679229001</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>10.7082264746498</v>
+        <v>8.256835472574515</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>10.89527027027023</v>
+        <v>9.350998798307174</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>9.000718509920922</v>
+        <v>7.31591531690831</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>8.924763454278356</v>
+        <v>8.732606668932043</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>10.55088997211184</v>
+        <v>7.51454406798122</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>13.17765133554607</v>
+        <v>10.42378644162367</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 1.655</t>
+          <t>X ≈ 1.672</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.1693459221575253</v>
+        <v>2.566539250204372</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-3.22977678628412</v>
+        <v>0.6870181336727654</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-6.218228153712012</v>
+        <v>-3.868898642630938</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-10.00894454382831</v>
+        <v>-4.562604250446817</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-5.758829713467698</v>
+        <v>-3.330038196884864</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-10.18704971584553</v>
+        <v>-3.131505968687001</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-12.49837738636108</v>
+        <v>-5.48486995059578</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-9.700008954956616</v>
+        <v>-5.763081395348898</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-12.73541596685701</v>
+        <v>-7.284094213434088</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-15.04771291608795</v>
+        <v>-9.619509889470578</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-13.23489211051107</v>
+        <v>-9.345450247308698</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-11.97552447552443</v>
+        <v>-9.624199650756672</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-14.63847723247315</v>
+        <v>-9.18486171761279</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-13.32137250504597</v>
+        <v>-7.843440594059359</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-13.98030374408323</v>
+        <v>-8.501583891640024</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-13.38524369446185</v>
+        <v>-9.46969696969699</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-11.98087585014923</v>
+        <v>-9.603614106674442</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-10.547397727783</v>
+        <v>-6.583454810495667</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-8.792813026389624</v>
+        <v>-6.367563429571319</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-7.067307692307644</v>
+        <v>-6.180717619603293</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-6.072046562844065</v>
+        <v>-6.723263787569323</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-4.609540080025177</v>
+        <v>-3.674109748978402</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-5.873226452004616</v>
+        <v>-4.962135036496285</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-2.872244714349982</v>
+        <v>-1.912967289719646</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 1.728</t>
+          <t>X ≈ 1.747</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.1880283744512425</v>
+        <v>0.03171577964976535</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>8.725965929155976</v>
+        <v>12.03970627689748</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.690537499239639</v>
+        <v>5.69484760522495</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.3488372093023244</v>
+        <v>6.238293509931317</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>6.262637191720138</v>
+        <v>10.95881827536498</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>4.124220409378083</v>
+        <v>8.680786379375618</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.025772881975229</v>
+        <v>5.452630049404277</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.7472182364567033</v>
+        <v>10.17441860465121</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>3.114315696828129</v>
+        <v>10.21590578656587</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-4.636263899987846</v>
+        <v>-0.5570098894706277</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-9.013067423570149</v>
+        <v>-2.78295024730869</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-4.64099853634734</v>
+        <v>1.938300349243271</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-8.091071150183318</v>
+        <v>-4.184861717612854</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.9898976201776364</v>
+        <v>0.5940594059405981</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>0.3309663811403354</v>
+        <v>2.435916108360075</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-1.399554964587075</v>
+        <v>0.5303030303029956</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-3.859230054084875</v>
+        <v>0.396385893325558</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-3.96421347018012</v>
+        <v>-2.208454810495631</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-3.748090307248304</v>
+        <v>-4.492563429571263</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-8.212209302325547</v>
+        <v>-4.305717619603236</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-4.104246920625862</v>
+        <v>0.1517362124307269</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-6.505783371617348</v>
+        <v>-4.924109748978395</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-6.231008205135119</v>
+        <v>-2.149635036496385</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-8.632530939752449</v>
+        <v>-2.225467289719582</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 1.801</t>
+          <t>X ≈ 1.821</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>9.58332012507843</v>
+        <v>-2.018750846440668</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>5.926032633113032</v>
+        <v>-8.75346931652922</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.217669282185405</v>
+        <v>-10.22096949763564</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>13.83720930232558</v>
+        <v>-1.378232707583599</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>3.471939517301578</v>
+        <v>-8.047639990396519</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>23.65910413030832</v>
+        <v>11.37664948047404</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>19.55290466492101</v>
+        <v>4.242952630049402</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>22.60768335273568</v>
+        <v>7.190547636909187</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>19.31586608442504</v>
+        <v>4.00622836721103</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>11.87536400698904</v>
+        <v>0.007506239561642758</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>18.81638994077099</v>
+        <v>6.733178784949367</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>15.2039627039627</v>
+        <v>3.228622929888466</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>24.07947148547552</v>
+        <v>15.00868666948396</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>17.19144800777455</v>
+        <v>8.335994889811559</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>19.86585010207062</v>
+        <v>10.90365804384387</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>17.12757681835857</v>
+        <v>11.4980449657869</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>13.66014979087636</v>
+        <v>8.138321377196519</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>13.55516637478108</v>
+        <v>8.033480673375337</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>17.10462287104618</v>
+        <v>14.70098495752547</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>13.95833333333329</v>
+        <v>11.6620243158806</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>13.41513292433543</v>
+        <v>7.893671696301659</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>10.00584453535949</v>
+        <v>4.592019283279704</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>13.61395303517485</v>
+        <v>8.092300447374612</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>16.87134502923971</v>
+        <v>8.016468194151336</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 1.875</t>
+          <t>X ≈ 1.895</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-12.67883573167249</v>
+        <v>-9.052778931613801</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-13.02691114311773</v>
+        <v>-3.975623911781781</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-14.53990647539035</v>
+        <v>-21.81989296081277</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-15.2536997885835</v>
+        <v>-17.07830152571008</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-11.07351502815307</v>
+        <v>-6.437103915997177</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-10.88635041514623</v>
+        <v>-17.25208817416758</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-16.20467109265486</v>
+        <v>-18.15848106170683</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-16.48322573817342</v>
+        <v>-23.99224806201542</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-16.44170967315072</v>
+        <v>-23.9507608801008</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-17.21554508392022</v>
+        <v>-30.27923211169284</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-16.94118581680488</v>
+        <v>-30.00517246953092</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-17.22027972027981</v>
+        <v>-30.28392187297892</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-9.25386184785777</v>
+        <v>-20.29597282872392</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-18.56612774980121</v>
+        <v>-20.51705170517047</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-14.6796044433841</v>
+        <v>-26.73075055830655</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-4.993635302853434</v>
+        <v>-15.02525252525253</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-5.127728997002428</v>
+        <v>-9.603614106674442</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-9.778166958552184</v>
+        <v>-15.26401036605118</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-14.10749834107498</v>
+        <v>-26.15923009623797</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-9.375</v>
+        <v>-20.41682873071438</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-14.4636549544525</v>
+        <v>-15.40381934312486</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-9.994155464640563</v>
+        <v>-15.47966530453396</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-9.719380298158434</v>
+        <v>-15.20519059205191</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-14.34077618288145</v>
+        <v>-20.83657840083073</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 1.949</t>
+          <t>X ≈ 1.97</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.300682625604111</v>
+        <v>1.872986878662886</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-8.946773590794564</v>
+        <v>-20.27997173786876</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-15.44899738448126</v>
+        <v>-10.84842556950844</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>3.837209302325583</v>
+        <v>4.723205391285994</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>13.47193951730154</v>
+        <v>4.561909351310533</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-6.340895869691643</v>
+        <v>-6.209890467229663</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-7.11376200174567</v>
+        <v>-7.047369950595758</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.607683352735812</v>
+        <v>3.78552971576228</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2.649199417758332</v>
+        <v>3.827016897676984</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-3.124635993011054</v>
+        <v>3.054101221640494</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-2.850276725895718</v>
+        <v>3.328160863802417</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-3.129370629370591</v>
+        <v>3.04941146035442</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.7461381521422297</v>
+        <v>1.926249393498338</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-4.475218658892118</v>
+        <v>-3.850385038503887</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-5.134149897929355</v>
+        <v>1.047027219471154</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>0.4609101516918841</v>
+        <v>1.641414141414145</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>0.3268164575430319</v>
+        <v>-4.048058551118885</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>0.221833041447681</v>
+        <v>-4.152899254940067</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.4379562043795673</v>
+        <v>1.618547681539816</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-4.374999999999993</v>
+        <v>-3.750162064047714</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>5.081799591001975</v>
+        <v>1.262847323541813</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>0.005844535359464942</v>
+        <v>1.187001362132591</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-4.719380298158427</v>
+        <v>-4.094079480940792</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-4.795321637426895</v>
+        <v>-4.169911734164067</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 2.022</t>
+          <t>X ≈ 2.044</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-3.648792125102275</v>
+        <v>2.530491559336944</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-13.86492002069901</v>
+        <v>2.19571476098713</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-15.44899738448126</v>
+        <v>-17.55609147339856</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-16.16279069767442</v>
+        <v>-24.46898828460332</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-16.52806048269846</v>
+        <v>-12.60707609749141</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>3.659104130308251</v>
+        <v>6.153150161865916</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-7.113762001745847</v>
+        <v>-7.047369950595801</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>2.607683352735734</v>
+        <v>-1.075581395348834</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>2.64919941775851</v>
+        <v>-1.03409421343413</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-8.124635993011061</v>
+        <v>-8.057009889470621</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-7.850276725895725</v>
+        <v>-7.782950247308698</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-8.129370629370626</v>
+        <v>-8.061699650756694</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.7461381521421586</v>
+        <v>-2.934861717612854</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.5247813411078752</v>
+        <v>-3.155940594059402</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.1341498979294258</v>
+        <v>-3.81408389163996</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>0.4609101516919551</v>
+        <v>-3.219696969696969</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>0.3268164575431101</v>
+        <v>-3.353614106674442</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>0.2218330414477521</v>
+        <v>-3.458454810495624</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>0.4379562043796454</v>
+        <v>-3.242563429571298</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>0.625</v>
+        <v>3.194282380396729</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-9.918200408997954</v>
+        <v>-3.598263787569302</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-9.994155464640563</v>
+        <v>2.57589025102164</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>0.2806197018415659</v>
+        <v>9.100364963503651</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-19.7953216374269</v>
+        <v>-3.475467289719624</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 2.096</t>
+          <t>X ≈ 2.118</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>14.01295342418112</v>
+        <v>17.24288395336543</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.6929703897829214</v>
+        <v>3.036471544249551</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-5.448997384481309</v>
+        <v>29.37986254207484</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-20.4485049833887</v>
+        <v>14.68085643589359</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-13.67091762555566</v>
+        <v>0.624447281090724</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-6.340895869691678</v>
+        <v>14.92625940556371</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-7.113762001745648</v>
+        <v>28.66691576368995</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-7.392316647264266</v>
+        <v>28.38870431893687</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-14.49365772509888</v>
+        <v>14.1444772151374</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-15.26749313586821</v>
+        <v>13.37156153910081</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-14.99313386875287</v>
+        <v>13.64562118126273</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-15.27222777222782</v>
+        <v>-0.918842507899555</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-9.253861847857713</v>
+        <v>12.24370971095862</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-2.332361516034986</v>
+        <v>12.02263083451213</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-2.991292755072287</v>
+        <v>11.36448753693147</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-9.539089848307988</v>
+        <v>-2.32683982683983</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-9.673183542456968</v>
+        <v>-2.460756963817303</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-9.778166958552248</v>
+        <v>-2.565597667638485</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-2.419186652763337</v>
+        <v>11.93600799900013</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-2.232142857142804</v>
+        <v>12.12285380896816</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-9.918200408997954</v>
+        <v>-2.705406644712163</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-2.851298321783467</v>
+        <v>-2.781252606121363</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-2.576523155301238</v>
+        <v>-2.50677789363921</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-2.652464494569763</v>
+        <v>-2.582610146862486</v>
       </c>
     </row>
   </sheetData>
@@ -2610,2457 +2610,2457 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2935</v>
+        <v>2938</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.03146235059438141</v>
+        <v>0.02593220390497919</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.1501229190410314</v>
+        <v>-0.1554751626269422</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.02001717698165351</v>
+        <v>0.01415548355652163</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.1329803995714371</v>
+        <v>-0.1387756000119396</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.4114898286828819</v>
+        <v>-0.4217783157469484</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.2730992595221835</v>
+        <v>-0.2835458435503639</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.009658915953913549</v>
+        <v>-0.02061749546538039</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.002527314743879572</v>
+        <v>-0.008508224617131077</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.1740106263542884</v>
+        <v>-0.1848058366127177</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.07013835378229061</v>
+        <v>0.07858333086836922</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.05875246622919406</v>
+        <v>0.06716843699106789</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.1388806439740264</v>
+        <v>0.1472555731239069</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.2185357609012542</v>
+        <v>-0.2096326711248579</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.2839172657558748</v>
+        <v>-0.2949802954506495</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.3109004077866686</v>
+        <v>-0.3220608094946797</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.1375257544624162</v>
+        <v>-0.148814117404946</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.0003968723679221853</v>
+        <v>0.009157632455988107</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>0.05176501423687085</v>
+        <v>0.06048844468615755</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.2542202397657576</v>
+        <v>0.2627050952417562</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.1170013614703933</v>
+        <v>-0.1081657664920854</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.2654935652798684</v>
+        <v>-0.2766894931116397</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.1848911594634544</v>
+        <v>-0.1962185925158124</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.0260242504582564</v>
+        <v>-0.03752207290329324</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.06789403947119155</v>
+        <v>-0.0590275347842919</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; 0.07354</t>
+          <t>X &gt; 0.07432</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2935</v>
+        <v>2938</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.03146235059438141</v>
+        <v>0.02593220390497919</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.1501229190410314</v>
+        <v>-0.1554751626269422</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.02001717698165351</v>
+        <v>0.01415548355652163</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.1329803995714371</v>
+        <v>-0.1387756000119396</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.4114898286828819</v>
+        <v>-0.4217783157469484</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.2730992595221835</v>
+        <v>-0.2835458435503639</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.009658915953913549</v>
+        <v>-0.02061749546538039</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.002527314743879572</v>
+        <v>-0.008508224617131077</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.1740106263542884</v>
+        <v>-0.1848058366127177</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.07013835378229061</v>
+        <v>0.07858333086836922</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.05875246622919406</v>
+        <v>0.06716843699106789</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.1388806439740264</v>
+        <v>0.1472555731239069</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.2185357609012542</v>
+        <v>-0.2096326711248579</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.2839172657558748</v>
+        <v>-0.2949802954506495</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.3109004077866686</v>
+        <v>-0.3220608094946797</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.1375257544624162</v>
+        <v>-0.148814117404946</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.0003968723679221853</v>
+        <v>0.009157632455988107</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0.05176501423687085</v>
+        <v>0.06048844468615755</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.2542202397657576</v>
+        <v>0.2627050952417562</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.1170013614703933</v>
+        <v>-0.1081657664920854</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.2654935652798684</v>
+        <v>-0.2766894931116397</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.1848911594634544</v>
+        <v>-0.1962185925158124</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.0260242504582564</v>
+        <v>-0.03752207290329324</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.06789403947119155</v>
+        <v>-0.0590275347842919</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; 0.1471</t>
+          <t>X &gt; 0.1486</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2935</v>
+        <v>2938</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.03146235059438141</v>
+        <v>0.02593220390497919</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.1501229190410314</v>
+        <v>-0.1554751626269422</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.02001717698165351</v>
+        <v>0.01415548355652163</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.1329803995714371</v>
+        <v>-0.1387756000119396</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.4114898286828819</v>
+        <v>-0.4217783157469484</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2730992595221835</v>
+        <v>-0.2835458435503639</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.009658915953913549</v>
+        <v>-0.02061749546538039</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.002527314743879572</v>
+        <v>-0.008508224617131077</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.1740106263542884</v>
+        <v>-0.1848058366127177</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.07013835378229061</v>
+        <v>0.07858333086836922</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.05875246622919406</v>
+        <v>0.06716843699106789</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.1388806439740264</v>
+        <v>0.1472555731239069</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.2185357609012542</v>
+        <v>-0.2096326711248579</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.2839172657558748</v>
+        <v>-0.2949802954506495</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.3109004077866686</v>
+        <v>-0.3220608094946797</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.1375257544624162</v>
+        <v>-0.148814117404946</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.0003968723679221853</v>
+        <v>0.009157632455988107</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>0.05176501423687085</v>
+        <v>0.06048844468615755</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.2542202397657576</v>
+        <v>0.2627050952417562</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.1170013614703933</v>
+        <v>-0.1081657664920854</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.2654935652798684</v>
+        <v>-0.2766894931116397</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.1848911594634544</v>
+        <v>-0.1962185925158124</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.0260242504582564</v>
+        <v>-0.03752207290329324</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.06789403947119155</v>
+        <v>-0.0590275347842919</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; 0.2206</t>
+          <t>X &gt; 0.223</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2935</v>
+        <v>2938</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.03146235059438141</v>
+        <v>0.02593220390497919</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.1501229190410314</v>
+        <v>-0.1554751626269422</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.02001717698165351</v>
+        <v>0.01415548355652163</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.1329803995714371</v>
+        <v>-0.1387756000119396</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.4114898286828819</v>
+        <v>-0.4217783157469484</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.2730992595221835</v>
+        <v>-0.2835458435503639</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.009658915953913549</v>
+        <v>-0.02061749546538039</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.002527314743879572</v>
+        <v>-0.008508224617131077</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.1740106263542884</v>
+        <v>-0.1848058366127177</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.07013835378229061</v>
+        <v>0.07858333086836922</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.05875246622919406</v>
+        <v>0.06716843699106789</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.1388806439740264</v>
+        <v>0.1472555731239069</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.2185357609012542</v>
+        <v>-0.2096326711248579</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.2839172657558748</v>
+        <v>-0.2949802954506495</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.3109004077866686</v>
+        <v>-0.3220608094946797</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.1375257544624162</v>
+        <v>-0.148814117404946</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.0003968723679221853</v>
+        <v>0.009157632455988107</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>0.05176501423687085</v>
+        <v>0.06048844468615755</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.2542202397657576</v>
+        <v>0.2627050952417562</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.1170013614703933</v>
+        <v>-0.1081657664920854</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.2654935652798684</v>
+        <v>-0.2766894931116397</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.1848911594634544</v>
+        <v>-0.1962185925158124</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.0260242504582564</v>
+        <v>-0.03752207290329324</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.06789403947119155</v>
+        <v>-0.0590275347842919</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; 0.2941</t>
+          <t>X &gt; 0.2973</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2935</v>
+        <v>2938</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.03146235059438141</v>
+        <v>0.02593220390497919</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.1501229190410314</v>
+        <v>-0.1554751626269422</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.02001717698165351</v>
+        <v>0.01415548355652163</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.1329803995714371</v>
+        <v>-0.1387756000119396</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.4114898286828819</v>
+        <v>-0.4217783157469484</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.2730992595221835</v>
+        <v>-0.2835458435503639</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.009658915953913549</v>
+        <v>-0.02061749546538039</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.002527314743879572</v>
+        <v>-0.008508224617131077</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.1740106263542884</v>
+        <v>-0.1848058366127177</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.07013835378229061</v>
+        <v>0.07858333086836922</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.05875246622919406</v>
+        <v>0.06716843699106789</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.1388806439740264</v>
+        <v>0.1472555731239069</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.2185357609012542</v>
+        <v>-0.2096326711248579</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.2839172657558748</v>
+        <v>-0.2949802954506495</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.3109004077866686</v>
+        <v>-0.3220608094946797</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.1375257544624162</v>
+        <v>-0.148814117404946</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.0003968723679221853</v>
+        <v>0.009157632455988107</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>0.05176501423687085</v>
+        <v>0.06048844468615755</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.2542202397657576</v>
+        <v>0.2627050952417562</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.1170013614703933</v>
+        <v>-0.1081657664920854</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.2654935652798684</v>
+        <v>-0.2766894931116397</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.1848911594634544</v>
+        <v>-0.1962185925158124</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.0260242504582564</v>
+        <v>-0.03752207290329324</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.06789403947119155</v>
+        <v>-0.0590275347842919</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; 0.3677</t>
+          <t>X &gt; 0.3716</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2935</v>
+        <v>2938</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.03146235059438141</v>
+        <v>0.02593220390497919</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.1501229190410314</v>
+        <v>-0.1554751626269422</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.02001717698165351</v>
+        <v>0.01415548355652163</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.1329803995714371</v>
+        <v>-0.1387756000119396</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.4114898286828819</v>
+        <v>-0.4217783157469484</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.2730992595221835</v>
+        <v>-0.2835458435503639</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.009658915953913549</v>
+        <v>-0.02061749546538039</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.002527314743879572</v>
+        <v>-0.008508224617131077</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.1740106263542884</v>
+        <v>-0.1848058366127177</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.07013835378229061</v>
+        <v>0.07858333086836922</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.05875246622919406</v>
+        <v>0.06716843699106789</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.1388806439740264</v>
+        <v>0.1472555731239069</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.2185357609012542</v>
+        <v>-0.2096326711248579</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.2839172657558748</v>
+        <v>-0.2949802954506495</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.3109004077866686</v>
+        <v>-0.3220608094946797</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.1375257544624162</v>
+        <v>-0.148814117404946</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.0003968723679221853</v>
+        <v>0.009157632455988107</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.05176501423687085</v>
+        <v>0.06048844468615755</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.2542202397657576</v>
+        <v>0.2627050952417562</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.1170013614703933</v>
+        <v>-0.1081657664920854</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.2654935652798684</v>
+        <v>-0.2766894931116397</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.1848911594634544</v>
+        <v>-0.1962185925158124</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-0.0260242504582564</v>
+        <v>-0.03752207290329324</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.06789403947119155</v>
+        <v>-0.0590275347842919</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; 0.4412</t>
+          <t>X &gt; 0.4459</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2935</v>
+        <v>2938</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.03146235059438141</v>
+        <v>0.02593220390497919</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.1501229190410314</v>
+        <v>-0.1554751626269422</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.02001717698165351</v>
+        <v>0.01415548355652163</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.1329803995714371</v>
+        <v>-0.1387756000119396</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.4114898286828819</v>
+        <v>-0.4217783157469484</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.2730992595221835</v>
+        <v>-0.2835458435503639</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.009658915953913549</v>
+        <v>-0.02061749546538039</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.002527314743879572</v>
+        <v>-0.008508224617131077</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.1740106263542884</v>
+        <v>-0.1848058366127177</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.07013835378229061</v>
+        <v>0.07858333086836922</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.05875246622919406</v>
+        <v>0.06716843699106789</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.1388806439740264</v>
+        <v>0.1472555731239069</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.2185357609012542</v>
+        <v>-0.2096326711248579</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.2839172657558748</v>
+        <v>-0.2949802954506495</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.3109004077866686</v>
+        <v>-0.3220608094946797</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.1375257544624162</v>
+        <v>-0.148814117404946</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.0003968723679221853</v>
+        <v>0.009157632455988107</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.05176501423687085</v>
+        <v>0.06048844468615755</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>0.2542202397657576</v>
+        <v>0.2627050952417562</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.1170013614703933</v>
+        <v>-0.1081657664920854</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.2654935652798684</v>
+        <v>-0.2766894931116397</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.1848911594634544</v>
+        <v>-0.1962185925158124</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.0260242504582564</v>
+        <v>-0.03752207290329324</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.06789403947119155</v>
+        <v>-0.0590275347842919</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; 0.5148</t>
+          <t>X &gt; 0.5202</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2935</v>
+        <v>2938</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.03146235059438141</v>
+        <v>0.02593220390497919</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.1501229190410314</v>
+        <v>-0.1554751626269422</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.02001717698165351</v>
+        <v>0.01415548355652163</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.1329803995714371</v>
+        <v>-0.1387756000119396</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.4114898286828819</v>
+        <v>-0.4217783157469484</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.2730992595221835</v>
+        <v>-0.2835458435503639</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.009658915953913549</v>
+        <v>-0.02061749546538039</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.002527314743879572</v>
+        <v>-0.008508224617131077</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.1740106263542884</v>
+        <v>-0.1848058366127177</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.07013835378229061</v>
+        <v>0.07858333086836922</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.05875246622919406</v>
+        <v>0.06716843699106789</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.1388806439740264</v>
+        <v>0.1472555731239069</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.2185357609012542</v>
+        <v>-0.2096326711248579</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.2839172657558748</v>
+        <v>-0.2949802954506495</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.3109004077866686</v>
+        <v>-0.3220608094946797</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.1375257544624162</v>
+        <v>-0.148814117404946</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.0003968723679221853</v>
+        <v>0.009157632455988107</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.05176501423687085</v>
+        <v>0.06048844468615755</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.2542202397657576</v>
+        <v>0.2627050952417562</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.1170013614703933</v>
+        <v>-0.1081657664920854</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.2654935652798684</v>
+        <v>-0.2766894931116397</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.1848911594634544</v>
+        <v>-0.1962185925158124</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-0.0260242504582564</v>
+        <v>-0.03752207290329324</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.06789403947119155</v>
+        <v>-0.0590275347842919</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; 0.5883</t>
+          <t>X &gt; 0.5945</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2931</v>
+        <v>2932</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.002598350264115368</v>
+        <v>-0.0004813836656296644</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.2126867509036003</v>
+        <v>-0.2154613101557672</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.006474495366305177</v>
+        <v>-0.008695485380719958</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.158720141365059</v>
+        <v>-0.1604952853402608</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.4031877307473266</v>
+        <v>-0.4094881649085877</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.2648605675871352</v>
+        <v>-0.2713507103960495</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.03394597788077647</v>
+        <v>0.02762156620099177</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.01257465708356165</v>
+        <v>0.006394164732640206</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.1642562397339802</v>
+        <v>-0.1703420911930422</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.04729740828013718</v>
+        <v>0.09516402357286324</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.06950573501521262</v>
+        <v>0.08317275642897926</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.1501261404355674</v>
+        <v>0.1639971541379381</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.2402564056808956</v>
+        <v>-0.2253241453584707</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.3054330175175082</v>
+        <v>-0.3103948613154444</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.3315631041921918</v>
+        <v>-0.3361927351773701</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.1587697938306931</v>
+        <v>-0.1638106137936006</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.02047669873888225</v>
+        <v>-0.00524787114007097</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>0.06515729212894428</v>
+        <v>0.08044542784281106</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.2675984531018827</v>
+        <v>0.2826409301017279</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.1043796864348963</v>
+        <v>-0.08936327548061485</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.2523292872795793</v>
+        <v>-0.2571223906357432</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.171508807068939</v>
+        <v>-0.1763251545680475</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.01279551480804031</v>
+        <v>-0.01785869827609332</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.0546188056288841</v>
+        <v>-0.03924628016982723</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; 0.6618</t>
+          <t>X &gt; 0.6689</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2916</v>
+        <v>2913</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.004352708690625207</v>
+        <v>0.07421764457757973</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.2103190669027839</v>
+        <v>-0.2081503352389902</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.06385764351330181</v>
+        <v>-0.05893627595601458</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.2473457607497664</v>
+        <v>-0.2412336230395482</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.4912255577325695</v>
+        <v>-0.5238208999017644</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.3190603186851959</v>
+        <v>-0.3518978798839711</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.01478589253068918</v>
+        <v>-0.04600383037718103</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.03485676334484111</v>
+        <v>-0.0314235545562056</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.2128224401651266</v>
+        <v>-0.2095897705086287</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.1062383239288351</v>
+        <v>0.1652123327516009</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.05884524198947361</v>
+        <v>0.1171865515969159</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.07295336242705019</v>
+        <v>0.1319370238926325</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.2795028734987923</v>
+        <v>-0.2184003897551818</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.343891709507723</v>
+        <v>-0.3025867268451634</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.3325761723050675</v>
+        <v>-0.3242687598357819</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.1961740372197553</v>
+        <v>-0.1546284765462858</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.04618675186199539</v>
+        <v>0.1086161091528908</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.0985875775655245</v>
+        <v>0.1613190071877213</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.3352164783521729</v>
+        <v>0.3634530256909514</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.03961116820828892</v>
+        <v>-0.0121648075319456</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.2197768312049391</v>
+        <v>-0.2117754473772635</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.1381390093783139</v>
+        <v>-0.1299416529235131</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>0.0542822532818974</v>
+        <v>0.06210140825313459</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>0.01263446682550295</v>
+        <v>0.0754252609154662</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; 0.7354</t>
+          <t>X &gt; 0.7432</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2865</v>
+        <v>2863</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.1906966185126322</v>
+        <v>0.1732999045985437</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.2298239661648864</v>
+        <v>-0.2468691424442895</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.1246824347760906</v>
+        <v>-0.1395277630334562</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.4375998579797553</v>
+        <v>-0.4514841722027541</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.7488171644062049</v>
+        <v>-0.7332207861361226</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.5422847585805712</v>
+        <v>-0.526897473721732</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.2537411611760589</v>
+        <v>-0.271831382145443</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.1650755075839356</v>
+        <v>-0.2174826814107078</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.3817355839795553</v>
+        <v>-0.4343028365217592</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.0609740174164628</v>
+        <v>0.02994663226851202</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.0616814546857043</v>
+        <v>-0.09331907124745698</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.1119793250228085</v>
+        <v>-0.1431476145575914</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.4507999132718297</v>
+        <v>-0.4801263415682442</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.4776551364417188</v>
+        <v>-0.5271105104939409</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.5937599257845818</v>
+        <v>-0.6422796422495054</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.2914409454867268</v>
+        <v>-0.3407771090697835</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.06210033075793575</v>
+        <v>0.03389025024434744</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>0.08246021914809631</v>
+        <v>0.0544461657944737</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.3194480133722521</v>
+        <v>0.2911826464663747</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.03050906555090904</v>
+        <v>-0.05938126231087892</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.2042136632707141</v>
+        <v>-0.2530090771715336</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.1895497423795689</v>
+        <v>-0.2382458746328595</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>0.1410036459951414</v>
+        <v>0.05706887411817263</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>0.09996632068828148</v>
+        <v>0.071948008918163</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; 0.8089</t>
+          <t>X &gt; 0.8175</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2731</v>
+        <v>2712</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.2335485324534972</v>
+        <v>0.1827899154740038</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.2638423749405803</v>
+        <v>-0.2420953612693353</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.01065616949399839</v>
+        <v>-0.04930755253741381</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.4131545986933389</v>
+        <v>-0.5588314124899441</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.6125162526292911</v>
+        <v>-0.7643295561373407</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.5142389141199359</v>
+        <v>-0.6669168678784345</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.06458167387685165</v>
+        <v>-0.2083527155389149</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.067243760966889</v>
+        <v>-0.1722431708440695</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.4058497984282923</v>
+        <v>-0.5868465070121118</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.2318179106195188</v>
+        <v>-0.3844695076791425</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.483391240848313</v>
+        <v>-0.6033689032029272</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.522657750859139</v>
+        <v>-0.5672103046876273</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.7502122128212747</v>
+        <v>-0.8239649884691147</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.7311514810900093</v>
+        <v>-0.8980390872604289</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.6381674289739792</v>
+        <v>-0.7626133034046632</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.3867332534962031</v>
+        <v>-0.4406421701383039</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.2285361182699006</v>
+        <v>-0.1849238932822388</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.01939502872768628</v>
+        <v>-0.01025827019381609</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.218577776591637</v>
+        <v>0.2276133009147117</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.08458302852962873</v>
+        <v>-0.07919828258670236</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.3865502077538991</v>
+        <v>-0.4007499754146053</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.2576986564414412</v>
+        <v>-0.3073079803711849</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>0.07556660773683888</v>
+        <v>0.06286035605801743</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>0.1094751403101881</v>
+        <v>0.082792297301026</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; 0.8824</t>
+          <t>X &gt; 0.8918</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2440</v>
+        <v>2381</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.03109032063356665</v>
+        <v>-0.07686211968457002</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.2007429489083634</v>
+        <v>-0.1807948875949634</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.273773260601871</v>
+        <v>-0.386525730942104</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.1318208525236457</v>
+        <v>-0.2000527398548471</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.311183189587986</v>
+        <v>-0.2619699162683418</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.001719351142959624</v>
+        <v>0.2408694601116323</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.4076403627059833</v>
+        <v>0.6626175128392617</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.5195919987389956</v>
+        <v>0.5515602678354483</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.3128568857911986</v>
+        <v>-0.3024888622635586</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.3930978453162481</v>
+        <v>-0.4901202573635999</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.7482359095691962</v>
+        <v>-1.010374996472578</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.5140174239806754</v>
+        <v>-0.7634980614635083</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.8388291681192044</v>
+        <v>-1.025865901713225</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.7093829416873874</v>
+        <v>-0.8703757405029151</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.9763412307176509</v>
+        <v>-1.127290254134728</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-0.5615847358336055</v>
+        <v>-0.7176031673519034</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.3684800659743459</v>
+        <v>-0.4917582206250088</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.2446154037241044</v>
+        <v>-0.4041798733623523</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.07774335133004229</v>
+        <v>-0.07956552600735023</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.1612407862407892</v>
+        <v>-0.2453149350395094</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.4587409495384946</v>
+        <v>-0.5361832506565563</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.3874369066725194</v>
+        <v>-0.6291034543917391</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>0.03471806249730491</v>
+        <v>-0.07784662339810922</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.2871249161154239</v>
+        <v>-0.3806541859816974</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 0.956</t>
+          <t>X &gt; 0.9661</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2027</v>
+        <v>1973</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.8535340029618794</v>
+        <v>0.7812634393318447</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.006373990476568281</v>
+        <v>0.0716360178310893</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.230967007215213</v>
+        <v>-0.4840654960240371</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.3568132356459941</v>
+        <v>-0.4647952691332193</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.2535506787768966</v>
+        <v>-0.2690339784825468</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.08067275775930227</v>
+        <v>0.1981303705741908</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.3862379982542876</v>
+        <v>0.6139203719848894</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.6753635881452453</v>
+        <v>0.9405476369092298</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.3831852731150391</v>
+        <v>-0.4510130233181471</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.9116821166617015</v>
+        <v>-0.9717854820071778</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.198337599729797</v>
+        <v>-1.101154987601184</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.761983595971806</v>
+        <v>-0.5944948071643594</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.9737635677594909</v>
+        <v>-0.8809747918177564</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.8714821790494511</v>
+        <v>-0.7991763335848958</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.9113264842550493</v>
+        <v>-0.8721646997207628</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.8284599270482076</v>
+        <v>-0.6521123309905477</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.7164906290711457</v>
+        <v>-0.5540691117300511</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.6939719807088167</v>
+        <v>-0.5577975809708491</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.3994822192657566</v>
+        <v>-0.1602417300265344</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.4789921143420344</v>
+        <v>-0.3988350285101561</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.9236217988451756</v>
+        <v>-0.8401666215774029</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.9211771608930306</v>
+        <v>-0.784869242649286</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.1732530164613451</v>
+        <v>0.02615017120375285</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-0.4465303202093409</v>
+        <v>-0.1714885770992538</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 1.03</t>
+          <t>X &gt; 1.04</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1569</v>
+        <v>1510</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.60734601992916</v>
+        <v>1.280412729087722</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.1046271302377875</v>
+        <v>-0.2001807075795483</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.4141652122203325</v>
+        <v>-0.6830253524027938</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.254620969998669</v>
+        <v>-1.622980938177932</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.5711530048784397</v>
+        <v>-0.7387032422764719</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.1938743234305917</v>
+        <v>-0.2517214642037615</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.2696555378673722</v>
+        <v>-0.525630820160977</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.7560663584427729</v>
+        <v>0.5136807917394322</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.815267587317777</v>
+        <v>-0.9228549253655771</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.335295891488215</v>
+        <v>-1.432092288943259</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.060936624372879</v>
+        <v>-1.02619349055194</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.7960372960372908</v>
+        <v>-0.541910732550889</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.312311657260565</v>
+        <v>-1.165059737414794</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.025409256096701</v>
+        <v>-0.7920792079207928</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-1.329318365825166</v>
+        <v>-1.054182901540955</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-1.01491682031822</v>
+        <v>-0.8831712101196914</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-1.085397282914982</v>
+        <v>-0.9783662547246763</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.9359277728016124</v>
+        <v>-0.9510192520025598</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.2367732672945309</v>
+        <v>-0.3655793025871716</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.7499204328453217</v>
+        <v>-0.8675971695701747</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-1.22946711810043</v>
+        <v>-1.277780663810205</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.5674038722838759</v>
+        <v>-0.6918132565892563</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>0.1913908936835043</v>
+        <v>0.350364963503651</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.1394898974651397</v>
+        <v>0.009632048028720419</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 1.103</t>
+          <t>X &gt; 1.115</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1173</v>
+        <v>1121</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.9250347123926588</v>
+        <v>0.1036462786385144</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.2086212447194455</v>
+        <v>-0.00736994352781295</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.5039424394263108</v>
+        <v>-0.4268821488092414</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.809451728950833</v>
+        <v>-1.444618181668943</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.8597017686544675</v>
+        <v>-0.5826350213262188</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.3341276801823767</v>
+        <v>0.09626014922380222</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.4301748613057796</v>
+        <v>-0.005740189745445434</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.270680812515586</v>
+        <v>0.6017879580612657</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.9101226161399367</v>
+        <v>-0.4578530786823549</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.260229213350044</v>
+        <v>-0.8761588256408359</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.901124183522839</v>
+        <v>-0.4247942189399083</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.7078269482849606</v>
+        <v>-0.6526490740042519</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.5951182145810279</v>
+        <v>-0.1262471527815521</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.05246823444391424</v>
+        <v>0.4519634911981498</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.3210657857799006</v>
+        <v>-0.2061798063824085</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-0.6105184197366142</v>
+        <v>-0.5363636363636317</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-1.084748168307307</v>
+        <v>-1.06268883977053</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.594493489164492</v>
+        <v>-0.544753742879962</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-0.3280012424289396</v>
+        <v>-0.2761787456888385</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.5664893617021249</v>
+        <v>-0.3930616481237692</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-0.9394770047426348</v>
+        <v>-0.5791015772306238</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.7096580200068345</v>
+        <v>-0.4766944192101334</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>0.04191552451846547</v>
+        <v>0.2076352578836662</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.3922316447555332</v>
+        <v>0.3102151366853647</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 1.177</t>
+          <t>X &gt; 1.189</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>925</v>
+        <v>898</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.1308089265107313</v>
+        <v>0.4340427544094467</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.6044369851842717</v>
+        <v>0.8701910661917935</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.346956568154738</v>
+        <v>-0.2868513400850929</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.275572652561635</v>
+        <v>-1.159709563036969</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.6140819880748154</v>
+        <v>-0.440288005288977</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.2118636116271659</v>
+        <v>0.02988846780786503</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.447095335079041</v>
+        <v>-0.2367387213598846</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.02703819144541342</v>
+        <v>0.03875968992248602</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.591920065557026</v>
+        <v>-1.408262727846548</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.25811284984637</v>
+        <v>-1.959448913860861</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.445540450330597</v>
+        <v>-1.131065546643505</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.7558507154847334</v>
+        <v>-0.5228969900028062</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.4809877897307473</v>
+        <v>-0.02836893181925149</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.1641314683646797</v>
+        <v>0.1945033571059724</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-0.6513912772397674</v>
+        <v>-0.3526521491316359</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-1.178787798685612</v>
+        <v>-0.8681431406181659</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-1.312881492834535</v>
+        <v>-1.002060277595639</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-0.7706157179912978</v>
+        <v>-0.6629498160450069</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-1.138717661711141</v>
+        <v>-1.048118985126855</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-1.05966522678186</v>
+        <v>-0.9074973748869226</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-1.27889155370638</v>
+        <v>-1.11633942716886</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.9228811665844106</v>
+        <v>-0.6360118624377975</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-0.5842451630233043</v>
+        <v>-0.4068733438460157</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.2277540698593299</v>
+        <v>0.07408727598193821</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 1.25</t>
+          <t>X &gt; 1.263</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>758</v>
+        <v>738</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.6452503219978922</v>
+        <v>0.8557971818700452</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.7744514413348895</v>
+        <v>0.6552485714396994</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.9870551272634174</v>
+        <v>-1.319683229269145</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.044680461453943</v>
+        <v>-1.153478700685625</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.2862733604908456</v>
+        <v>-0.6077441149831344</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.09910874748405973</v>
+        <v>-0.4802730187269759</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.04786743320830311</v>
+        <v>0.3075558253826429</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.163530921723904</v>
+        <v>0.4342026802247148</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.035011108557427</v>
+        <v>-0.7976077269476463</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.808846519326856</v>
+        <v>-1.705658538119266</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.8765925153694027</v>
+        <v>-0.755923220281673</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.1030548398969415</v>
+        <v>-0.2238618129188552</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.4829802574053872</v>
+        <v>0.2197390942951714</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.6563602884763</v>
+        <v>0.2692962124358687</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>0.7869027336495193</v>
+        <v>0.8290148904980654</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>0.4082092294258146</v>
+        <v>0.4761758313855751</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.8011247579382825</v>
+        <v>0.7482126862890155</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>0.4326367305123142</v>
+        <v>0.3727359878805601</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.6487598934441294</v>
+        <v>0.588627368804886</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>0.5722990777338595</v>
+        <v>0.8568840064129972</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>0.02909866873590516</v>
+        <v>0.3143378384469671</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>0.6119051414200456</v>
+        <v>1.187001362132712</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>0.8347094116041021</v>
+        <v>1.190473364587668</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>1.418398679195789</v>
+        <v>1.656646531418581</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 1.324</t>
+          <t>X &gt; 1.338</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>627</v>
+        <v>604</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.072714037287184</v>
+        <v>1.441120099682792</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.9827791493354638</v>
+        <v>0.7784744488739506</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.163283098766975</v>
+        <v>-1.807085583763595</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.400885935769651</v>
+        <v>-1.77520124954944</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.289965244603223</v>
+        <v>-1.528176926486999</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.420260949056754</v>
+        <v>-1.58019886143358</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.39947628745999</v>
+        <v>-1.106775891189812</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.2494595044071275</v>
+        <v>0.1001611789085857</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.706921408950699</v>
+        <v>-2.00356616062885</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-2.957704355491181</v>
+        <v>-3.601564344916163</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.36538006452848</v>
+        <v>-2.832455197803746</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.690578896461247</v>
+        <v>-2.616155096301242</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.5893149480167494</v>
+        <v>-1.168332791992974</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.3337242232800364</v>
+        <v>-0.8935438998445306</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-0.3567254146225878</v>
+        <v>-0.72524091643335</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-0.1441853897093139</v>
+        <v>-0.4614325068870428</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>0.6771349288806121</v>
+        <v>0.5616751495239072</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.2240268311637124</v>
+        <v>-0.534901091487356</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>0.4698033381375311</v>
+        <v>0.1768580580320034</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>0.3383757961783473</v>
+        <v>0.4624943009265294</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.5232959503992234</v>
+        <v>-0.411177694854068</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>0.9931056818562567</v>
+        <v>0.8374796549951142</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>0.4082114083806374</v>
+        <v>0.2841397979407319</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>1.448697501329079</v>
+        <v>1.367247942068452</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 1.397</t>
+          <t>X &gt; 1.412</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.837849128319192</v>
+        <v>0.9730888564362132</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.8709977389050678</v>
+        <v>0.2616642238114366</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.94346232913071</v>
+        <v>-2.306298328044413</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-2.10375010726851</v>
+        <v>-2.353012074595135</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.8085032871265057</v>
+        <v>-0.5077560728405928</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.8058405191381723</v>
+        <v>-0.8878976372158078</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.025201116136856</v>
+        <v>-1.554945708171516</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.5412626885290948</v>
+        <v>0.2501761804087437</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.897935517546621</v>
+        <v>-1.981063910403833</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-3.96567111315894</v>
+        <v>-4.079737162197894</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-2.767097428298683</v>
+        <v>-3.048101762460213</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.306819797577653</v>
+        <v>-2.379881468938514</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.582882180574963</v>
+        <v>-1.499852229946775</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.434553224511347</v>
+        <v>-1.341424465027139</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-1.169270045803728</v>
+        <v>-0.8610478385090303</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-0.4650157742339687</v>
+        <v>-0.07690759588292906</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>0.6971868279134057</v>
+        <v>0.7379418705551544</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.3337225141078051</v>
+        <v>-0.1259121159984673</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.0675858340092006</v>
+        <v>0.4694859062920784</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>0.06944444444444287</v>
+        <v>0.5802139393320829</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-0.288570779368321</v>
+        <v>0.0376677713660527</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>0.746585276100177</v>
+        <v>0.9123921521622833</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>0.5774657129732859</v>
+        <v>0.9967527962032747</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>1.429168158491464</v>
+        <v>1.871490885185324</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 1.471</t>
+          <t>X &gt; 1.486</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>444</v>
+        <v>427</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.906235737106343</v>
+        <v>1.451745479160628</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.6782030796048772</v>
+        <v>0.191042754884883</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-2.205149509760901</v>
+        <v>-2.635865183034994</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-2.918942822954058</v>
+        <v>-3.458383523178952</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.823362496121284</v>
+        <v>-1.578666522570224</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.03494305648281681</v>
+        <v>-0.2289096387984273</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.632777661700956</v>
+        <v>-1.569514472740281</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.1020905115724275</v>
+        <v>0.4832764135089747</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.745419416322342</v>
+        <v>-0.8738378031777216</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-4.088761553549176</v>
+        <v>-3.744655577116305</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-2.469110806613209</v>
+        <v>-2.071994536352989</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-2.523989463451336</v>
+        <v>-2.350743939800985</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.9578977222972327</v>
+        <v>-0.7736467643417839</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.5066087934212717</v>
+        <v>-0.5274359211622084</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-1.165540032458573</v>
+        <v>-0.7182894991165938</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>0.01147194944476837</v>
+        <v>0.3433871424525563</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>0.7762546597902258</v>
+        <v>0.9104045849143461</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.2276051607994347</v>
+        <v>-0.1290155581591748</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>0.4379562043795673</v>
+        <v>0.554165542391317</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>0.625</v>
+        <v>0.8816360103733132</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.1429195101215512</v>
+        <v>0.1048978049365559</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>0.9047209398538243</v>
+        <v>1.200012030881084</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>1.316655737877603</v>
+        <v>1.24029470589241</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>1.916390074284813</v>
+        <v>1.867038565081316</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 1.544</t>
+          <t>X &gt; 1.561</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>347</v>
+        <v>328</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.325878594249204</v>
+        <v>0.4132069406220893</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.009296920395122754</v>
+        <v>-0.2218701580280253</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-2.440401395942573</v>
+        <v>-2.861090408260218</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-2.867661757846335</v>
+        <v>-3.716958426038651</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.227200883844596</v>
+        <v>-1.779607996609435</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.1804374169696175</v>
+        <v>-0.08206779238516759</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.526369451602442</v>
+        <v>-1.289794193019993</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.4873395131941791</v>
+        <v>0.8562367864693456</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.4542488581036963</v>
+        <v>-0.9204578497977707</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-3.239578521746694</v>
+        <v>-3.814585647046371</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-2.67786293279228</v>
+        <v>-3.237495701854158</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-2.956956836267182</v>
+        <v>-3.21321480227185</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.3458158708462804</v>
+        <v>-0.8261991036310548</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.5822526054756878</v>
+        <v>0.1685274910469801</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>0.210677688277471</v>
+        <v>0.1182869290287343</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>1.267826578204925</v>
+        <v>1.016625218752878</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>1.998286198177041</v>
+        <v>1.490610817337711</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>1.028749467960722</v>
+        <v>0.7778673779542231</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>1.82124150697323</v>
+        <v>1.297710126659702</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>1.720100864553309</v>
+        <v>1.66989213649429</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>1.176900455555355</v>
+        <v>0.8224679197477727</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>2.253683152074139</v>
+        <v>2.27101220224111</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>1.952089442475575</v>
+        <v>1.6308527683817</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>2.74070141732814</v>
+        <v>2.469654661499888</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 1.618</t>
+          <t>X &gt; 1.635</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.3894498729040805</v>
+        <v>-0.2317562043410604</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-1.089588891198048</v>
+        <v>-0.9453208814787502</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-4.533246468730347</v>
+        <v>-5.034855082024897</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-4.88073941562314</v>
+        <v>-4.415570364285934</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-1.949305903943888</v>
+        <v>-1.882234781047067</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.6632401920359996</v>
+        <v>0.5948077409281822</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-2.901307789291494</v>
+        <v>-1.491814395040201</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.1168408618932375</v>
+        <v>1.295108259823571</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.306844538285588</v>
+        <v>-0.1959716080701384</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-5.743683612058675</v>
+        <v>-4.800304908627702</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-5.103023978642973</v>
+        <v>-4.143103504013681</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-5.74841824841824</v>
+        <v>-5.188136432365887</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-3.576206170202092</v>
+        <v>-2.863022637153044</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-3.064962248635716</v>
+        <v>-2.31781798869541</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-2.258692022471543</v>
+        <v>-1.443394236467554</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-1.297331606549797</v>
+        <v>-0.8490073145245631</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-1.065124934398355</v>
+        <v>-0.599782689049924</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-1.536408716794</v>
+        <v>-1.087765155323218</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.5876848212614547</v>
+        <v>-0.4887320119467802</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.766941391941387</v>
+        <v>-0.3018862019787534</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.9438414346389763</v>
+        <v>-0.8444323699447835</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>0.4454049749198745</v>
+        <v>0.6122887184545505</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.3787209574990911</v>
+        <v>0.1204799060323936</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.08836193046719387</v>
+        <v>0.4277894152612163</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 1.691</t>
+          <t>X &gt; 1.709</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.5640735588608408</v>
+        <v>-1.140847113431967</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.420780173983637</v>
+        <v>-1.475623911781781</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-4.006689692173573</v>
+        <v>-5.413642960812773</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-3.27817531305903</v>
+        <v>-4.367803010406263</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.7588297134676907</v>
+        <v>-1.411882402297735</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>2.312950284154475</v>
+        <v>1.805386814102668</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.09777645979275462</v>
+        <v>-0.1945780724231625</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>3.184606429658807</v>
+        <v>3.588124188407519</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2.264584033142981</v>
+        <v>2.106768730728305</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-2.836174454549521</v>
+        <v>-3.234674864089911</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-2.561815187434185</v>
+        <v>-2.45300100873002</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-3.802447552447553</v>
+        <v>-3.746978838573959</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.1192464632423835</v>
+        <v>-0.809227199846319</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.1401659564924884</v>
+        <v>-0.5226918630949342</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>1.404311640532114</v>
+        <v>0.8496216921163935</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>2.480140920922729</v>
+        <v>1.951622827257339</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>2.346047226773806</v>
+        <v>2.32531990347784</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>1.279525349140066</v>
+        <v>0.6976365600627545</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>1.976417742841107</v>
+        <v>1.421142154185056</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>1.201923076923073</v>
+        <v>1.607987964153082</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>0.6587226679251188</v>
+        <v>1.065441796187052</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>2.02507530459021</v>
+        <v>2.00482426117388</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>1.33831200953388</v>
+        <v>1.771684760457958</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>0.7816014394961712</v>
+        <v>1.188238294036729</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 1.765</t>
+          <t>X &gt; 1.784</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.6620732129797062</v>
+        <v>-1.439589251796747</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-2.804477643286688</v>
+        <v>-4.919020138196878</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-5.752027687511564</v>
+        <v>-8.243831640058055</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-4.041578576462292</v>
+        <v>-7.06999320667061</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-2.58866654330452</v>
+        <v>-4.563653275587598</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.840922312126501</v>
+        <v>0.05369265734522344</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.1440650320487364</v>
+        <v>-1.633357211742258</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>3.819804564856938</v>
+        <v>1.910087394460078</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>2.043138811697766</v>
+        <v>0.04074655089707591</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-2.367060235435297</v>
+        <v>-3.916882500935593</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.8805797561987561</v>
+        <v>-2.368937508455197</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-3.583916083916087</v>
+        <v>-5.195457612540132</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>1.958259364263434</v>
+        <v>0.05080707219610048</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.08127926495272675</v>
+        <v>-0.8072144794097227</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>1.684031920252387</v>
+        <v>0.4454702484874247</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>3.491213181994979</v>
+        <v>2.313742520748889</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>3.963180093906665</v>
+        <v>2.816768058930649</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>2.646075465690181</v>
+        <v>1.438042004791001</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>3.468259234682591</v>
+        <v>2.927818736033792</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>3.655303030303024</v>
+        <v>3.114664546001819</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>1.899981409183859</v>
+        <v>1.298233027717323</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>4.248268777783686</v>
+        <v>3.770157766945161</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>3.31092273214459</v>
+        <v>2.770747129108742</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>3.234981392876122</v>
+        <v>2.057972200726233</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 1.838</t>
+          <t>X &gt; 1.858</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-2.938827288103738</v>
+        <v>-1.297097113431967</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-4.744591038042181</v>
+        <v>-3.975623911781781</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-7.300849236333114</v>
+        <v>-7.757392960812773</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-8.014642549526272</v>
+        <v>-8.470346980255513</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-3.935467890105876</v>
+        <v>-3.706481940991765</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-3.007562536358343</v>
+        <v>-2.73211418009123</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-4.521169409153117</v>
+        <v>-3.07911598234179</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.3552796102272282</v>
+        <v>0.6109265411591096</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-1.795245026686075</v>
+        <v>-0.9348878642277825</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-5.532043400418473</v>
+        <v>-4.882406714867443</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-5.257684133303137</v>
+        <v>-4.60834707270552</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-7.75900025900026</v>
+        <v>-7.268048857105903</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-2.957565551561473</v>
+        <v>-3.629306162057254</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-3.919663103336568</v>
+        <v>-3.056734244853054</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-2.356372120151654</v>
+        <v>-2.127575955132016</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>0.4609101516919551</v>
+        <v>0.05411255411255667</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>1.808297939024513</v>
+        <v>1.507497004436672</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>0.2218330414477521</v>
+        <v>-0.1846452866860986</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>0.4379562043795673</v>
+        <v>0.03124609423822733</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>1.36574074074074</v>
+        <v>1.011742697857045</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.6589411497387019</v>
+        <v>-0.324454263759776</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>2.968807498322398</v>
+        <v>3.567953743085084</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>1.021360442582306</v>
+        <v>1.461476074614765</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>0.2046783625730981</v>
+        <v>0.591993027740692</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 1.912</t>
+          <t>X &gt; 1.932</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-1.042542458382378</v>
+        <v>-0.004483477068326636</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-3.132103937938979</v>
+        <v>-3.975623911781781</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-5.891475260587455</v>
+        <v>-5.413642960812773</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-6.605268573780613</v>
+        <v>-7.03568788934642</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-2.545759597742716</v>
+        <v>-3.251378278490854</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-1.473639232523539</v>
+        <v>-0.3121185144118357</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-2.246505364577565</v>
+        <v>-0.5658884691142845</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>2.784674503178216</v>
+        <v>4.711455641688204</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1.056279063776067</v>
+        <v>2.901090971751053</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-3.257379355842922</v>
+        <v>-0.6496024820632158</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-2.983020088727585</v>
+        <v>-0.3755428399012928</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-5.916981248839647</v>
+        <v>-3.432070021127068</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-1.731737954052463</v>
+        <v>-0.8515283842794759</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-1.068139012874425</v>
+        <v>-0.1466813348001494</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>0.04284125251305682</v>
+        <v>1.972953145397078</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>1.522857054346815</v>
+        <v>2.567340067340069</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>3.158674864622675</v>
+        <v>3.35934885628852</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>2.168735696315004</v>
+        <v>2.328582226541414</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>3.269814611459211</v>
+        <v>4.396325459317588</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>3.456858407079643</v>
+        <v>4.583171269285614</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>2.028702245869297</v>
+        <v>2.188773249467737</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>5.492570199076248</v>
+        <v>6.742556917688255</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>3.112478108921209</v>
+        <v>4.239253852392537</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>3.036536769652741</v>
+        <v>4.163421599169261</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 1.985</t>
+          <t>X &gt; 2.007</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-1.546461831282706</v>
+        <v>-0.3799775482145691</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-1.881637345927032</v>
+        <v>-0.7147543465643835</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-3.836094158674811</v>
+        <v>-4.32668643907364</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-8.850962740685169</v>
+        <v>-9.387466545472904</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-5.990426074096312</v>
+        <v>-4.81403580445113</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.4269173750680295</v>
+        <v>0.8674358761517311</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-1.199783507122056</v>
+        <v>0.7304078271820131</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>2.822737116176597</v>
+        <v>4.896640826873387</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.7137155467906311</v>
+        <v>2.71590578656587</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-3.285926315591709</v>
+        <v>-1.390343222803956</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-3.011567048476373</v>
+        <v>-1.116283580642033</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-6.516467403564178</v>
+        <v>-4.728366317423358</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-2.264614536029811</v>
+        <v>-1.40708393983504</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.3354337126555649</v>
+        <v>0.5940594059405981</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>1.156172682715734</v>
+        <v>2.158138330582261</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>1.751232732337115</v>
+        <v>2.752525252525253</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>3.767676672596792</v>
+        <v>4.840830337770001</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>2.587424439297216</v>
+        <v>3.624878522837705</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>3.878816419433328</v>
+        <v>4.951881014873145</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>5.141129032258064</v>
+        <v>6.249837935952286</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>1.372122171647206</v>
+        <v>2.37395843465292</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>6.672511202026094</v>
+        <v>7.853668028799383</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>4.79674873409963</v>
+        <v>5.905920519059208</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>4.720807394831162</v>
+        <v>5.830088265835933</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 2.059</t>
+          <t>X &gt; 2.081</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-1.293169024798409</v>
+        <v>-1.009268166063549</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.4378683489665534</v>
+        <v>-1.344044964413364</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-2.43694919171017</v>
+        <v>-1.466274539760143</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-7.970019613337065</v>
+        <v>-6.126596980255513</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-4.720831567035816</v>
+        <v>-3.129054119469451</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.9192091227037267</v>
+        <v>-0.2754212667054006</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.4872559776493119</v>
+        <v>2.412089508863701</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>2.848647208157423</v>
+        <v>6.187932118164674</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.4805247189631814</v>
+        <v>3.526716597376684</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-2.70294924602311</v>
+        <v>0.05109821863748465</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-2.428589978907773</v>
+        <v>0.3251578607994077</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-6.322141713707978</v>
+        <v>-4.007645596702638</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-2.627355823761377</v>
+        <v>-1.076753609504706</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.4390740805788695</v>
+        <v>1.404870216751412</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>1.311633234600691</v>
+        <v>3.449429621873549</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>1.906693284222072</v>
+        <v>4.04381654381654</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>4.182238144290011</v>
+        <v>6.612602109541768</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>2.872435451086311</v>
+        <v>5.156410054369246</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>4.293377891126546</v>
+        <v>6.723652786644912</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>5.685240963855421</v>
+        <v>6.910498596612939</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>2.732402000640604</v>
+        <v>3.665249725944207</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>8.680543330540154</v>
+        <v>8.994809169940517</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>5.340860665696987</v>
+        <v>5.215229828368521</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>7.674557880645388</v>
+        <v>7.842100277847941</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 2.133</t>
+          <t>X &gt; 2.155</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-4.398759086910211</v>
+        <v>-2.916209432272545</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.3861085145980141</v>
+        <v>-1.801710868303523</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-1.825808978684151</v>
+        <v>-4.689005279653351</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-5.438153016514995</v>
+        <v>-8.300510023733771</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-2.904872076901356</v>
+        <v>-3.521210982214548</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.180843260743103</v>
+        <v>-1.86365656082306</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.8572524910079196</v>
+        <v>-0.3309520401479986</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>4.926523932445875</v>
+        <v>3.868448455397434</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>3.51876463514968</v>
+        <v>2.417398323879297</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.1536215002574366</v>
+        <v>-1.340591979022861</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.1207377668578999</v>
+        <v>-1.066532336860938</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-4.506182223573518</v>
+        <v>-4.330356367174602</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-1.282847355104145</v>
+        <v>-2.468443807165052</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.05492880381966359</v>
+        <v>0.2955519432540257</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>2.184690681780715</v>
+        <v>2.622483272539149</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>4.229026093720933</v>
+        <v>4.709407507914975</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>6.993483124209689</v>
+        <v>7.560564997803169</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>5.43922434579558</v>
+        <v>5.963186980549153</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>5.655347508727395</v>
+        <v>6.179078361473479</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>7.291666666666657</v>
+        <v>6.365924171441506</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>5.299190895349874</v>
+        <v>4.330840690042642</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>11.02033728898262</v>
+        <v>10.22514398236489</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>6.947286368508223</v>
+        <v>6.022006754548428</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>9.769895753877442</v>
+        <v>8.931249128190821</v>
       </c>
     </row>
   </sheetData>
@@ -5284,2379 +5284,2379 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; 0.07354</t>
+          <t>X &lt; 0.07432</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.985949362740044</v>
+        <v>-0.9526750704212148</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.6759635870617871</v>
+        <v>-0.6422905784484456</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-2.115664051147924</v>
+        <v>-2.080309627479437</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-1.324081020255065</v>
+        <v>-1.287887302836161</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.4611868291294954</v>
+        <v>0.5268598590251727</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.4269173750680295</v>
+        <v>-0.3614427720817588</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-2.059998560885489</v>
+        <v>-1.993606509735542</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-2.123499442963187</v>
+        <v>-2.056764191047755</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-1.006714560736256</v>
+        <v>-0.9400081919287544</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-2.521187717148997</v>
+        <v>-2.573138921728685</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-2.462345691412963</v>
+        <v>-2.514133043007618</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-2.956956836267182</v>
+        <v>-3.007936209896478</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.6331721926853646</v>
+        <v>-0.6902380616988282</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.2079772795817831</v>
+        <v>-0.1386992147490602</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.004839553101831484</v>
+        <v>0.06522645318763409</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-1.133917434514942</v>
+        <v>-1.064524555903866</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-2.005796933385696</v>
+        <v>-2.060510658398577</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-2.326763070863258</v>
+        <v>-2.380868603599069</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-3.622518957607475</v>
+        <v>-3.673597912329917</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-1.275647948164149</v>
+        <v>-1.331579688568787</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.306969307486078</v>
+        <v>-0.2370326860574252</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.8148898058932588</v>
+        <v>-0.7448440902310978</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-1.836010967704873</v>
+        <v>-1.766265706042788</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-1.35376319586846</v>
+        <v>-1.410132516501484</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; 0.1471</t>
+          <t>X &lt; 0.1486</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.985949362740044</v>
+        <v>-0.9526750704212148</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.6759635870617871</v>
+        <v>-0.6422905784484456</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-2.115664051147924</v>
+        <v>-2.080309627479437</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-1.324081020255065</v>
+        <v>-1.287887302836161</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.4611868291294954</v>
+        <v>0.5268598590251727</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.4269173750680295</v>
+        <v>-0.3614427720817588</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-2.059998560885489</v>
+        <v>-1.993606509735542</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-2.123499442963187</v>
+        <v>-2.056764191047755</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-1.006714560736256</v>
+        <v>-0.9400081919287544</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-2.521187717148997</v>
+        <v>-2.573138921728685</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-2.462345691412963</v>
+        <v>-2.514133043007618</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-2.956956836267182</v>
+        <v>-3.007936209896478</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.6331721926853646</v>
+        <v>-0.6902380616988282</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.2079772795817831</v>
+        <v>-0.1386992147490602</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.004839553101831484</v>
+        <v>0.06522645318763409</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-1.133917434514942</v>
+        <v>-1.064524555903866</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-2.005796933385696</v>
+        <v>-2.060510658398577</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-2.326763070863258</v>
+        <v>-2.380868603599069</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-3.622518957607475</v>
+        <v>-3.673597912329917</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-1.275647948164149</v>
+        <v>-1.331579688568787</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.306969307486078</v>
+        <v>-0.2370326860574252</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.8148898058932588</v>
+        <v>-0.7448440902310978</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-1.836010967704873</v>
+        <v>-1.766265706042788</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-1.35376319586846</v>
+        <v>-1.410132516501484</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; 0.2206</t>
+          <t>X &lt; 0.223</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.985949362740044</v>
+        <v>-0.9526750704212148</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.6759635870617871</v>
+        <v>-0.6422905784484456</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-2.115664051147924</v>
+        <v>-2.080309627479437</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-1.324081020255065</v>
+        <v>-1.287887302836161</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.4611868291294954</v>
+        <v>0.5268598590251727</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.4269173750680295</v>
+        <v>-0.3614427720817588</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-2.059998560885489</v>
+        <v>-1.993606509735542</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-2.123499442963187</v>
+        <v>-2.056764191047755</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-1.006714560736256</v>
+        <v>-0.9400081919287544</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-2.521187717148997</v>
+        <v>-2.573138921728685</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-2.462345691412963</v>
+        <v>-2.514133043007618</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-2.956956836267182</v>
+        <v>-3.007936209896478</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.6331721926853646</v>
+        <v>-0.6902380616988282</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.2079772795817831</v>
+        <v>-0.1386992147490602</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.004839553101831484</v>
+        <v>0.06522645318763409</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-1.133917434514942</v>
+        <v>-1.064524555903866</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-2.005796933385696</v>
+        <v>-2.060510658398577</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-2.326763070863258</v>
+        <v>-2.380868603599069</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-3.622518957607475</v>
+        <v>-3.673597912329917</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-1.275647948164149</v>
+        <v>-1.331579688568787</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.306969307486078</v>
+        <v>-0.2370326860574252</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.8148898058932588</v>
+        <v>-0.7448440902310978</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-1.836010967704873</v>
+        <v>-1.766265706042788</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-1.35376319586846</v>
+        <v>-1.410132516501484</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; 0.2941</t>
+          <t>X &lt; 0.2973</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.985949362740044</v>
+        <v>-0.9526750704212148</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.6759635870617871</v>
+        <v>-0.6422905784484456</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-2.115664051147924</v>
+        <v>-2.080309627479437</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-1.324081020255065</v>
+        <v>-1.287887302836161</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.4611868291294954</v>
+        <v>0.5268598590251727</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.4269173750680295</v>
+        <v>-0.3614427720817588</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-2.059998560885489</v>
+        <v>-1.993606509735542</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-2.123499442963187</v>
+        <v>-2.056764191047755</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-1.006714560736256</v>
+        <v>-0.9400081919287544</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-2.521187717148997</v>
+        <v>-2.573138921728685</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-2.462345691412963</v>
+        <v>-2.514133043007618</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-2.956956836267182</v>
+        <v>-3.007936209896478</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.6331721926853646</v>
+        <v>-0.6902380616988282</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.2079772795817831</v>
+        <v>-0.1386992147490602</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.004839553101831484</v>
+        <v>0.06522645318763409</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-1.133917434514942</v>
+        <v>-1.064524555903866</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-2.005796933385696</v>
+        <v>-2.060510658398577</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-2.326763070863258</v>
+        <v>-2.380868603599069</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-3.622518957607475</v>
+        <v>-3.673597912329917</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-1.275647948164149</v>
+        <v>-1.331579688568787</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.306969307486078</v>
+        <v>-0.2370326860574252</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.8148898058932588</v>
+        <v>-0.7448440902310978</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-1.836010967704873</v>
+        <v>-1.766265706042788</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-1.35376319586846</v>
+        <v>-1.410132516501484</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; 0.3677</t>
+          <t>X &lt; 0.3716</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.985949362740044</v>
+        <v>-0.9526750704212148</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.6759635870617871</v>
+        <v>-0.6422905784484456</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-2.115664051147924</v>
+        <v>-2.080309627479437</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-1.324081020255065</v>
+        <v>-1.287887302836161</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.4611868291294954</v>
+        <v>0.5268598590251727</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.4269173750680295</v>
+        <v>-0.3614427720817588</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-2.059998560885489</v>
+        <v>-1.993606509735542</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-2.123499442963187</v>
+        <v>-2.056764191047755</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.006714560736256</v>
+        <v>-0.9400081919287544</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-2.521187717148997</v>
+        <v>-2.573138921728685</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-2.462345691412963</v>
+        <v>-2.514133043007618</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-2.956956836267182</v>
+        <v>-3.007936209896478</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.6331721926853646</v>
+        <v>-0.6902380616988282</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.2079772795817831</v>
+        <v>-0.1386992147490602</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.004839553101831484</v>
+        <v>0.06522645318763409</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-1.133917434514942</v>
+        <v>-1.064524555903866</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-2.005796933385696</v>
+        <v>-2.060510658398577</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-2.326763070863258</v>
+        <v>-2.380868603599069</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-3.622518957607475</v>
+        <v>-3.673597912329917</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-1.275647948164149</v>
+        <v>-1.331579688568787</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.306969307486078</v>
+        <v>-0.2370326860574252</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.8148898058932588</v>
+        <v>-0.7448440902310978</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-1.836010967704873</v>
+        <v>-1.766265706042788</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-1.35376319586846</v>
+        <v>-1.410132516501484</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; 0.4412</t>
+          <t>X &lt; 0.4459</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.985949362740044</v>
+        <v>-0.9526750704212148</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.6759635870617871</v>
+        <v>-0.6422905784484456</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-2.115664051147924</v>
+        <v>-2.080309627479437</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.324081020255065</v>
+        <v>-1.287887302836161</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.4611868291294954</v>
+        <v>0.5268598590251727</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.4269173750680295</v>
+        <v>-0.3614427720817588</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-2.059998560885489</v>
+        <v>-1.993606509735542</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-2.123499442963187</v>
+        <v>-2.056764191047755</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.006714560736256</v>
+        <v>-0.9400081919287544</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.521187717148997</v>
+        <v>-2.573138921728685</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.462345691412963</v>
+        <v>-2.514133043007618</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-2.956956836267182</v>
+        <v>-3.007936209896478</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.6331721926853646</v>
+        <v>-0.6902380616988282</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.2079772795817831</v>
+        <v>-0.1386992147490602</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.004839553101831484</v>
+        <v>0.06522645318763409</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-1.133917434514942</v>
+        <v>-1.064524555903866</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-2.005796933385696</v>
+        <v>-2.060510658398577</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-2.326763070863258</v>
+        <v>-2.380868603599069</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-3.622518957607475</v>
+        <v>-3.673597912329917</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-1.275647948164149</v>
+        <v>-1.331579688568787</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.306969307486078</v>
+        <v>-0.2370326860574252</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.8148898058932588</v>
+        <v>-0.7448440902310978</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-1.836010967704873</v>
+        <v>-1.766265706042788</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-1.35376319586846</v>
+        <v>-1.410132516501484</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; 0.5148</t>
+          <t>X &lt; 0.5202</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.985949362740044</v>
+        <v>-0.9526750704212148</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.6759635870617871</v>
+        <v>-0.6422905784484456</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-2.115664051147924</v>
+        <v>-2.080309627479437</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.324081020255065</v>
+        <v>-1.287887302836161</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.4611868291294954</v>
+        <v>0.5268598590251727</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.4269173750680295</v>
+        <v>-0.3614427720817588</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-2.059998560885489</v>
+        <v>-1.993606509735542</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-2.123499442963187</v>
+        <v>-2.056764191047755</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.006714560736256</v>
+        <v>-0.9400081919287544</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-2.521187717148997</v>
+        <v>-2.573138921728685</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-2.462345691412963</v>
+        <v>-2.514133043007618</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-2.956956836267182</v>
+        <v>-3.007936209896478</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.6331721926853646</v>
+        <v>-0.6902380616988282</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.2079772795817831</v>
+        <v>-0.1386992147490602</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.004839553101831484</v>
+        <v>0.06522645318763409</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-1.133917434514942</v>
+        <v>-1.064524555903866</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-2.005796933385696</v>
+        <v>-2.060510658398577</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-2.326763070863258</v>
+        <v>-2.380868603599069</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-3.622518957607475</v>
+        <v>-3.673597912329917</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-1.275647948164149</v>
+        <v>-1.331579688568787</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.306969307486078</v>
+        <v>-0.2370326860574252</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.8148898058932588</v>
+        <v>-0.7448440902310978</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-1.836010967704873</v>
+        <v>-1.766265706042788</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-1.35376319586846</v>
+        <v>-1.410132516501484</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; 0.5883</t>
+          <t>X &lt; 0.5945</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.7956565869874694</v>
+        <v>-0.7746050752154048</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.2779536368130309</v>
+        <v>-0.2601249733529087</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.930873717103857</v>
+        <v>-1.910458247436978</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.152129716864181</v>
+        <v>-1.137212691508168</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.4015770439539921</v>
+        <v>0.4378248614222642</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.477356424062684</v>
+        <v>-0.4367800777457518</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-2.316320637140159</v>
+        <v>-2.270299886901491</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.16843605024934</v>
+        <v>-2.123882881548411</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.060821904203252</v>
+        <v>-1.020824574368312</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.355405223780288</v>
+        <v>-2.64299715061712</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.508396384015377</v>
+        <v>-2.581251733508275</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-3.001165501165495</v>
+        <v>-3.072315362009348</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.4931780871740088</v>
+        <v>-0.5861356029631324</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.07350925718272094</v>
+        <v>-0.04423846639982543</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.1222603584808297</v>
+        <v>0.1486820658068524</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.9920813012994927</v>
+        <v>-0.9590586718246286</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-1.857337718045827</v>
+        <v>-1.944039638589338</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-2.390586658766381</v>
+        <v>-2.474412257304138</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-3.673392832023005</v>
+        <v>-3.747882578507465</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-1.345021413276228</v>
+        <v>-1.433377194071362</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.3892924860857434</v>
+        <v>-0.3599908664605564</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.893513066353627</v>
+        <v>-0.8622760602790436</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-1.903534473747293</v>
+        <v>-1.867119045025134</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-1.42622292498055</v>
+        <v>-1.516512065839024</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; 0.6618</t>
+          <t>X &lt; 0.6689</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.7815594222797202</v>
+        <v>-1.191867521595235</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.290288655932315</v>
+        <v>-0.3021545240266761</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.523377549770515</v>
+        <v>-1.53609194040461</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.5842783009802019</v>
+        <v>-0.6163928986228626</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.9099560462271512</v>
+        <v>1.088632955360481</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.1425487622536608</v>
+        <v>0.05110934553948709</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.948472745547356</v>
+        <v>-1.741247501616172</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.813804250570051</v>
+        <v>-1.815377313716183</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.7392303343077486</v>
+        <v>-0.7534819685361711</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.638093549946881</v>
+        <v>-2.954969073144099</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.363734282831544</v>
+        <v>-2.680909430982176</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.435788848832324</v>
+        <v>-2.755577201777108</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.247650667733545</v>
+        <v>-0.6134331461842351</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.1521105336544579</v>
+        <v>-0.1012371175767797</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.1142973070395215</v>
+        <v>0.0586154948631048</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.7399180056579482</v>
+        <v>-0.9829894032347966</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-2.204303874407181</v>
+        <v>-2.548399382748059</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-2.51675617017051</v>
+        <v>-2.857739064074359</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-3.960384044583087</v>
+        <v>-4.073340525685822</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-1.698651452282164</v>
+        <v>-1.84150494066666</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.5821008239357113</v>
+        <v>-0.6269523121594673</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-1.072993638914419</v>
+        <v>-1.112634339142339</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-2.250500630108647</v>
+        <v>-2.272585856168483</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-1.791163633268901</v>
+        <v>-2.143500076604873</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; 0.7354</t>
+          <t>X &lt; 0.7432</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.711504583320888</v>
+        <v>-1.603810076394929</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.1775212194605444</v>
+        <v>-0.08673502289289559</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.056474019995278</v>
+        <v>-0.9691985163683299</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.4727233210171704</v>
+        <v>0.5400696864111509</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>2.163528302348269</v>
+        <v>2.056131065715725</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.04228170040178</v>
+        <v>0.9468009555168138</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.4782479830541178</v>
+        <v>-0.380703283929094</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.9437185164231465</v>
+        <v>-0.6589147286821699</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.2192928757022941</v>
+        <v>0.493683564343641</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.132126629715181</v>
+        <v>-1.945898778359506</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.483235527393845</v>
+        <v>-1.301468765827224</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.200531678059768</v>
+        <v>-1.024662613719656</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.6712317851010354</v>
+        <v>0.8151382823871884</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.8244068092726735</v>
+        <v>1.07643417402965</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>1.476336993456336</v>
+        <v>1.716992175150395</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.1757939681582315</v>
+        <v>0.08503401360543705</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-2.074684480543269</v>
+        <v>-1.904170692945321</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-2.179667896638549</v>
+        <v>-2.009011396766503</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-3.464482820010673</v>
+        <v>-3.277350071500791</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-1.588883677298313</v>
+        <v>-1.420745448916819</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.6311459999923272</v>
+        <v>-0.368709884223577</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.7071010556349364</v>
+        <v>-0.4445558456326779</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-2.496115757820718</v>
+        <v>-2.028817192630179</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-2.088554720133672</v>
+        <v>-1.918775839905493</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; 0.8089</t>
+          <t>X &lt; 0.8175</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>666</v>
+        <v>689</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.506707354928672</v>
+        <v>-1.253003408656284</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.04816089647883359</v>
+        <v>-0.1406022041117438</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.338384529473778</v>
+        <v>-1.144467852274424</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.1899746237007705</v>
+        <v>0.7474985334926743</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.020519487406162</v>
+        <v>1.569450463260893</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.6097767760482284</v>
+        <v>1.177545448200519</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.209427173644066</v>
+        <v>-0.6074278377158748</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.189028156980257</v>
+        <v>-0.740921482179516</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.1977793878629939</v>
+        <v>0.8924615029189766</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.4899054540889125</v>
+        <v>0.1195458268824865</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.5329568070384028</v>
+        <v>0.9724766702021554</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.7029646999706856</v>
+        <v>0.8384450670435939</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.674281864717074</v>
+        <v>1.886050004529004</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.602625652485123</v>
+        <v>2.188262304491317</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>1.24309561105261</v>
+        <v>1.675046543142649</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.1914490738476431</v>
+        <v>0.3853754940711411</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.4527937373595137</v>
+        <v>-0.6181068602976296</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-1.307402340861096</v>
+        <v>-1.30265770904635</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-2.290679477779356</v>
+        <v>-2.246186617977095</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-1.054160419790108</v>
+        <v>-1.044848054385881</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>0.2017396209870554</v>
+        <v>0.2388189410228634</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.3239905470993421</v>
+        <v>-0.1273027823601112</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-1.698390792911056</v>
+        <v>-1.594482641721314</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-1.687213529318797</v>
+        <v>-1.525177013957645</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; 0.8824</t>
+          <t>X &lt; 0.8918</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>957</v>
+        <v>1020</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.458353770896025</v>
+        <v>-0.1774324792856206</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.2748570863702255</v>
+        <v>-0.3170873264159226</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.2622753927800119</v>
+        <v>0.0009911855286972582</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.7110773020357897</v>
+        <v>-0.516840882694531</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.2456098077244278</v>
+        <v>-0.3648264771930272</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.039440568236373</v>
+        <v>-1.543713949632235</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-2.066935779060998</v>
+        <v>-2.510784584742098</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.345490424579559</v>
+        <v>-2.247456395348834</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.2228089069034453</v>
+        <v>-0.2528442134341304</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.0003640069889456754</v>
+        <v>0.2030096608715155</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.8997232741042751</v>
+        <v>1.414701416096399</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.3081293706293735</v>
+        <v>0.8424099382844048</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.162804818808894</v>
+        <v>1.480500317612233</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.8372813411078752</v>
+        <v>1.122952647860288</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>1.532516768737246</v>
+        <v>1.738070858604893</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.4609101516919551</v>
+        <v>0.7653666933784464</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.02771951743089573</v>
+        <v>0.2396767846086121</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.3412535070402498</v>
+        <v>0.0368928878393362</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-1.167883211678834</v>
+        <v>-0.7266476607172407</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.5637382690302459</v>
+        <v>-0.3439154648530263</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>0.2070605513360704</v>
+        <v>0.3478146438032468</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>0.02672136208177278</v>
+        <v>0.5660863294529648</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-1.055497208388083</v>
+        <v>-0.7280664090453683</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.1296999028396542</v>
+        <v>0.0784542789078273</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 0.956</t>
+          <t>X &lt; 0.9661</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1370</v>
+        <v>1428</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.531782988902577</v>
+        <v>-1.339591883306447</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.5597689610632486</v>
+        <v>-0.628343577053748</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.329171676420259</v>
+        <v>0.02568758312028052</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.2034883720930196</v>
+        <v>-0.0596513735609534</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.3507349013031131</v>
+        <v>-0.3257068391347175</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.8499867787825863</v>
+        <v>-0.975560736719352</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.291345698980059</v>
+        <v>-1.538304399689203</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.715460752067756</v>
+        <v>-1.987130592836628</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.1455604075691426</v>
+        <v>-0.06148430415289852</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.651766046318869</v>
+        <v>0.6720403898589851</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.071791737323501</v>
+        <v>0.847378194340493</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.4285317741253749</v>
+        <v>0.1493415791524626</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.7607047945311649</v>
+        <v>0.563565955343158</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.6121811954414511</v>
+        <v>0.4541992660804581</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>0.6815820758506135</v>
+        <v>0.5652867377306663</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>0.548310006025531</v>
+        <v>0.2505827505827511</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.3851254954439014</v>
+        <v>0.1166656136052779</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>0.3530283767247155</v>
+        <v>0.123595574388915</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.08682513672830794</v>
+        <v>-0.4302821139659869</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>0.0273323615160308</v>
+        <v>-0.1034782914017285</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>0.6944910570851945</v>
+        <v>0.5158818706940025</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>0.6914754616905796</v>
+        <v>0.4400359092849015</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.4195991165391746</v>
+        <v>-0.6860496023226759</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>0.05869296111325184</v>
+        <v>-0.341713788319062</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 1.03</t>
+          <t>X &lt; 1.04</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1828</v>
+        <v>1891</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.580592313853025</v>
+        <v>-1.219794481853022</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.5019559742287285</v>
+        <v>-0.2387818065186238</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.1472029309739256</v>
+        <v>0.0600412497135494</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.5292658855682362</v>
+        <v>0.7681398618497539</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.05363175582142787</v>
+        <v>0.06392833667089093</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.3800902082872142</v>
+        <v>-0.3280528456527705</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.3054831346433033</v>
+        <v>-0.1000015295431211</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.183166320466881</v>
+        <v>-0.9274771299459843</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.1655392870394081</v>
+        <v>0.2198552336432797</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.6219580124385331</v>
+        <v>0.636351543616847</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.383092957855645</v>
+        <v>0.3087735270718994</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.1585246814254546</v>
+        <v>-0.07540550210092078</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.6152766472349214</v>
+        <v>0.4355916297777966</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.3720262947358037</v>
+        <v>0.140472908050306</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>0.6405364086717711</v>
+        <v>0.3580796967505364</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.3627104790242015</v>
+        <v>0.2136803390101534</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.4250697326522044</v>
+        <v>0.290844996227932</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>0.2982939917481318</v>
+        <v>0.2704258653227427</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.3048073128241526</v>
+        <v>-0.2000607896557725</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.133196721311478</v>
+        <v>0.1979782621285153</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>0.5520018873388395</v>
+        <v>0.5320848653625561</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.0160253388887881</v>
+        <v>0.06531942649728251</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.670719827956141</v>
+        <v>-0.7701424360735132</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.3314266702496553</v>
+        <v>-0.4446634822103732</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 1.103</t>
+          <t>X &lt; 1.115</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2224</v>
+        <v>2280</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.6539871775628754</v>
+        <v>-0.2114019408675318</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.2285362939969175</v>
+        <v>-0.3277427409648368</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.146983961662464</v>
+        <v>-0.1930226025777344</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.5068601528179784</v>
+        <v>0.2735777685430918</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.007302095636362083</v>
+        <v>-0.1495871033051941</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.272826008518372</v>
+        <v>-0.486867313013839</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.2141204246847721</v>
+        <v>-0.4287592035446437</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.5822808049703596</v>
+        <v>-0.7259310456984807</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.04167253603794308</v>
+        <v>-0.2036746330145434</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.2348440607764744</v>
+        <v>0.01032723339776709</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.04209995571862635</v>
+        <v>-0.2151462228117609</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.05762175044685591</v>
+        <v>-0.1001948388581795</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.105879785077498</v>
+        <v>-0.348466267044131</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.3904272726202507</v>
+        <v>-0.6313235262256995</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.2418214995444927</v>
+        <v>-0.3005112121303242</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-0.09539312331926197</v>
+        <v>-0.1439526614657893</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.1562599045807289</v>
+        <v>0.1161757357073441</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.1014718530291248</v>
+        <v>-0.1377145564439317</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-0.2445763506271632</v>
+        <v>-0.272239294661091</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.1207322551662244</v>
+        <v>-0.2167995293711229</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>0.0817995910020457</v>
+        <v>-0.1199552862546724</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.03909928486528713</v>
+        <v>-0.169616105839431</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.4384814217539343</v>
+        <v>-0.5089072855099417</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-0.5776957381463248</v>
+        <v>-0.5149409739301589</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 1.177</t>
+          <t>X &lt; 1.189</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2472</v>
+        <v>2503</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.1960353583040728</v>
+        <v>-0.3022143630345155</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.5312108729483995</v>
+        <v>-0.6157829575074274</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.2419205851246033</v>
+        <v>-0.2645375930195328</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.07212482927650399</v>
+        <v>0.01654417282599496</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.1724691713549404</v>
+        <v>-0.2397234368982097</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.3247992902148198</v>
+        <v>-0.410610133504612</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.229704030731213</v>
+        <v>-0.3078073263412904</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.4048015445659132</v>
+        <v>-0.4043403452294996</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.2005485921441945</v>
+        <v>0.114473805658946</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.4571528869244759</v>
+        <v>0.3194326095345588</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.1505294006661444</v>
+        <v>0.01959752339194409</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.1051770809835304</v>
+        <v>-0.1963073767622703</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.1977908514882643</v>
+        <v>-0.363674939436784</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.3146052609905965</v>
+        <v>-0.4417971677645767</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-0.1260788729092468</v>
+        <v>-0.2394525644179595</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>0.06542992570325623</v>
+        <v>-0.05980861244019309</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.1168850889519959</v>
+        <v>-0.01047489646303035</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-0.08511364675904076</v>
+        <v>-0.1314396468882819</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>0.05023407190784468</v>
+        <v>0.004643274339308334</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.01893939393939803</v>
+        <v>-0.04793629478283634</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>0.1060518141225018</v>
+        <v>0.03197573338877646</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.02650483787145674</v>
+        <v>-0.1397647010550784</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-0.1560968367755038</v>
+        <v>-0.2247149087008253</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.2483960710838531</v>
+        <v>-0.3567097987088417</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 1.25</t>
+          <t>X &lt; 1.263</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2639</v>
+        <v>2663</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.3232177912929615</v>
+        <v>-0.3747030298186829</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.5077908962987294</v>
+        <v>-0.4655417609229318</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.06496123990294933</v>
+        <v>0.02154568319171091</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.07992817413392572</v>
+        <v>-0.05636911324019422</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.2945388254479937</v>
+        <v>-0.2053833437254653</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.3499388237233276</v>
+        <v>-0.2425486481024919</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.3855298117720878</v>
+        <v>-0.4541686058068137</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.4164493772793492</v>
+        <v>-0.4870163729273074</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.07327418706817923</v>
+        <v>-0.1465755288302475</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.1552583864683825</v>
+        <v>0.1112144095948011</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.1144276692919561</v>
+        <v>-0.1539300528434779</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.3339761408844097</v>
+        <v>-0.2988863323878164</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.4925325427218112</v>
+        <v>-0.4119473891429308</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.5405756668256387</v>
+        <v>-0.4239046659156855</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.5725474791841521</v>
+        <v>-0.5732564861738396</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-0.4687950637275407</v>
+        <v>-0.480932924753148</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-0.5805559432131133</v>
+        <v>-0.5552813977947153</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-0.4740822384312153</v>
+        <v>-0.4505837460278528</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-0.538207246244724</v>
+        <v>-0.5124359455068017</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.5180734292202871</v>
+        <v>-0.588057327139822</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-0.3574279743141275</v>
+        <v>-0.4334100741409372</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-0.5244584949435946</v>
+        <v>-0.6745787921303759</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-0.5905924193705516</v>
+        <v>-0.6781635650248816</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-0.7199142861574828</v>
+        <v>-0.7694027009100139</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 1.324</t>
+          <t>X &lt; 1.338</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2770</v>
+        <v>2797</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.3742648777737543</v>
+        <v>-0.4425528703616024</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.4942323579847923</v>
+        <v>-0.4384749604842426</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.06879652364911948</v>
+        <v>0.0628861999269148</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.04510142605618483</v>
+        <v>0.02560785615985139</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.0671846750889884</v>
+        <v>-0.02568759505029306</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.03928007076888207</v>
+        <v>-0.01653079728861684</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.03761257645834348</v>
+        <v>-0.1128038055032974</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.2956583648352336</v>
+        <v>-0.3707610467184494</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.03331727618451907</v>
+        <v>0.0824538292704915</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.3225243233081301</v>
+        <v>0.4335561482652253</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.1864007282574605</v>
+        <v>0.2654828011243495</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.03609699652865572</v>
+        <v>0.2211646171449857</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.2038438557742879</v>
+        <v>-0.0826173285853784</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.2599558799144432</v>
+        <v>-0.1400817202176299</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-0.2493821629636344</v>
+        <v>-0.1710357632977164</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-0.3025036041596891</v>
+        <v>-0.2328924047896948</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.487304579920945</v>
+        <v>-0.4527043671096891</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.2826714630567508</v>
+        <v>-0.2152356813021896</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.4416400465216626</v>
+        <v>-0.3708211946551998</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-0.4135863685539078</v>
+        <v>-0.4338861308492596</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.2140157048132494</v>
+        <v>-0.2411209304264403</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-0.5571291203605213</v>
+        <v>-0.5100332931013085</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-0.4267061732937592</v>
+        <v>-0.3930231708780454</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-0.625646547174199</v>
+        <v>-0.5906800176423985</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 1.397</t>
+          <t>X &lt; 1.412</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2858</v>
+        <v>2875</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.2851745861470434</v>
+        <v>-0.3052093671478318</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.4279339162226563</v>
+        <v>-0.3103403709795671</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.04474392289008478</v>
+        <v>0.1034791422657477</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.04590495449949827</v>
+        <v>0.08232726740966001</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.1954230435892086</v>
+        <v>-0.2534632051376136</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.1974917624866706</v>
+        <v>-0.1854558687815313</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.1499737009100528</v>
+        <v>-0.0577505734331325</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.4435183191555936</v>
+        <v>-0.3854637075675882</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.01597057763297727</v>
+        <v>0.02199996939135218</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.4119493728425923</v>
+        <v>0.4119890713883976</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.1838815173946244</v>
+        <v>0.2212077568493029</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.09936019350246283</v>
+        <v>0.1012119610284046</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.02819041430353053</v>
+        <v>-0.05141284412927405</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.05442312504704461</v>
+        <v>-0.0786174317847852</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-0.09924588396781786</v>
+        <v>-0.1612049460971221</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-0.2371701275401534</v>
+        <v>-0.3093916261855156</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.4553064474848938</v>
+        <v>-0.4574842906383481</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.26017883420716</v>
+        <v>-0.2987325882733955</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.337725137339504</v>
+        <v>-0.4095484938297247</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.3396976581614837</v>
+        <v>-0.4311083802840656</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-0.2678507586483008</v>
+        <v>-0.3277634401057909</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-0.4628508126643496</v>
+        <v>-0.4871962974664044</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-0.4329164996274812</v>
+        <v>-0.5049896957453015</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-0.5580928060763028</v>
+        <v>-0.6298151158065863</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 1.471</t>
+          <t>X &lt; 1.486</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2953</v>
+        <v>2974</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.4103259817938678</v>
+        <v>-0.3320235840202059</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.3573278863998368</v>
+        <v>-0.2812073286991961</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.02054149131813432</v>
+        <v>0.07130687196314511</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.09983556495183876</v>
+        <v>0.1610284378046885</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.2128028201858356</v>
+        <v>-0.1078724026355644</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.3435912874814377</v>
+        <v>-0.3035243112018975</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.08646169840900342</v>
+        <v>-0.1052488398563867</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.3457893377565142</v>
+        <v>-0.3978705519753447</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.0682651810278827</v>
+        <v>-0.2034112539430026</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.2902038046280566</v>
+        <v>0.2149258104623968</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.04446011620954238</v>
+        <v>-0.02750636121154315</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.05490206722065949</v>
+        <v>0.01470785594571566</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.1721602948530432</v>
+        <v>-0.20362847364499</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.2384743157648046</v>
+        <v>-0.2373184016356618</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.1341498979294258</v>
+        <v>-0.2049289620624961</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-0.3161168753350694</v>
+        <v>-0.362014983786203</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.4301960466813668</v>
+        <v>-0.442540281171091</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.278505024813235</v>
+        <v>-0.2925434308380233</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-0.3804408196312536</v>
+        <v>-0.3924962704040738</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-0.4101826792963479</v>
+        <v>-0.4407075457281948</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.2904508320098032</v>
+        <v>-0.3252540462189515</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-0.4477776718172706</v>
+        <v>-0.4819054479031308</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-0.5115265405416451</v>
+        <v>-0.4899711709501275</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.5674178108098999</v>
+        <v>-0.545911136390778</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 1.544</t>
+          <t>X &lt; 1.561</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3050</v>
+        <v>3073</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.156206096304544</v>
+        <v>-0.1630082263404091</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.2458560601800741</v>
+        <v>-0.2215786043384185</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.02377744313228902</v>
+        <v>0.008823856927598683</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.002425639004272284</v>
+        <v>0.07282030689243157</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.186358493784212</v>
+        <v>-0.1334784207535833</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.3069754522096133</v>
+        <v>-0.3168720439074804</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.1480197505222094</v>
+        <v>-0.1820849765024946</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.3753453678909011</v>
+        <v>-0.409481622106199</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.2685551514322384</v>
+        <v>-0.2199334875754175</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.0536206181544614</v>
+        <v>0.09534019156665607</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.01226235620271154</v>
+        <v>0.03157634153696165</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.02156043890771997</v>
+        <v>0.03106713484174151</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.2669337432826069</v>
+        <v>-0.2163245784626326</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.3709362136485836</v>
+        <v>-0.3209308601204057</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-0.3238163465886785</v>
+        <v>-0.3107570497055221</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.4481807573989514</v>
+        <v>-0.4112554112554108</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.5302329372885026</v>
+        <v>-0.4610353473369955</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.4195282150967543</v>
+        <v>-0.3842182932766462</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.5113072980754225</v>
+        <v>-0.4415397051644092</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-0.5013916175507518</v>
+        <v>-0.4821882078385613</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-0.4357241561319185</v>
+        <v>-0.3879256861388711</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-0.5577203401320361</v>
+        <v>-0.5419959278401834</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-0.5256733168408374</v>
+        <v>-0.4759200072185337</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-0.5822068833285385</v>
+        <v>-0.5324962516460872</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 1.618</t>
+          <t>X &lt; 1.635</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3124</v>
+        <v>3140</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.08225872297902015</v>
+        <v>-0.09654331596361487</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.1460218806494922</v>
+        <v>-0.1611256528390825</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.09949228165546486</v>
+        <v>0.1278389897888701</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.1031126102136284</v>
+        <v>0.04819719327203842</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.1488049943115755</v>
+        <v>-0.1609308346900562</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.2619652522505547</v>
+        <v>-0.3679141396860928</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.06186770056773838</v>
+        <v>-0.189593580624269</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.3222529529967488</v>
+        <v>-0.4181035753234781</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.1988413595592533</v>
+        <v>-0.2951877158113163</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.1927636245797615</v>
+        <v>0.09137311623641864</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.1350595826793466</v>
+        <v>0.03500091031895636</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.1933334522620243</v>
+        <v>0.1235795370605715</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.01248583954254912</v>
+        <v>-0.06077412637193191</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.03041967995147843</v>
+        <v>-0.1043532924721049</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.09584795091378595</v>
+        <v>-0.1720546760159536</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.1840451484357644</v>
+        <v>-0.2257325478418224</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.2033655929200862</v>
+        <v>-0.245495263331577</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.1615535400218988</v>
+        <v>-0.2043225790906646</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.2459683721624657</v>
+        <v>-0.2556794868050005</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.2317774936061312</v>
+        <v>-0.2726387391961538</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.2124121135070709</v>
+        <v>-0.2237012676838432</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.3332469553635278</v>
+        <v>-0.3442243256811395</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.2633802981584381</v>
+        <v>-0.3054771250031934</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.2562691406279285</v>
+        <v>-0.2987156973629368</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 1.691</t>
+          <t>X &lt; 1.709</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3189</v>
+        <v>3204</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.07711112857857927</v>
+        <v>-0.04283222509450013</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.2086738674356141</v>
+        <v>-0.1437902164668543</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.02843663681770892</v>
+        <v>0.04880272509660699</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.1017124801611686</v>
+        <v>-0.04341883003824876</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.262474447785749</v>
+        <v>-0.2240261865085671</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.4631284858438462</v>
+        <v>-0.4232014591922137</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.3140115338729714</v>
+        <v>-0.2948086342343785</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.5124414522564678</v>
+        <v>-0.5243391593239934</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.4531726171979358</v>
+        <v>-0.4341408117565848</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.1165186030641365</v>
+        <v>-0.1017581803345067</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.1363479313922937</v>
+        <v>-0.1516167067429564</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.05376925480017292</v>
+        <v>-0.07040611841838995</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.2851118478577703</v>
+        <v>-0.2424044858865244</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.3004765519837207</v>
+        <v>-0.2584608180793211</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.3780523369538216</v>
+        <v>-0.3379712243508308</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.4524461198125778</v>
+        <v>-0.4099211290992102</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.4428956826321837</v>
+        <v>-0.4320164735383472</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.3728461447807234</v>
+        <v>-0.3315077699971809</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.4199022802791674</v>
+        <v>-0.3775743363958597</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.3709285937989364</v>
+        <v>-0.390505649528464</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.3317342435844211</v>
+        <v>-0.353408782892032</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.4203541484387472</v>
+        <v>-0.4106973971381009</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.377687508189787</v>
+        <v>-0.3984649896944745</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.3095894329741</v>
+        <v>-0.3309604233026491</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 1.765</t>
+          <t>X &lt; 1.784</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3232</v>
+        <v>3244</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.07854672843057386</v>
+        <v>-0.04207222828648582</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.08983795943601081</v>
+        <v>0.007219225473114932</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.007504306265744276</v>
+        <v>0.1180763159264302</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.1049801195686371</v>
+        <v>0.03526690693025358</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.1761687570755797</v>
+        <v>-0.08593129093890184</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.4024343312301397</v>
+        <v>-0.3109931771623238</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.2962796994988608</v>
+        <v>-0.2243095396788632</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.4957649231263304</v>
+        <v>-0.3930660579255161</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.4059283925280539</v>
+        <v>-0.3034252965884718</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.1763920004047748</v>
+        <v>-0.1073475199187541</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.253974722814057</v>
+        <v>-0.1839327465411174</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.1145740818983683</v>
+        <v>-0.04572913478617835</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.3886136209074209</v>
+        <v>-0.2908525010229539</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.283361780422041</v>
+        <v>-0.2479811595172947</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.3686454240016275</v>
+        <v>-0.3038625574868732</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.4650157742339687</v>
+        <v>-0.39835625628983</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.4882499209688547</v>
+        <v>-0.4218238882801018</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.4205387930179683</v>
+        <v>-0.3546086566494679</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.4641136133529002</v>
+        <v>-0.4282359441911794</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.4751236093943092</v>
+        <v>-0.4387225457116486</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.3818789252267081</v>
+        <v>-0.3471858694910779</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.5012674003239255</v>
+        <v>-0.4663155407220856</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.4555386650003825</v>
+        <v>-0.4200510611496568</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.4203216374269019</v>
+        <v>-0.3543205572905208</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 1.838</t>
+          <t>X &lt; 1.858</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3262</v>
+        <v>3275</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.0104096539325198</v>
+        <v>-0.06075002605332713</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.03427407543625094</v>
+        <v>-0.07577565685006959</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.01856277391045325</v>
+        <v>0.02047968642462905</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.02246219690206175</v>
+        <v>0.02281085454557541</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.1428120828203774</v>
+        <v>-0.1611423875127826</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.1823592843258197</v>
+        <v>-0.2000871233275205</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.1146769148289621</v>
+        <v>-0.1822423685787555</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.284323968801786</v>
+        <v>-0.32163122822638</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.2253809911522211</v>
+        <v>-0.2628176176894428</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.06602793440299592</v>
+        <v>-0.1062649822039745</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.0792843594835162</v>
+        <v>-0.118716670666366</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.02579125211990885</v>
+        <v>-0.01484841863013031</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.1643415301064692</v>
+        <v>-0.1465172258294913</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.123140419283331</v>
+        <v>-0.1669756016697477</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.1830646029126086</v>
+        <v>-0.1980668392648042</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.3036158421918387</v>
+        <v>-0.2860235003092129</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.3584083818573944</v>
+        <v>-0.3409693778505556</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.2922428459451467</v>
+        <v>-0.2753551457592565</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.3027845363611803</v>
+        <v>-0.2852463564005703</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.3425443968156827</v>
+        <v>-0.324320852296168</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.2551069939902888</v>
+        <v>-0.2692521951348823</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.4046946803268341</v>
+        <v>-0.4184643415936051</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.3261838531691623</v>
+        <v>-0.33950072636204</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.2612934338708044</v>
+        <v>-0.275085610330315</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 1.912</t>
+          <t>X &lt; 1.932</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3284</v>
+        <v>3293</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.07460537429284386</v>
+        <v>-0.1103703481935909</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.1212485088973878</v>
+        <v>-0.09696408684969526</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.07834685498050931</v>
+        <v>-0.09963329897702522</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.0792555887155828</v>
+        <v>-0.07102464561341293</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.2156172492743025</v>
+        <v>-0.1953986276744288</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.2536760029442462</v>
+        <v>-0.2935481549229308</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.2219110474894208</v>
+        <v>-0.2799983493872986</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.3923166472642734</v>
+        <v>-0.4503925165334834</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.3335226192225349</v>
+        <v>-0.3917121094438087</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.1804273817314908</v>
+        <v>-0.2704964331658104</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.1917993221953864</v>
+        <v>-0.2814378456148106</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.08932208568131017</v>
+        <v>-0.1797026764753014</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.2250302848835659</v>
+        <v>-0.256290289041381</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.246317626712397</v>
+        <v>-0.2778751989640398</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.2799136391987815</v>
+        <v>-0.3427029104164561</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.33495862109055</v>
+        <v>-0.3663949400089948</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.3902908046872895</v>
+        <v>-0.3914928945532239</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.3556745573364353</v>
+        <v>-0.3571362291073257</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.3951237591351813</v>
+        <v>-0.4264627625003428</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.4029805352798093</v>
+        <v>-0.4340160727424944</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.3502052766584285</v>
+        <v>-0.3519045642683238</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.4688967914817113</v>
+        <v>-0.5007410084624695</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.3890911048555452</v>
+        <v>-0.4207340043166212</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.3556139638580831</v>
+        <v>-0.3874776146512957</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 1.985</t>
+          <t>X &lt; 2.007</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3304</v>
+        <v>3311</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.06618394333347766</v>
+        <v>-0.0994305468053156</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.1747104542297109</v>
+        <v>-0.2079865656394873</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.1708018957594533</v>
+        <v>-0.1583877055575229</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.05569081801135667</v>
+        <v>-0.04368920014137245</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.1332365284402641</v>
+        <v>-0.1692063173266618</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.2903239250799956</v>
+        <v>-0.3259020359361813</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.2634157205051153</v>
+        <v>-0.3166007198265319</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.3742443581076387</v>
+        <v>-0.4274749931847168</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.31554900043988</v>
+        <v>-0.3688807438009363</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.1981742690809867</v>
+        <v>-0.2524986112751293</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.2078287307193634</v>
+        <v>-0.2618912822064061</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.1076577222536201</v>
+        <v>-0.1622112366730377</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.2191710484610851</v>
+        <v>-0.2444643666194324</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.2718390572023281</v>
+        <v>-0.2972383959263141</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.3092178122065121</v>
+        <v>-0.3351682289893532</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.3301526502404073</v>
+        <v>-0.3555059483049874</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.3859591389534955</v>
+        <v>-0.4113295979342411</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.3521850854404676</v>
+        <v>-0.3777342798956767</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.3900885221239108</v>
+        <v>-0.4153619820441605</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.4269951632406261</v>
+        <v>-0.4520222953197077</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.3173537201561061</v>
+        <v>-0.3431340350044252</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.4660247931342099</v>
+        <v>-0.4915712642213919</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.4152955780374015</v>
+        <v>-0.4406978384287115</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.3824887076448249</v>
+        <v>-0.4080405304323946</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 2.059</t>
+          <t>X &lt; 2.081</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3314</v>
+        <v>3327</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.07699910359252016</v>
+        <v>-0.08648630100663723</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.2161934721192651</v>
+        <v>-0.1961198783189815</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.2166135763853063</v>
+        <v>-0.2432903009203642</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.1040024553228847</v>
+        <v>-0.1624714197173986</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.1824259192421138</v>
+        <v>-0.2292035963005432</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.2784708997036773</v>
+        <v>-0.2945600226862624</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.2839811551530929</v>
+        <v>-0.3488053572943244</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.3652896202372418</v>
+        <v>-0.430576908361104</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.3066431776156122</v>
+        <v>-0.3720654881199508</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.221991762241835</v>
+        <v>-0.2898743013233656</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.2307997195837359</v>
+        <v>-0.2979203071889387</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.1317759210122347</v>
+        <v>-0.2000644306309098</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.2162678628953572</v>
+        <v>-0.2573602197098737</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.2694424856069304</v>
+        <v>-0.3109450891148455</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.3086909752691795</v>
+        <v>-0.3518536758126274</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.3277713654663899</v>
+        <v>-0.3692471945845313</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.38381287097247</v>
+        <v>-0.4254497395478722</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.3504561151787513</v>
+        <v>-0.3925232173363042</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.3875936600374175</v>
+        <v>-0.4289379793912289</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.4238245931283871</v>
+        <v>-0.4345077727104467</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.346298087623218</v>
+        <v>-0.3587742980798154</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.4947586009493747</v>
+        <v>-0.4768282830727273</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.4131962860920666</v>
+        <v>-0.3948273441886627</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.4410669602995654</v>
+        <v>-0.4227922070625709</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 2.133</t>
+          <t>X &lt; 2.155</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3328</v>
+        <v>3334</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.018496219239303</v>
+        <v>-0.04919286604001627</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.2182521442757235</v>
+        <v>-0.1891003578163648</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.238486784302097</v>
+        <v>-0.1795242611408412</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.1890750465394149</v>
+        <v>-0.130176932522815</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.2388462610074029</v>
+        <v>-0.2273039205832248</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.3038366945571909</v>
+        <v>-0.2622908578722161</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.3125661870969765</v>
+        <v>-0.288193585331662</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.394708991761874</v>
+        <v>-0.3703575147518166</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.3660563405425634</v>
+        <v>-0.3417233564618982</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.2850189972001687</v>
+        <v>-0.2613109647394367</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.2926592460992623</v>
+        <v>-0.2687584337443099</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.1952388928436761</v>
+        <v>-0.2015681504578311</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.2541613387232999</v>
+        <v>-0.2311995352510792</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.278094632529033</v>
+        <v>-0.2851271969302118</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.3199455227421311</v>
+        <v>-0.3273205054598805</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.3664279778044488</v>
+        <v>-0.3733474783744057</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.4228087298632701</v>
+        <v>-0.4297140767432808</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.3900445830273469</v>
+        <v>-0.3970775649866454</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.3961272039612709</v>
+        <v>-0.4030156607782516</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.4314225690276032</v>
+        <v>-0.4081741804181291</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.38652823847859</v>
+        <v>-0.3636968112432655</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.5046659751510774</v>
+        <v>-0.4816637058129416</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.4222940860827364</v>
+        <v>-0.399260223902651</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.450369714349975</v>
+        <v>-0.4273269177940122</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/nasdaq_hourly_24hrs/volume/volume_ratio_24.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/volume/volume_ratio_24.xlsx
@@ -618,1805 +618,1805 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ 0.5574</t>
+          <t>X ≈ 0.5588</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>12.93337199674036</v>
+        <v>0.9952263181003929</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>29.15775559645451</v>
+        <v>9.781091401175445</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>11.18066230422256</v>
+        <v>8.53927069371494</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>10.47491063042425</v>
+        <v>7.953053769154856</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-6.427565358763232</v>
+        <v>-1.358794212209467</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-6.242900911625284</v>
+        <v>-10.24441277280515</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-23.59343896310069</v>
+        <v>-11.03791217121754</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-7.290809153533317</v>
+        <v>-2.297263321035182</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-7.252756098363719</v>
+        <v>-2.171102983773643</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-8.023848504061945</v>
+        <v>6.090351032305769</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-7.753608995003262</v>
+        <v>15.42089408247217</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-8.033797015732979</v>
+        <v>15.15072248833445</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>7.458267737702108</v>
+        <v>23.10658092779493</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>7.237604223813733</v>
+        <v>22.85885856958645</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>6.583740207447939</v>
+        <v>22.18618555112123</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>7.179473784518024</v>
+        <v>22.75406154964922</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>7.048647056399503</v>
+        <v>22.65817903360612</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-9.691823991199222</v>
+        <v>13.45763891800401</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-9.479272872998266</v>
+        <v>4.597997975773588</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-9.29631637409296</v>
+        <v>4.813258572295823</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-9.838480236332472</v>
+        <v>13.32800446829772</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-9.917478602985206</v>
+        <v>13.25736655287457</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-9.646357807394686</v>
+        <v>13.50541224375733</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-9.725467289719624</v>
+        <v>4.256833337724288</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ 0.6317</t>
+          <t>X ≈ 0.6333</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-11.45302187168954</v>
+        <v>-7.65492457753826</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-1.336349201343197</v>
+        <v>4.513257824499505</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>7.694010985453936</v>
+        <v>7.409595999777899</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>12.21796669981947</v>
+        <v>6.823068993691926</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>17.11952536325725</v>
+        <v>10.69250699445853</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>12.07780216951566</v>
+        <v>6.7090295719305</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>11.31555736789682</v>
+        <v>5.921311558224716</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>5.804447653595837</v>
+        <v>1.47272140412344</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>5.84694684808651</v>
+        <v>1.600142994679565</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-10.64434779946189</v>
+        <v>-11.64027055929725</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-5.131679102739533</v>
+        <v>-7.221956656266862</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>5.079321333327222</v>
+        <v>4.957678188775063</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-1.286845201800396</v>
+        <v>-0.3071114764635823</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-1.507505161942944</v>
+        <v>-0.5548277346727488</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-2.164326428336999</v>
+        <v>-1.235365093372351</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-1.57157723492039</v>
+        <v>-0.6753935022561492</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-17.46239390237149</v>
+        <v>-13.25359771236852</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-12.31875123698371</v>
+        <v>-9.231141128283035</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-12.10712930418224</v>
+        <v>-4.858839501546704</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-11.92510733519119</v>
+        <v>-4.646798441600005</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-7.209524796529223</v>
+        <v>-9.376158141747261</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-7.287648327754589</v>
+        <v>-5.29067194246533</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-12.27700555720472</v>
+        <v>-9.214151859384998</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-17.62020413182609</v>
+        <v>-9.37953029863634</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ 0.7061</t>
+          <t>X ≈ 0.7078</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-5.599232564223378</v>
+        <v>-9.721821857479576</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>2.008888565336406</v>
+        <v>-1.694407239329898</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>4.555732274098013</v>
+        <v>1.199400452475842</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>11.79771282204568</v>
+        <v>13.03320924836734</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>11.4664165858777</v>
+        <v>12.76204522187503</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>9.668578863265893</v>
+        <v>10.85175488426453</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>12.88488178387323</v>
+        <v>12.13818669774716</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>10.62232204913236</v>
+        <v>11.83882087454812</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>12.65748038940346</v>
+        <v>14.0437826584515</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>7.910526342413348</v>
+        <v>9.107802254976392</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>12.17073851566555</v>
+        <v>13.53278250844946</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>15.88328342155209</v>
+        <v>17.41402195095243</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>14.76802761106098</v>
+        <v>16.30764539293224</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>12.55364512488394</v>
+        <v>13.98310109288455</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>17.88503436717404</v>
+        <v>21.61788102589572</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>10.50424222174891</v>
+        <v>13.87261722014748</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>4.387418790256405</v>
+        <v>7.537098173723201</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>6.280857905364627</v>
+        <v>9.486759528560725</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>4.501654940089914</v>
+        <v>7.624004734008807</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>2.691449393109636</v>
+        <v>5.759148816107725</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>2.149262194643363</v>
+        <v>7.273401921542671</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>6.071558082153921</v>
+        <v>9.282629738777054</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>0.3502643128213805</v>
+        <v>3.281588848961171</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>0.2745327102812851</v>
+        <v>3.120469701362715</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ 0.7803</t>
+          <t>X ≈ 0.7824</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.00285679536521144</v>
+        <v>1.942984733729183</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.3326075169243552</v>
+        <v>-0.1299840358800637</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-1.759906642935874</v>
+        <v>0.4443909149723382</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1.476500699710243</v>
+        <v>2.290896222549975</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.174499036180606</v>
+        <v>2.016240548325847</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1.987887936562949</v>
+        <v>3.394301099682863</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-1.411925049939441</v>
+        <v>0.7685373607420942</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-1.029996275163789</v>
+        <v>0.4635206692926559</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>2.305421894404276</v>
+        <v>4.25687104392356</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>7.47297028483834</v>
+        <v>9.570190407035128</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>9.067311023211154</v>
+        <v>10.45798748555376</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>7.473130634665395</v>
+        <v>9.573088708783544</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>5.69530683985662</v>
+        <v>7.847283514796977</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>6.134864987457902</v>
+        <v>8.210083948376514</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>1.518944788563587</v>
+        <v>3.857595635469778</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>1.452825842041719</v>
+        <v>3.809315708374868</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>3.963850231993234</v>
+        <v>6.154617944628605</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>1.21655497639226</v>
+        <v>3.572792775900972</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>1.43290493213604</v>
+        <v>3.175203557906329</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.2965376713848542</v>
+        <v>1.55506146628818</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>2.400456591935651</v>
+        <v>3.437178399682061</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>1.002127839025036</v>
+        <v>1.523329462810231</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.04694767568885538</v>
+        <v>1.153689131916536</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.12281828309726</v>
+        <v>1.970162952896459</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ 0.8547</t>
+          <t>X ≈ 0.8569</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2.050558784696264</v>
+        <v>1.285587430875445</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.6830513365523032</v>
+        <v>-0.1227737831757878</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2.376422002693864</v>
+        <v>2.998870149281487</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-3.13965322380168</v>
+        <v>-1.958156340336828</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-4.377980016947177</v>
+        <v>-3.399683425168661</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-7.196944804266138</v>
+        <v>-5.866753953762981</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-6.47354943387257</v>
+        <v>-5.4911783134377</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-5.378817151194291</v>
+        <v>-4.046694772301379</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-2.632331558813661</v>
+        <v>-1.880431243600867</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.3755136796280709</v>
+        <v>0.2461052293852859</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>2.324369791887868</v>
+        <v>2.561012640959333</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.8447569124826444</v>
+        <v>0.533874926076443</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.628379647283829</v>
+        <v>0.5916502268606436</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-1.097031318769943</v>
+        <v>-1.409591472725026</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>1.860636907133944</v>
+        <v>1.419022275207617</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>1.551636181419397</v>
+        <v>1.103044820782159</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>2.022243881349652</v>
+        <v>1.585619434469265</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>2.823359062568379</v>
+        <v>2.039511128712036</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>2.437259182792133</v>
+        <v>1.962089841853214</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>1.115737516477125</v>
+        <v>0.7118143536935406</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>0.5734694455857365</v>
+        <v>0.4376878050218096</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>2.007480610695062</v>
+        <v>1.82848729028656</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>1.075015395589872</v>
+        <v>0.8999107484381028</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>3.4165266679843</v>
+        <v>3.083812809867112</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ 0.9289</t>
+          <t>X ≈ 0.9315</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-4.226572237183106</v>
+        <v>-3.911955402608449</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.401496300353827</v>
+        <v>-1.005932046904491</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.08515553500557616</v>
+        <v>0.05373169186614746</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1.080185030405559</v>
+        <v>0.5669981851772334</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.2278096350217496</v>
+        <v>-0.4362160581546988</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.4475464788797012</v>
+        <v>0.4498899973282136</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.8981063827061249</v>
+        <v>0.8713464800785786</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.329498749768952</v>
+        <v>-1.864781122023544</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.4157419459734371</v>
+        <v>-0.03537308227357272</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.839108880434871</v>
+        <v>1.115573172008823</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.5713825393727561</v>
+        <v>-1.638901049989926</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.580761347571894</v>
+        <v>-2.401932632847881</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.726528058144027</v>
+        <v>-2.542182564301676</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.214680715623658</v>
+        <v>-1.815378230987335</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-2.361022408200327</v>
+        <v>-2.497883244058229</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-1.034302726520963</v>
+        <v>-0.9618777418782685</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.1904361908450483</v>
+        <v>-0.09007640621560853</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.3386822274012431</v>
+        <v>0.9975614198682194</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.3105671958795284</v>
+        <v>0.7238720450550531</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.4970751248075018</v>
+        <v>0.9395842241878185</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>0.9338147660758551</v>
+        <v>1.348904850331998</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>0.1241463010792145</v>
+        <v>0.4407622482284523</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-0.5807526914115755</v>
+        <v>0.195811629637511</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-1.392133956386232</v>
+        <v>-1.188821252182571</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ 1.003</t>
+          <t>X ≈ 1.006</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.846631652528572</v>
+        <v>-0.4871506690330349</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.9581225305094279</v>
+        <v>0.8779464360170053</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.1648100614963184</v>
+        <v>-0.3815777219203511</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>3.312440930127096</v>
+        <v>3.073090616468399</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.262716752249268</v>
+        <v>1.516502454007743</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.66524974533597</v>
+        <v>1.88584522551843</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>4.330383223259737</v>
+        <v>4.28780383854491</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2.332705166512703</v>
+        <v>2.177197937074887</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.087823417484479</v>
+        <v>1.246768545144725</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.5294311021688003</v>
+        <v>0.9974224483744365</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.345629848388157</v>
+        <v>-0.2259081955430702</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.7659893053637816</v>
+        <v>0.3493210350149738</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.04552254695447289</v>
+        <v>0.7281449203091626</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.8223224669602587</v>
+        <v>0.04925180214370783</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.2785416225101827</v>
+        <v>0.346864194371058</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.1014490242686534</v>
+        <v>0.6964061777744135</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.8297077477124901</v>
+        <v>1.146483941918433</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.7246316269295292</v>
+        <v>0.9249834138518196</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>0.5094337226010381</v>
+        <v>1.139891289091516</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>1.129957267387539</v>
+        <v>1.570923841676908</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>0.5870411619464093</v>
+        <v>1.002933859170881</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-1.088356367812672</v>
+        <v>-0.1454082286250298</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-1.031224205411462</v>
+        <v>-0.4191080425452682</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.7621843523546659</v>
+        <v>-1.010431586190862</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ 1.078</t>
+          <t>X ≈ 1.081</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>389</v>
+        <v>375</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>4.671557178839812</v>
+        <v>4.014386902707535</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.7558127551425073</v>
+        <v>-1.267675203961787</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-1.421165535509139</v>
+        <v>-1.991514388244781</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-2.136977467860675</v>
+        <v>-2.053998334495333</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.188452537097149</v>
+        <v>-1.387376249170309</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-1.254516807782963</v>
+        <v>-1.49552546080276</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-2.023824642001109</v>
+        <v>-2.025367390175816</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.2597781350638968</v>
+        <v>0.5925341528063655</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-2.262873100511804</v>
+        <v>-1.257536600086816</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-3.034152474963854</v>
+        <v>-2.052412074373009</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-2.759274682009739</v>
+        <v>-1.514396328871641</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.2227907305734504</v>
+        <v>1.13420496609983</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-4.158655900329599</v>
+        <v>-2.371003698338555</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-4.377096857566883</v>
+        <v>-2.883602647018513</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-3.497914186046657</v>
+        <v>-2.23508503954892</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-1.882583267139076</v>
+        <v>-0.6109590722362483</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.7353698078444566</v>
+        <v>0.6160095348565804</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-2.121774099628311</v>
+        <v>-0.8476054384642282</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-0.6232091850628336</v>
+        <v>0.4330345987005373</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-2.2350889935841</v>
+        <v>-0.6850854329569103</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-3.29119777449327</v>
+        <v>-1.519196601004246</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-1.311731551453043</v>
+        <v>-0.2610257896262027</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>0.7616760174882273</v>
+        <v>1.849275362318885</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.8565726881772022</v>
+        <v>0.6204697013626799</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ 1.152</t>
+          <t>X ≈ 1.155</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.226829215721551</v>
+        <v>-0.03407424054068287</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-3.541225489394229</v>
+        <v>-2.053801395829261</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.9907730287836003</v>
+        <v>1.549379983063396</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-2.591918358940291</v>
+        <v>-0.3673287919353996</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-1.155853050032206</v>
+        <v>-1.534878551535066</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.3635326600377766</v>
+        <v>0.3878125694338195</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.9244691438409234</v>
+        <v>0.916864558482466</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>2.869049773256883</v>
+        <v>2.819427975914074</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>3.369357078041602</v>
+        <v>2.518614464626076</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>3.486148345756412</v>
+        <v>3.049015493787202</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>2.419293907866525</v>
+        <v>1.103955608169827</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.17514849747198</v>
+        <v>-1.583335155747697</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.5203935313652366</v>
+        <v>-0.4925760619904196</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>1.488731206062567</v>
+        <v>1.472058163192578</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.383650524509072</v>
+        <v>0.3459526159357225</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.799681183459569</v>
+        <v>0.7288943118707607</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-1.30683435023267</v>
+        <v>-1.592969273435308</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.0687892868163047</v>
+        <v>-0.8400191433441719</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>2.832351904604181</v>
+        <v>2.741163218045429</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>1.67852257893145</v>
+        <v>1.181581233709878</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>1.5843046525655</v>
+        <v>1.503025621217979</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>0.1648619216797655</v>
+        <v>-0.3499146785150842</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>2.682203528526074</v>
+        <v>2.115942028985508</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>1.261079795482168</v>
+        <v>0.6204697013627154</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ 1.226</t>
+          <t>X ≈ 1.229</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>160</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.511299542252551</v>
+        <v>-2.901955636665029</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.861613323235844</v>
+        <v>0.5873287922612889</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>4.477085748776332</v>
+        <v>3.063068128375285</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.188449415632519</v>
+        <v>-1.259767508438514</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.3321033006752572</v>
+        <v>0.9577755028562294</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>2.383008324449854</v>
+        <v>2.984337911450076</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-2.747297318209746</v>
+        <v>-2.169095735738679</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.785221102846492</v>
+        <v>-1.849206681236218</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-4.224908919492748</v>
+        <v>-4.218722802361086</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-3.130057021969002</v>
+        <v>-3.144529379130262</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.86140952698748</v>
+        <v>-2.870800230496172</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.902196744302543</v>
+        <v>-3.145589224131591</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.172767202271963</v>
+        <v>-2.388894353445821</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.1504786881031492</v>
+        <v>-1.388066418985858</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-5.80309136942364</v>
+        <v>-7.063323381449415</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-7.068814398985431</v>
+        <v>-8.375986809206616</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-9.075194323513593</v>
+        <v>-10.97664318286332</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-5.44005058665168</v>
+        <v>-6.739682566085932</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-8.597611542637026</v>
+        <v>-10.27090851566989</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-9.045706496132844</v>
+        <v>-10.06841876629021</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-7.715338314821864</v>
+        <v>-8.760863267670914</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-9.044660360769214</v>
+        <v>-10.7110257896262</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-7.774635036496392</v>
+        <v>-9.217391304347821</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-7.225467289719589</v>
+        <v>-8.129530298637292</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ 1.3</t>
+          <t>X ≈ 1.304</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>134</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.782524029763508</v>
+        <v>-1.291179048476032</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.09981252688532294</v>
+        <v>1.431058586486408</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.8772646969595783</v>
+        <v>2.396082920443092</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.648912489715421</v>
+        <v>2.549462652803946</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>3.54107243836269</v>
+        <v>4.504199363148338</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>4.477601675263955</v>
+        <v>3.183043676312266</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>6.682603264261445</v>
+        <v>5.373851063610864</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.939882283172025</v>
+        <v>1.35163479333584</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>4.638204914421379</v>
+        <v>3.70657192690269</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>6.840066143263755</v>
+        <v>5.884889083529735</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>8.603967185862565</v>
+        <v>7.646968375823491</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>10.55931089725246</v>
+        <v>10.34830167555357</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>6.47642132801186</v>
+        <v>6.273506005104842</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>5.510754628983335</v>
+        <v>6.770978145104571</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>7.834764945621764</v>
+        <v>9.070981586579315</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>4.702410430763678</v>
+        <v>5.160493998831214</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>1.589023672901867</v>
+        <v>3.567202131355472</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>4.46387625607629</v>
+        <v>5.668991028462926</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>2.444662172587151</v>
+        <v>4.393597144943541</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>2.634580887859464</v>
+        <v>3.868148397888973</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>3.584572033326261</v>
+        <v>4.046972553224613</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>2.762457415200664</v>
+        <v>3.971810031269285</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>5.275738097832047</v>
+        <v>5.707981829980532</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>2.961099874459443</v>
+        <v>3.307036865541825</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ 1.375</t>
+          <t>X ≈ 1.378</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>4.597330791319983</v>
+        <v>1.21797201989704</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>4.263630581987854</v>
+        <v>3.333664813760038</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.559400358437799</v>
+        <v>2.068997514835473</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.121317903963849</v>
+        <v>2.663005054141863</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-8.409476529282031</v>
+        <v>-7.058951604225427</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-6.248794296543217</v>
+        <v>-3.36110403502181</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.9154974899945</v>
+        <v>4.14539899637213</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.9114784465924828</v>
+        <v>2.660196024122271</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-2.155312104453962</v>
+        <v>0.4080992493663018</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.3769630386316933</v>
+        <v>1.980145957671049</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.378223236146006</v>
+        <v>1.06833187051334</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-4.209487506465202</v>
+        <v>-2.7647917243184</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.067298289592927</v>
+        <v>2.066198481083703</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>2.12677888587406</v>
+        <v>0.6303944729259001</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.190585250384693</v>
+        <v>-1.238384857715467</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-3.054510752889144</v>
+        <v>-3.053795728958775</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.6269953025585977</v>
+        <v>-1.967901198699927</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-3.292954951835526</v>
+        <v>-2.102360300475233</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-1.796504098183327</v>
+        <v>-0.6987531299911254</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.3313586452442294</v>
+        <v>-0.4850854329567724</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-3.438007377312815</v>
+        <v>-3.433482315289957</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>0.3323005074319312</v>
+        <v>0.062783734183391</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-4.521429908291296</v>
+        <v>-4.455486542442991</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-2.033159597412002</v>
+        <v>-2.236673155780146</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ 1.449</t>
+          <t>X ≈ 1.453</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.091420011274138</v>
+        <v>0.4626571934159358</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.5662638928179078</v>
+        <v>-1.769825625436425</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.8848332060143491</v>
+        <v>-3.038800596318943</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>2.414600132933067</v>
+        <v>0.3365938452984665</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>4.111221321447836</v>
+        <v>2.06367766596243</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-3.730199408167522</v>
+        <v>-2.74114515491808</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.492108713516359</v>
+        <v>-1.550416635534923</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.7552157340740777</v>
+        <v>-0.8510521876861645</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-6.756675504197268</v>
+        <v>-6.704723450838124</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-5.524988039266965</v>
+        <v>-5.517410406233111</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-7.258180404357006</v>
+        <v>-7.232140680408776</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-2.505555458248878</v>
+        <v>-1.532523585477847</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-4.632071763414778</v>
+        <v>-4.635028041066654</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-4.852263942101139</v>
+        <v>-3.884270107779166</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-1.476783302353191</v>
+        <v>-1.570804566417358</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-1.889693992542057</v>
+        <v>-1.00904852729289</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.005912463095071985</v>
+        <v>0.8841510098133725</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.1125265624366278</v>
+        <v>-0.2486291306781538</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.1042515162478637</v>
+        <v>-0.03326286292285374</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.7198590337447399</v>
+        <v>-0.8184187662902076</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.2523041916097668</v>
+        <v>0.6141367323291149</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.3281501530188109</v>
+        <v>1.538974210373802</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.05367544053669349</v>
+        <v>1.782608695652122</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>1.890694326442045</v>
+        <v>3.620469701362715</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 1.523</t>
+          <t>X ≈ 1.527</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>4.892560031086276</v>
+        <v>5.469946366087051</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.559077456252872</v>
+        <v>4.158867133997674</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.889664436834231</v>
+        <v>-1.342119240364845</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.601690915724618</v>
+        <v>-1.930922110905357</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.9129210328241442</v>
+        <v>0.9638416402776073</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.7154159582281991</v>
+        <v>-2.099682110267132</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.496264490399398</v>
+        <v>-2.88733600508646</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.7523902767031529</v>
+        <v>-2.162635835794752</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.7193794669011595</v>
+        <v>-2.009346812497256</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-3.51296807270149</v>
+        <v>-4.905215714898603</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.789463870559999</v>
+        <v>0.7129312493912039</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.5067352813146258</v>
+        <v>-1.709116316765979</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.5995339634641894</v>
+        <v>-1.194809986471498</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.833254094946199</v>
+        <v>-3.598665695633443</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-3.489977059032434</v>
+        <v>-3.213177280294289</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-1.887139009330305</v>
+        <v>-2.654415268134713</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-1.011894851801465</v>
+        <v>-1.688110875975489</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-3.1336378111409</v>
+        <v>-3.961364588905489</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-1.909295302457494</v>
+        <v>-3.751986375079852</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-1.729960043845693</v>
+        <v>-2.904440271666552</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-2.272506211811724</v>
+        <v>-3.471884773047286</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-2.348352173220825</v>
+        <v>-4.622316112206867</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.05367544053675743</v>
+        <v>-2.228143992519861</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-0.1295076937600328</v>
+        <v>-2.390282986809325</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 1.598</t>
+          <t>X ≈ 1.602</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2.925675311299436</v>
+        <v>2.034093165021368</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2.59634833183226</v>
+        <v>1.788186329317497</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>5.606858544763355</v>
+        <v>6.157831880104787</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.9954999800305657</v>
+        <v>-0.04354875862527763</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.379823060218065</v>
+        <v>1.062400074033789</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-2.718851586337216</v>
+        <v>-2.224492699839686</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.502819973209931</v>
+        <v>-0.2113082418341179</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.8533968634627627</v>
+        <v>0.892222018982622</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-3.742710224289034</v>
+        <v>-1.796750479784016</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.02530580478531874</v>
+        <v>0.2240994334473001</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.2903197662597776</v>
+        <v>1.904785152277029</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>4.480136622422826</v>
+        <v>5.853555310481795</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>7.108292571730722</v>
+        <v>4.738663193031059</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>9.854141971834508</v>
+        <v>5.898879835823301</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>6.201850872230686</v>
+        <v>2.399824045487499</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>8.284238520027657</v>
+        <v>5.778029472757822</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>9.63378552132535</v>
+        <v>7.082599765258173</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>8.045480679229001</v>
+        <v>6.949715660096615</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>8.256835472574515</v>
+        <v>5.755727183017044</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>9.350998798307174</v>
+        <v>5.970313628075971</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>7.31591531690831</v>
+        <v>5.402869126695236</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>8.732606668932043</v>
+        <v>8.144608013190783</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>7.51454406798122</v>
+        <v>6.979791794243688</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>10.42378644162367</v>
+        <v>11.04300491263036</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 1.672</t>
+          <t>X ≈ 1.676</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2.566539250204372</v>
+        <v>2.374394409249504</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.6870181336727654</v>
+        <v>0.4420468955795513</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-3.868898642630938</v>
+        <v>-2.514531899722158</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-4.562604250446817</v>
+        <v>-3.101142592738874</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-3.330038196884864</v>
+        <v>-3.36511772125516</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-3.131505968687001</v>
+        <v>-1.506299421846968</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-5.48486995059578</v>
+        <v>-4.00696352949236</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-5.763081395348898</v>
+        <v>-6.006799227138217</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-7.284094213434088</v>
+        <v>-5.878870317454108</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-9.619509889470578</v>
+        <v>-8.369837066910691</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-9.345450247308698</v>
+        <v>-9.792517306543644</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-9.624199650756672</v>
+        <v>-10.06909926101496</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-9.18486171761279</v>
+        <v>-6.099245615753887</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-7.843440594059359</v>
+        <v>-2.95764916871245</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-8.501583891640024</v>
+        <v>-3.639803550597485</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-9.46969696969699</v>
+        <v>-6.468330040252347</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-9.603614106674442</v>
+        <v>-6.572210451977355</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-6.583454810495667</v>
+        <v>-5.010179302901697</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-6.367563429571319</v>
+        <v>-3.100801821518658</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-6.180717619603293</v>
+        <v>-2.886215376459617</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-6.723263787569323</v>
+        <v>-3.453659877840352</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-3.674109748978402</v>
+        <v>-1.83390714555842</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-4.962135036496285</v>
+        <v>-3.285187914517259</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-1.912967289719646</v>
+        <v>-1.752411654569507</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 1.747</t>
+          <t>X ≈ 1.751</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.03171577964976535</v>
+        <v>0.1054788095485506</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>12.03970627689748</v>
+        <v>11.98113969895587</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>5.69484760522495</v>
+        <v>3.433379175834077</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>6.238293509931317</v>
+        <v>2.850410939290015</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>10.95881827536498</v>
+        <v>7.441089952128237</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>8.680786379375618</v>
+        <v>7.620036136742591</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>5.452630049404277</v>
+        <v>4.426273345249321</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>10.17441860465121</v>
+        <v>8.999401682328511</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>10.21590578656587</v>
+        <v>9.127330592012619</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.5570098894706277</v>
+        <v>-1.42481846418233</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.78295024730869</v>
+        <v>-3.591607839821897</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.938300349243271</v>
+        <v>1.009858986194601</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-4.184861717612854</v>
+        <v>-4.983081911743966</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.5940594059405981</v>
+        <v>-0.3532671926892448</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>2.435916108360075</v>
+        <v>1.403602815669572</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>0.5303030303029956</v>
+        <v>-2.913141945998568</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.396385893325558</v>
+        <v>-3.017022357723576</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-2.208454810495631</v>
+        <v>-5.588930853129114</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-4.492563429571263</v>
+        <v>-7.813493016227213</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-4.305717619603236</v>
+        <v>-7.598906571168229</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>0.1517362124307269</v>
+        <v>-3.288302292061154</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-4.924109748978395</v>
+        <v>-8.241513594504276</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-2.149635036496385</v>
+        <v>-5.558854718981962</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-2.225467289719582</v>
+        <v>-5.720993713271461</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 1.821</t>
+          <t>X ≈ 1.825</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-2.018750846440668</v>
+        <v>-0.4298524994174855</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-8.75346931652922</v>
+        <v>-9.996749282132669</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-10.22096949763564</v>
+        <v>-11.27125222867341</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.378232707583599</v>
+        <v>-2.547616691632598</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-8.047639990396519</v>
+        <v>-5.903759687870199</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>11.37664948047404</v>
+        <v>9.789807900200891</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>4.242952630049402</v>
+        <v>2.825663589151716</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>7.190547636909187</v>
+        <v>5.64574314574314</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>4.00622836721103</v>
+        <v>2.648672055427205</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.007506239561642758</v>
+        <v>-1.272379439792132</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>6.733178784949367</v>
+        <v>5.249855574812202</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>3.228622929888466</v>
+        <v>1.848273620340926</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>15.00868666948396</v>
+        <v>10.10838150289013</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>8.335994889811559</v>
+        <v>3.610147441457066</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>10.90365804384387</v>
+        <v>6.052993059572053</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>11.4980449657869</v>
+        <v>9.73929707839163</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>8.138321377196519</v>
+        <v>6.510416666666664</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>8.033480673375337</v>
+        <v>6.377532561505021</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>14.70098495752547</v>
+        <v>12.84199478865079</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>11.6620243158806</v>
+        <v>9.931581233709778</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>7.893671696301659</v>
+        <v>6.239136732329044</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>4.592019283279704</v>
+        <v>3.038974210373802</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>8.092300447374612</v>
+        <v>6.407608695652179</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>8.016468194151336</v>
+        <v>6.245469701362715</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 1.895</t>
+          <t>X ≈ 1.9</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-9.052778931613801</v>
+        <v>-13.43813044435165</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-3.975623911781781</v>
+        <v>-3.784854117203288</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-21.81989296081277</v>
+        <v>-19.92879687609678</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-17.07830152571008</v>
+        <v>-15.56792804686762</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-6.437103915997177</v>
+        <v>-5.900149664779896</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-17.25208817416758</v>
+        <v>-15.63504032841164</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-18.15848106170683</v>
+        <v>-11.54933641084817</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-23.99224806201542</v>
+        <v>-16.85425685425686</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-23.9507608801008</v>
+        <v>-16.72632794457268</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-30.27923211169284</v>
+        <v>-22.52237943979202</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-30.00517246953092</v>
+        <v>-22.25014442518768</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-30.28392187297892</v>
+        <v>-22.52672637965909</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-20.29597282872392</v>
+        <v>-8.641618497109761</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-20.51705170517047</v>
+        <v>-8.889852558542934</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-26.73075055830655</v>
+        <v>-14.57200694042806</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-15.02525252525253</v>
+        <v>-4.010702921608257</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-9.603614106674442</v>
+        <v>-4.114583333333329</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-15.26401036605118</v>
+        <v>-9.247467438494873</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-26.15923009623797</v>
+        <v>-14.03300521134909</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-20.41682873071438</v>
+        <v>-13.81841876629011</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-15.40381934312486</v>
+        <v>-9.38586326767085</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-15.47966530453396</v>
+        <v>-9.461025789626198</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-15.20519059205191</v>
+        <v>-4.217391304347814</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-20.83657840083073</v>
+        <v>-9.379530298637285</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 1.97</t>
+          <t>X ≈ 1.974</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.872986878662886</v>
+        <v>4.737419181054825</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-20.27997173786876</v>
+        <v>-20.27484279483591</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-10.84842556950844</v>
+        <v>-5.048146504859993</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>4.723205391285994</v>
+        <v>19.08645572328697</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>4.561909351310533</v>
+        <v>10.59479658302372</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-6.209890467229663</v>
+        <v>-5.700147167921955</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-7.047369950595758</v>
+        <v>-14.88266974418157</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>3.78552971576228</v>
+        <v>1.479076479076475</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.827016897676984</v>
+        <v>1.60700538876052</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>3.054101221640494</v>
+        <v>0.8109538935412459</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>3.328160863802417</v>
+        <v>1.08318890814558</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>3.04941146035442</v>
+        <v>0.806606953674283</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>1.926249393498338</v>
+        <v>-0.308285163776489</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-3.850385038503887</v>
+        <v>-8.889852558542998</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>1.047027219471154</v>
+        <v>-1.238673607094654</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>1.641414141414145</v>
+        <v>-0.6773695882749919</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-4.048058551118885</v>
+        <v>-9.114583333333336</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-4.152899254940067</v>
+        <v>-9.247467438495001</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>1.618547681539816</v>
+        <v>-0.6996718780158275</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-3.750162064047714</v>
+        <v>-8.818418766290179</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>1.262847323541813</v>
+        <v>-1.052529934337578</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>1.187001362132591</v>
+        <v>-1.127692456292863</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-4.094079480940792</v>
+        <v>-9.217391304347821</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-4.169911734164067</v>
+        <v>-9.379530298637285</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 2.044</t>
+          <t>X ≈ 2.049</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>16</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.530491559336944</v>
+        <v>2.661570473754828</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>2.19571476098713</v>
+        <v>2.415663638050958</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-17.55609147339856</v>
+        <v>-17.39166204278802</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-24.46898828460332</v>
+        <v>-24.20824811901128</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-12.60707609749141</v>
+        <v>-12.0887363057462</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>6.153150161865916</v>
+        <v>6.660802230298543</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-7.047369950595801</v>
+        <v>-6.549336410848241</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.075581395348834</v>
+        <v>-0.6042568542568603</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.03409421343413</v>
+        <v>-0.4763279445726667</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-8.057009889470621</v>
+        <v>-7.52237943979209</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-7.782950247308698</v>
+        <v>-7.250144425187756</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-8.061699650756694</v>
+        <v>-7.52672637965901</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-2.934861717612854</v>
+        <v>-2.391618497109825</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-3.155940594059402</v>
+        <v>-2.639852558542849</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-3.81408389163996</v>
+        <v>-3.32200694042799</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-3.219696969696969</v>
+        <v>-2.760702921608328</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-3.353614106674442</v>
+        <v>-2.864583333333336</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-3.458454810495624</v>
+        <v>-2.997467438494894</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-3.242563429571298</v>
+        <v>-2.783005211349163</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>3.194282380396729</v>
+        <v>3.681581233709821</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-3.598263787569302</v>
+        <v>-3.135863267670914</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>2.57589025102164</v>
+        <v>3.038974210373844</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>9.100364963503651</v>
+        <v>9.532608695652179</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-3.475467289719624</v>
+        <v>-3.129530298637242</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 2.118</t>
+          <t>X ≈ 2.123</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>17.24288395336543</v>
+        <v>-3.515108841484313</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>3.036471544249551</v>
+        <v>-3.761015677188183</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>29.37986254207484</v>
+        <v>14.69443514845641</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>14.68085643589359</v>
+        <v>-5.663147751140556</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.624447281090724</v>
+        <v>-15.75708783950633</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>14.92625940556371</v>
+        <v>-5.690045996487548</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>28.66691576368995</v>
+        <v>13.45066358915183</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>28.38870431893687</v>
+        <v>13.14574314574307</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>14.1444772151374</v>
+        <v>3.273672055427177</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>13.37156153910081</v>
+        <v>2.477620560207988</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>13.64562118126273</v>
+        <v>2.749855574812322</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.918842507899555</v>
+        <v>-17.52672637965919</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>12.24370971095862</v>
+        <v>-8.641618497109825</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>12.02263083451213</v>
+        <v>-8.889852558543076</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>11.36448753693147</v>
+        <v>-9.57200694042799</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-2.32683982683983</v>
+        <v>-19.01070292160833</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-2.460756963817303</v>
+        <v>-19.11458333333334</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-2.565597667638485</v>
+        <v>-9.247467438494937</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>11.93600799900013</v>
+        <v>0.9669947886508368</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>12.12285380896816</v>
+        <v>1.181581233709821</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-2.705406644712163</v>
+        <v>-9.385863267670914</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-2.781252606121363</v>
+        <v>0.5389742103736523</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-2.50677789363921</v>
+        <v>-9.217391304347821</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-2.582610146862486</v>
+        <v>0.6204697013625662</v>
       </c>
     </row>
   </sheetData>
@@ -2610,2457 +2610,2457 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2938</v>
+        <v>2962</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.02593220390497919</v>
+        <v>-0.07296531342739598</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.1554751626269422</v>
+        <v>-0.0661995597903271</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.01415548355652163</v>
+        <v>0.1731426798155908</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.1387756000119396</v>
+        <v>0.1361822160226396</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.4217783157469484</v>
+        <v>-0.1542225799744656</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.2835458435503639</v>
+        <v>-0.04572518437777973</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.02061749546538039</v>
+        <v>0.1520408145464458</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.008508224617131077</v>
+        <v>0.1349904575710994</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.1848058366127177</v>
+        <v>0.04678129912473139</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.07858333086836922</v>
+        <v>0.2785620531467146</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.06716843699106789</v>
+        <v>0.3347866208936452</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.1472555731239069</v>
+        <v>0.4477016149573672</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.2096326711248579</v>
+        <v>0.1601317553304327</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.2949802954506495</v>
+        <v>0.08019119776807315</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.3220608094946797</v>
+        <v>0.0576226892016436</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.148814117404946</v>
+        <v>0.2348342963101615</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.009157632455988107</v>
+        <v>0.3193789308176065</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>0.06048844468615755</v>
+        <v>0.3750468857382998</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.2627050952417562</v>
+        <v>0.6433265485968889</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.1081657664920854</v>
+        <v>0.2035036620403403</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.2766894931116397</v>
+        <v>0.1419613529024417</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.1962185925158124</v>
+        <v>0.1543588257584148</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.03752207290329324</v>
+        <v>0.3168645174544054</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.0590275347842919</v>
+        <v>0.2423468114234879</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; 0.07432</t>
+          <t>X &gt; 0.07451</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2938</v>
+        <v>2962</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.02593220390497919</v>
+        <v>-0.07296531342739598</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.1554751626269422</v>
+        <v>-0.0661995597903271</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.01415548355652163</v>
+        <v>0.1731426798155908</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.1387756000119396</v>
+        <v>0.1361822160226396</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.4217783157469484</v>
+        <v>-0.1542225799744656</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.2835458435503639</v>
+        <v>-0.04572518437777973</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.02061749546538039</v>
+        <v>0.1520408145464458</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.008508224617131077</v>
+        <v>0.1349904575710994</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.1848058366127177</v>
+        <v>0.04678129912473139</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.07858333086836922</v>
+        <v>0.2785620531467146</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.06716843699106789</v>
+        <v>0.3347866208936452</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.1472555731239069</v>
+        <v>0.4477016149573672</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.2096326711248579</v>
+        <v>0.1601317553304327</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.2949802954506495</v>
+        <v>0.08019119776807315</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.3220608094946797</v>
+        <v>0.0576226892016436</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.148814117404946</v>
+        <v>0.2348342963101615</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.009157632455988107</v>
+        <v>0.3193789308176065</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0.06048844468615755</v>
+        <v>0.3750468857382998</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.2627050952417562</v>
+        <v>0.6433265485968889</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.1081657664920854</v>
+        <v>0.2035036620403403</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.2766894931116397</v>
+        <v>0.1419613529024417</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.1962185925158124</v>
+        <v>0.1543588257584148</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.03752207290329324</v>
+        <v>0.3168645174544054</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.0590275347842919</v>
+        <v>0.2423468114234879</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; 0.1486</t>
+          <t>X &gt; 0.149</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2938</v>
+        <v>2962</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.02593220390497919</v>
+        <v>-0.07296531342739598</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.1554751626269422</v>
+        <v>-0.0661995597903271</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.01415548355652163</v>
+        <v>0.1731426798155908</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.1387756000119396</v>
+        <v>0.1361822160226396</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.4217783157469484</v>
+        <v>-0.1542225799744656</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2835458435503639</v>
+        <v>-0.04572518437777973</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.02061749546538039</v>
+        <v>0.1520408145464458</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.008508224617131077</v>
+        <v>0.1349904575710994</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.1848058366127177</v>
+        <v>0.04678129912473139</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.07858333086836922</v>
+        <v>0.2785620531467146</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.06716843699106789</v>
+        <v>0.3347866208936452</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.1472555731239069</v>
+        <v>0.4477016149573672</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.2096326711248579</v>
+        <v>0.1601317553304327</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.2949802954506495</v>
+        <v>0.08019119776807315</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.3220608094946797</v>
+        <v>0.0576226892016436</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.148814117404946</v>
+        <v>0.2348342963101615</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.009157632455988107</v>
+        <v>0.3193789308176065</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>0.06048844468615755</v>
+        <v>0.3750468857382998</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.2627050952417562</v>
+        <v>0.6433265485968889</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.1081657664920854</v>
+        <v>0.2035036620403403</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.2766894931116397</v>
+        <v>0.1419613529024417</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.1962185925158124</v>
+        <v>0.1543588257584148</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.03752207290329324</v>
+        <v>0.3168645174544054</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.0590275347842919</v>
+        <v>0.2423468114234879</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; 0.223</t>
+          <t>X &gt; 0.2235</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2938</v>
+        <v>2962</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.02593220390497919</v>
+        <v>-0.07296531342739598</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.1554751626269422</v>
+        <v>-0.0661995597903271</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.01415548355652163</v>
+        <v>0.1731426798155908</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.1387756000119396</v>
+        <v>0.1361822160226396</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.4217783157469484</v>
+        <v>-0.1542225799744656</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.2835458435503639</v>
+        <v>-0.04572518437777973</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.02061749546538039</v>
+        <v>0.1520408145464458</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.008508224617131077</v>
+        <v>0.1349904575710994</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.1848058366127177</v>
+        <v>0.04678129912473139</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.07858333086836922</v>
+        <v>0.2785620531467146</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.06716843699106789</v>
+        <v>0.3347866208936452</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.1472555731239069</v>
+        <v>0.4477016149573672</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.2096326711248579</v>
+        <v>0.1601317553304327</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.2949802954506495</v>
+        <v>0.08019119776807315</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.3220608094946797</v>
+        <v>0.0576226892016436</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.148814117404946</v>
+        <v>0.2348342963101615</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.009157632455988107</v>
+        <v>0.3193789308176065</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>0.06048844468615755</v>
+        <v>0.3750468857382998</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.2627050952417562</v>
+        <v>0.6433265485968889</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.1081657664920854</v>
+        <v>0.2035036620403403</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.2766894931116397</v>
+        <v>0.1419613529024417</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.1962185925158124</v>
+        <v>0.1543588257584148</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.03752207290329324</v>
+        <v>0.3168645174544054</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.0590275347842919</v>
+        <v>0.2423468114234879</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; 0.2973</t>
+          <t>X &gt; 0.2981</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2938</v>
+        <v>2962</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.02593220390497919</v>
+        <v>-0.07296531342739598</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.1554751626269422</v>
+        <v>-0.0661995597903271</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.01415548355652163</v>
+        <v>0.1731426798155908</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.1387756000119396</v>
+        <v>0.1361822160226396</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.4217783157469484</v>
+        <v>-0.1542225799744656</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.2835458435503639</v>
+        <v>-0.04572518437777973</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.02061749546538039</v>
+        <v>0.1520408145464458</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.008508224617131077</v>
+        <v>0.1349904575710994</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.1848058366127177</v>
+        <v>0.04678129912473139</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.07858333086836922</v>
+        <v>0.2785620531467146</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.06716843699106789</v>
+        <v>0.3347866208936452</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.1472555731239069</v>
+        <v>0.4477016149573672</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.2096326711248579</v>
+        <v>0.1601317553304327</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.2949802954506495</v>
+        <v>0.08019119776807315</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.3220608094946797</v>
+        <v>0.0576226892016436</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.148814117404946</v>
+        <v>0.2348342963101615</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.009157632455988107</v>
+        <v>0.3193789308176065</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>0.06048844468615755</v>
+        <v>0.3750468857382998</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.2627050952417562</v>
+        <v>0.6433265485968889</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.1081657664920854</v>
+        <v>0.2035036620403403</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.2766894931116397</v>
+        <v>0.1419613529024417</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.1962185925158124</v>
+        <v>0.1543588257584148</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.03752207290329324</v>
+        <v>0.3168645174544054</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.0590275347842919</v>
+        <v>0.2423468114234879</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; 0.3716</t>
+          <t>X &gt; 0.3726</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2938</v>
+        <v>2962</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.02593220390497919</v>
+        <v>-0.07296531342739598</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.1554751626269422</v>
+        <v>-0.0661995597903271</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.01415548355652163</v>
+        <v>0.1731426798155908</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.1387756000119396</v>
+        <v>0.1361822160226396</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.4217783157469484</v>
+        <v>-0.1542225799744656</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.2835458435503639</v>
+        <v>-0.04572518437777973</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.02061749546538039</v>
+        <v>0.1520408145464458</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.008508224617131077</v>
+        <v>0.1349904575710994</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.1848058366127177</v>
+        <v>0.04678129912473139</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.07858333086836922</v>
+        <v>0.2785620531467146</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.06716843699106789</v>
+        <v>0.3347866208936452</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.1472555731239069</v>
+        <v>0.4477016149573672</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.2096326711248579</v>
+        <v>0.1601317553304327</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.2949802954506495</v>
+        <v>0.08019119776807315</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.3220608094946797</v>
+        <v>0.0576226892016436</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.148814117404946</v>
+        <v>0.2348342963101615</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.009157632455988107</v>
+        <v>0.3193789308176065</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.06048844468615755</v>
+        <v>0.3750468857382998</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.2627050952417562</v>
+        <v>0.6433265485968889</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.1081657664920854</v>
+        <v>0.2035036620403403</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.2766894931116397</v>
+        <v>0.1419613529024417</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.1962185925158124</v>
+        <v>0.1543588257584148</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-0.03752207290329324</v>
+        <v>0.3168645174544054</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.0590275347842919</v>
+        <v>0.2423468114234879</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; 0.4459</t>
+          <t>X &gt; 0.4471</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2938</v>
+        <v>2962</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.02593220390497919</v>
+        <v>-0.07296531342739598</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.1554751626269422</v>
+        <v>-0.0661995597903271</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.01415548355652163</v>
+        <v>0.1731426798155908</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.1387756000119396</v>
+        <v>0.1361822160226396</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.4217783157469484</v>
+        <v>-0.1542225799744656</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.2835458435503639</v>
+        <v>-0.04572518437777973</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.02061749546538039</v>
+        <v>0.1520408145464458</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.008508224617131077</v>
+        <v>0.1349904575710994</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.1848058366127177</v>
+        <v>0.04678129912473139</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.07858333086836922</v>
+        <v>0.2785620531467146</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.06716843699106789</v>
+        <v>0.3347866208936452</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.1472555731239069</v>
+        <v>0.4477016149573672</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.2096326711248579</v>
+        <v>0.1601317553304327</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.2949802954506495</v>
+        <v>0.08019119776807315</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.3220608094946797</v>
+        <v>0.0576226892016436</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.148814117404946</v>
+        <v>0.2348342963101615</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.009157632455988107</v>
+        <v>0.3193789308176065</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.06048844468615755</v>
+        <v>0.3750468857382998</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>0.2627050952417562</v>
+        <v>0.6433265485968889</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.1081657664920854</v>
+        <v>0.2035036620403403</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.2766894931116397</v>
+        <v>0.1419613529024417</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.1962185925158124</v>
+        <v>0.1543588257584148</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.03752207290329324</v>
+        <v>0.3168645174544054</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.0590275347842919</v>
+        <v>0.2423468114234879</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; 0.5202</t>
+          <t>X &gt; 0.5216</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2938</v>
+        <v>2962</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.02593220390497919</v>
+        <v>-0.07296531342739598</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.1554751626269422</v>
+        <v>-0.0661995597903271</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.01415548355652163</v>
+        <v>0.1731426798155908</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.1387756000119396</v>
+        <v>0.1361822160226396</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.4217783157469484</v>
+        <v>-0.1542225799744656</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.2835458435503639</v>
+        <v>-0.04572518437777973</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.02061749546538039</v>
+        <v>0.1520408145464458</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.008508224617131077</v>
+        <v>0.1349904575710994</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.1848058366127177</v>
+        <v>0.04678129912473139</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.07858333086836922</v>
+        <v>0.2785620531467146</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.06716843699106789</v>
+        <v>0.3347866208936452</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.1472555731239069</v>
+        <v>0.4477016149573672</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.2096326711248579</v>
+        <v>0.1601317553304327</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.2949802954506495</v>
+        <v>0.08019119776807315</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.3220608094946797</v>
+        <v>0.0576226892016436</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.148814117404946</v>
+        <v>0.2348342963101615</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.009157632455988107</v>
+        <v>0.3193789308176065</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.06048844468615755</v>
+        <v>0.3750468857382998</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.2627050952417562</v>
+        <v>0.6433265485968889</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.1081657664920854</v>
+        <v>0.2035036620403403</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.2766894931116397</v>
+        <v>0.1419613529024417</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.1962185925158124</v>
+        <v>0.1543588257584148</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-0.03752207290329324</v>
+        <v>0.3168645174544054</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.0590275347842919</v>
+        <v>0.2423468114234879</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; 0.5945</t>
+          <t>X &gt; 0.5961</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2932</v>
+        <v>2951</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.0004813836656296644</v>
+        <v>-0.07694705112539424</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.2154613101557672</v>
+        <v>-0.102905829045028</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.008695485380719958</v>
+        <v>0.1419575194791349</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.1604952853402608</v>
+        <v>0.1070444365972136</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.4094881649085877</v>
+        <v>-0.1497324790071346</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.2713507103960495</v>
+        <v>-0.00770906663034765</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.02762156620099177</v>
+        <v>0.1937519236089429</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.006394164732640206</v>
+        <v>0.1440568051023305</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.1703420911930422</v>
+        <v>0.05504857364586968</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.09516402357286324</v>
+        <v>0.2568983192359227</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.08317275642897926</v>
+        <v>0.278552401280848</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.1639971541379381</v>
+        <v>0.3928953697499225</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.2253241453584707</v>
+        <v>0.07459771910640001</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.3103948613154444</v>
+        <v>-0.004717423407797128</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.3361927351773701</v>
+        <v>-0.02486263491937279</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.1638106137936006</v>
+        <v>0.1508927511435303</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.00524787114007097</v>
+        <v>0.2361099368729569</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>0.08044542784281106</v>
+        <v>0.3262808700300965</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.2826409301017279</v>
+        <v>0.6285853131855248</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.08936327548061485</v>
+        <v>0.1863205702027173</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.2571223906357432</v>
+        <v>0.09280971811107719</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.1763251545680475</v>
+        <v>0.1055167095272083</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.01785869827609332</v>
+        <v>0.2677035466006856</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.03924628016982723</v>
+        <v>0.2273826122403904</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; 0.6689</t>
+          <t>X &gt; 0.6706</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2913</v>
+        <v>2927</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.07421764457757973</v>
+        <v>-0.0148112599966268</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.2081503352389902</v>
+        <v>-0.1407561630679481</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.05893627595601458</v>
+        <v>0.08236636009164755</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.2412336230395482</v>
+        <v>0.05197624754006114</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.5238208999017644</v>
+        <v>-0.2386336567875205</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.3518978798839711</v>
+        <v>-0.06278311081396026</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.04600383037718103</v>
+        <v>0.1467886741279685</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.0314235545562056</v>
+        <v>0.1331623908978514</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.2095897705086287</v>
+        <v>0.04237953842044817</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.1652123327516009</v>
+        <v>0.3544494135593936</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.1171865515969159</v>
+        <v>0.3400529880185132</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.1319370238926325</v>
+        <v>0.355466333994336</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.2184003897551818</v>
+        <v>0.07772755193649061</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.3025867268451634</v>
+        <v>-0.0002067819761748524</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.3242687598357819</v>
+        <v>-0.01493709374996399</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.1546284765462858</v>
+        <v>0.1576679032042136</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.1086161091528908</v>
+        <v>0.3467190873962949</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.1613190071877213</v>
+        <v>0.4046471590494036</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.3634530256909514</v>
+        <v>0.6735795720012305</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.0121648075319456</v>
+        <v>0.2259498343924164</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.2117754473772635</v>
+        <v>0.1704507255031444</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.1299416529235131</v>
+        <v>0.1497628754472018</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>0.06210140825313459</v>
+        <v>0.3454502257068199</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>0.0754252609154662</v>
+        <v>0.3061547030709519</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; 0.7432</t>
+          <t>X &gt; 0.7451</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2863</v>
+        <v>2879</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.1732999045985437</v>
+        <v>0.1470284443031957</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.2468691424442895</v>
+        <v>-0.1148529843042922</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.1395277630334562</v>
+        <v>0.0637426586555776</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.4514841722027541</v>
+        <v>-0.1644527847766142</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.7332207861361226</v>
+        <v>-0.4553868996412263</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.526897473721732</v>
+        <v>-0.2447552621733777</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.271831382145443</v>
+        <v>-0.05313737836723931</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.2174826814107078</v>
+        <v>-0.06199968177155313</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.4343028365217592</v>
+        <v>-0.1910582350291818</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.02994663226851202</v>
+        <v>0.2085095259636986</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.09331907124745698</v>
+        <v>0.1200977893451167</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.1431476145575914</v>
+        <v>0.07105832092938869</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.4801263415682442</v>
+        <v>-0.1928650345059495</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.5271105104939409</v>
+        <v>-0.2333428632520764</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.6422796422495054</v>
+        <v>-0.3756092958142077</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.3407771090697835</v>
+        <v>-0.07099398189939166</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.03389025024434744</v>
+        <v>0.226837810514148</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>0.0544461657944737</v>
+        <v>0.2532260427810655</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.2911826464663747</v>
+        <v>0.5576989162956494</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.05938126231087892</v>
+        <v>0.1336978194141949</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.2530090771715336</v>
+        <v>0.05202708624997143</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.2382458746328595</v>
+        <v>-0.002504442871597234</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>0.05706887411817263</v>
+        <v>0.2964975845410649</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>0.071948008918163</v>
+        <v>0.2592331608972742</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; 0.8175</t>
+          <t>X &gt; 0.8197</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2712</v>
+        <v>2716</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.1827899154740038</v>
+        <v>0.03924461691864423</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.2420953612693353</v>
+        <v>-0.1139448983665687</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.04930755253741381</v>
+        <v>0.0408981572639604</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.5588314124899441</v>
+        <v>-0.3118098864681613</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.7643295561373407</v>
+        <v>-0.6037209475125849</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.6669168678784345</v>
+        <v>-0.4631522382347129</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.2083527155389149</v>
+        <v>-0.1024499639617957</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.1722431708440695</v>
+        <v>-0.09353864245765919</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.5868465070121118</v>
+        <v>-0.4579994988249467</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.3844695076791425</v>
+        <v>-0.3533292014349243</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.6033689032029272</v>
+        <v>-0.5003278441165904</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.5672103046876273</v>
+        <v>-0.4992034438792388</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.8239649884691147</v>
+        <v>-0.6753923590775202</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.8980390872604289</v>
+        <v>-0.740072822860121</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.7626133034046632</v>
+        <v>-0.6296639363883259</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.4406421701383039</v>
+        <v>-0.3038697107339772</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.1849238932822388</v>
+        <v>-0.1289162991547244</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.01025827019381609</v>
+        <v>0.05400314974036036</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.2276133009147117</v>
+        <v>0.4006100883933854</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.07919828258670236</v>
+        <v>0.04839506741107158</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.4007499754146053</v>
+        <v>-0.1511318475090349</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.3073079803711849</v>
+        <v>-0.09407694899314833</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>0.06286035605801743</v>
+        <v>0.2450534673752998</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>0.082792297301026</v>
+        <v>0.1565521755895176</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; 0.8918</t>
+          <t>X &gt; 0.8942</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2381</v>
+        <v>2375</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.07686211968457002</v>
+        <v>-0.1397039723694746</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.1807948875949634</v>
+        <v>-0.1126772563792144</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.386525730942104</v>
+        <v>-0.3838043476951825</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.2000527398548471</v>
+        <v>-0.07542919561795003</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.2619699162683418</v>
+        <v>-0.2022795980891345</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.2408694601116323</v>
+        <v>0.3126912080790376</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.6626175128392617</v>
+        <v>0.6712579801103189</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.5515602678354483</v>
+        <v>0.4740513534483313</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.3024888622635586</v>
+        <v>-0.2537682462065973</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.4901202573635999</v>
+        <v>-0.4393953660284708</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.010374996472578</v>
+        <v>-0.9398718885001216</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.7634980614635083</v>
+        <v>-0.6475317487865624</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.025865901713225</v>
+        <v>-0.8573129998374753</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.8703757405029151</v>
+        <v>-0.6439440398689982</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-1.127290254134728</v>
+        <v>-0.9238121461374789</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-0.7176031673519034</v>
+        <v>-0.505873018206394</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.4917582206250088</v>
+        <v>-0.3750875350140035</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.4041798733623523</v>
+        <v>-0.2310739958719878</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.07956552600735023</v>
+        <v>0.1764144690545351</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.2453149350395094</v>
+        <v>-0.04685797537726444</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.5361832506565563</v>
+        <v>-0.2356739534092469</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.6291034543917391</v>
+        <v>-0.370116698717105</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.07784662339810922</v>
+        <v>0.1510297482837615</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.3806541859816974</v>
+        <v>-0.263740824953075</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 0.9661</t>
+          <t>X &gt; 0.9687</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1973</v>
+        <v>1966</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.7812634393318447</v>
+        <v>0.6450624747148339</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.0716360178310893</v>
+        <v>0.07315245334857678</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.4840654960240371</v>
+        <v>-0.4748278676242705</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.4647952691332193</v>
+        <v>-0.2090776181740353</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.2690339784825468</v>
+        <v>-0.1536122470378416</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.1981303705741908</v>
+        <v>0.2841488353410213</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.6139203719848894</v>
+        <v>0.6296322443590441</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.9405476369092298</v>
+        <v>0.9606141624350997</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.4510130233181471</v>
+        <v>-0.2992024384998828</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.9717854820071778</v>
+        <v>-0.7628857689060169</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.101154987601184</v>
+        <v>-0.7944482226561078</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.5944948071643594</v>
+        <v>-0.2825521142081868</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.8809747918177564</v>
+        <v>-0.5067984261518959</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.7991763335848958</v>
+        <v>-0.4002428271694001</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.8721646997207628</v>
+        <v>-0.5963477112190674</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.6521123309905477</v>
+        <v>-0.411007335611373</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.5540691117300511</v>
+        <v>-0.4343802876480609</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.5577975809708491</v>
+        <v>-0.4866751581495805</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.1602417300265344</v>
+        <v>0.062523243935388</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.3988350285101561</v>
+        <v>-0.2520740789490503</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.8401666215774029</v>
+        <v>-0.5653243759576441</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.784869242649286</v>
+        <v>-0.5388092161640685</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>0.02615017120375285</v>
+        <v>0.1417134769339725</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-0.1714885770992538</v>
+        <v>-0.07129021725376106</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 1.04</t>
+          <t>X &gt; 1.043</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1510</v>
+        <v>1500</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.280412729087722</v>
+        <v>0.9968033580391662</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.2001807075795483</v>
+        <v>-0.1768702106004199</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.6830253524027938</v>
+        <v>-0.5037975795562843</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.622980938177932</v>
+        <v>-1.228737883069613</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.7387032422764719</v>
+        <v>-0.6724612141626736</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.2517214642037615</v>
+        <v>-0.2134448432074194</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.525630820160977</v>
+        <v>-0.506839730901369</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.5136807917394322</v>
+        <v>0.5826621364469986</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.9228549253655771</v>
+        <v>-0.7794840907521561</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.432092288943259</v>
+        <v>-1.30975485507448</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.02619349055194</v>
+        <v>-0.9710746577458949</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.541910732550889</v>
+        <v>-0.4788540392335179</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.165059737414794</v>
+        <v>-0.8904541591191375</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.7920792079207928</v>
+        <v>-0.5398858253426724</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-1.054182901540955</v>
+        <v>-0.8893722098890677</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.8831712101196914</v>
+        <v>-0.7550438004365603</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.9783662547246763</v>
+        <v>-0.9255021083000443</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.9510192520025598</v>
+        <v>-0.9252304211846862</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.3655793025871716</v>
+        <v>-0.2721790954264449</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.8675971695701747</v>
+        <v>-0.8184187662901863</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-1.277780663810205</v>
+        <v>-1.052529934337578</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.6918132565892563</v>
+        <v>-0.6610257896262013</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>0.350364963503651</v>
+        <v>0.3159420289855177</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>0.009632048028720419</v>
+        <v>0.2204697013627097</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 1.115</t>
+          <t>X &gt; 1.118</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1121</v>
+        <v>1125</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.1036462786385144</v>
+        <v>-0.0090578235169545</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.00736994352781295</v>
+        <v>0.1867314538533691</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.4268821488092414</v>
+        <v>-0.007891976660111766</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.444618181668943</v>
+        <v>-0.9536510659277013</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.5826350213262188</v>
+        <v>-0.4341562024934689</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.09626014922380222</v>
+        <v>0.2139153626576871</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.005740189745445434</v>
+        <v>-0.0006638444765556528</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.6017879580612657</v>
+        <v>0.5793714643272097</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.4578530786823549</v>
+        <v>-0.6201332543072624</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.8761588256408359</v>
+        <v>-1.062202448641642</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.4247942189399083</v>
+        <v>-0.7899674340373082</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.6526490740042519</v>
+        <v>-1.016540374344622</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.1262471527815521</v>
+        <v>-0.3969376460459912</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.4519634911981498</v>
+        <v>0.2413531152159365</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.2061798063824085</v>
+        <v>-0.4408012666691192</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-0.5363636363636317</v>
+        <v>-0.8030720431699976</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-1.06268883977053</v>
+        <v>-1.439339322685591</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.544753742879962</v>
+        <v>-0.9511054154248342</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-0.2761787456888385</v>
+        <v>-0.5072503268021009</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.3930616481237692</v>
+        <v>-0.8628632107346164</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-0.5791015772306238</v>
+        <v>-0.8969743787820263</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.4766944192101334</v>
+        <v>-0.7943591229595341</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>0.2076352578836662</v>
+        <v>-0.1951690821256022</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.3102151366853647</v>
+        <v>0.08713636802938396</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 1.189</t>
+          <t>X &gt; 1.192</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.4340427544094467</v>
+        <v>-0.00280371926103129</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.8701910661917935</v>
+        <v>0.7468646662740284</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.2868513400850929</v>
+        <v>-0.3972099665909994</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.159709563036969</v>
+        <v>-1.100231634425775</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.440288005288977</v>
+        <v>-0.158975615233075</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.02988846780786503</v>
+        <v>0.170441060963654</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.2367387213598846</v>
+        <v>-0.2300459452163111</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.03875968992248602</v>
+        <v>0.01935733643050241</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.408262727846548</v>
+        <v>-1.404820184040602</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.959448913860861</v>
+        <v>-2.090006934248855</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.131065546643505</v>
+        <v>-1.263448194589088</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.5228969900028062</v>
+        <v>-0.8748416789938602</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.02836893181925149</v>
+        <v>-0.3730280420598859</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.1945033571059724</v>
+        <v>-0.06632314677822393</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-0.3526521491316359</v>
+        <v>-0.6374897373203297</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-0.8681431406181659</v>
+        <v>-1.186063631930189</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-1.002060277595639</v>
+        <v>-1.400931834998154</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-0.6629498160450069</v>
+        <v>-0.978876983444998</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-1.048118985126855</v>
+        <v>-1.319353713013982</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.9074973748869226</v>
+        <v>-1.373974321845736</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-1.11633942716886</v>
+        <v>-1.496974378782021</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.6360118624377975</v>
+        <v>-0.9054702340706413</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-0.4068733438460157</v>
+        <v>-0.772946859903378</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>0.07408727598193821</v>
+        <v>-0.0461969653039489</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 1.263</t>
+          <t>X &gt; 1.267</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.8557971818700452</v>
+        <v>0.6240399385560664</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.6552485714396994</v>
+        <v>0.7813589093038047</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.319683229269145</v>
+        <v>-1.145378203340464</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.153478700685625</v>
+        <v>-1.065737391395999</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.6077441149831344</v>
+        <v>-0.4004353164415662</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.4802730187269759</v>
+        <v>-0.4379690688712472</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.3075558253826429</v>
+        <v>0.1892080635452871</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.4342026802247148</v>
+        <v>0.4233711780881606</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.7976077269476463</v>
+        <v>-0.7964088071064381</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.705658538119266</v>
+        <v>-1.862002081301526</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.755923220281673</v>
+        <v>-0.9159126192578313</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.2238618129188552</v>
+        <v>-0.3838692368019139</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.2197390942951714</v>
+        <v>0.06283494418572388</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.2692962124358687</v>
+        <v>0.2194591823477552</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>0.8290148904980654</v>
+        <v>0.7518796992481285</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>0.4761758313855751</v>
+        <v>0.368514352345791</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.7482126862890155</v>
+        <v>0.6694922402159236</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>0.3727359878805601</v>
+        <v>0.266702601990886</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.588627368804886</v>
+        <v>0.6161175956683778</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>0.8568840064129972</v>
+        <v>0.5059055580341507</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>0.3143378384469671</v>
+        <v>0.07359619178854615</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>1.187001362132712</v>
+        <v>1.214649886049479</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>1.190473364587668</v>
+        <v>1.052878965922446</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>1.656646531418581</v>
+        <v>1.701550782443796</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 1.338</t>
+          <t>X &gt; 1.341</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.441120099682792</v>
+        <v>1.047537206315631</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.7784744488739506</v>
+        <v>0.6376959443822514</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.807085583763595</v>
+        <v>-1.928473567345399</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.77520124954944</v>
+        <v>-1.865138061235584</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.528176926486999</v>
+        <v>-1.484958496416887</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.58019886143358</v>
+        <v>-1.238655055429973</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.106775891189812</v>
+        <v>-0.9572311476903437</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.1001611789085857</v>
+        <v>0.2181115667957698</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-2.00356616062885</v>
+        <v>-1.792117418256964</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-3.601564344916163</v>
+        <v>-3.57501101873946</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.832455197803746</v>
+        <v>-2.809354951503543</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.616155096301242</v>
+        <v>-2.756989537553785</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.168332791992974</v>
+        <v>-1.310481759053815</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.8935438998445306</v>
+        <v>-1.229226528888894</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-0.72524091643335</v>
+        <v>-1.0876576817789</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-0.4614325068870428</v>
+        <v>-0.6910983087582423</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>0.5616751495239072</v>
+        <v>0.02874450851180654</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.534901091487356</v>
+        <v>-0.9278628256448513</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>0.1768580580320034</v>
+        <v>-0.2191666611020437</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>0.4624943009265294</v>
+        <v>-0.2375606804815931</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.411177694854068</v>
+        <v>-0.8050051818623274</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>0.8374796549951142</v>
+        <v>0.6049808110338759</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>0.2841397979407319</v>
+        <v>0.02353278806142356</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>1.367247942068452</v>
+        <v>1.346542308623441</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 1.412</t>
+          <t>X &gt; 1.416</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.9730888564362132</v>
+        <v>1.020110914474948</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.2616642238114366</v>
+        <v>0.2038618734478845</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-2.306298328044413</v>
+        <v>-2.571744775972206</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-2.353012074595135</v>
+        <v>-2.593804769457236</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.5077560728405928</v>
+        <v>-0.5879940882637982</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.8878976372158078</v>
+        <v>-0.8971115414726611</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.554945708171516</v>
+        <v>-1.778344044436025</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.2501761804087437</v>
+        <v>-0.1748675412797596</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.981063910403833</v>
+        <v>-2.146175272817032</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-4.079737162197894</v>
+        <v>-4.46894432528827</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-3.048101762460213</v>
+        <v>-3.433350532057986</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.379881468938514</v>
+        <v>-2.755734013246837</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.499852229946775</v>
+        <v>-1.85385559080008</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.341424465027139</v>
+        <v>-1.528475885502779</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-0.8610478385090303</v>
+        <v>-1.063402733927035</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-0.07690759588292906</v>
+        <v>-0.3108941261972404</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>0.7379418705551544</v>
+        <v>0.3500438177182943</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.1259121159984673</v>
+        <v>-0.7388632319939816</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.4694859062920784</v>
+        <v>-0.1419918270279439</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>0.5802139393320829</v>
+        <v>-0.1977291111177735</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>0.0376677713660527</v>
+        <v>-0.3820318500463955</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>0.9123921521622833</v>
+        <v>0.6922309153546422</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>0.9967527962032747</v>
+        <v>0.7442945194069637</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>1.871490885185324</v>
+        <v>1.923151693699879</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 1.486</t>
+          <t>X &gt; 1.49</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.451745479160628</v>
+        <v>1.152208952640578</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.191042754884883</v>
+        <v>0.6715603328991477</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-2.635865183034994</v>
+        <v>-2.461068041292897</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-3.458383523178952</v>
+        <v>-3.288212024138687</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.578666522570224</v>
+        <v>-1.216352323862431</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.2289096387984273</v>
+        <v>-0.4601367515566963</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.569514472740281</v>
+        <v>-1.832355278772773</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.4832764135089747</v>
+        <v>-0.01463421274742416</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.8738378031777216</v>
+        <v>-1.065950586082188</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-3.744655577116305</v>
+        <v>-4.220492647339256</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-2.071994536352989</v>
+        <v>-2.533163293112288</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-2.350743939800985</v>
+        <v>-3.045594304187361</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.7736467643417839</v>
+        <v>-1.194809986471519</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.5274359211622084</v>
+        <v>-0.9702308091339589</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.7182894991165938</v>
+        <v>-0.9431653328629821</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>0.3433871424525563</v>
+        <v>-0.1454546946579782</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>0.9104045849143461</v>
+        <v>0.2234781323877044</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.1290155581591748</v>
+        <v>-0.8550324503152709</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>0.554165542391317</v>
+        <v>-0.1677569843988138</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>0.8816360103733132</v>
+        <v>-0.05064625444184401</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>0.1048978049365559</v>
+        <v>-0.6180907558225783</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>1.200012030881084</v>
+        <v>0.4915808454448936</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>1.24029470589241</v>
+        <v>0.498248506078717</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>1.867038565081316</v>
+        <v>1.520943635012003</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 1.561</t>
+          <t>X &gt; 1.565</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.4132069406220893</v>
+        <v>-0.0683064864187557</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.2218701580280253</v>
+        <v>-0.314213322122626</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-2.861090408260218</v>
+        <v>-2.777366638515716</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-3.716958426038651</v>
+        <v>-3.671883640949318</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.779607996609435</v>
+        <v>-1.832638155671006</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.08206779238516759</v>
+        <v>0.003321358960242549</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.289794193019993</v>
+        <v>-1.534138842459178</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.8562367864693456</v>
+        <v>0.5925516563814455</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.9204578497977707</v>
+        <v>-0.7992762728402312</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-3.814585647046371</v>
+        <v>-4.026938710308812</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-3.237495701854158</v>
+        <v>-3.450752327923311</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-3.21321480227185</v>
+        <v>-3.423382914613455</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.8261991036310548</v>
+        <v>-1.194809986471519</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.1685274910469801</v>
+        <v>-0.2272385767800102</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>0.1182869290287343</v>
+        <v>-0.3014902231027605</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>1.016625218752878</v>
+        <v>0.5637651634980543</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>1.490610817337711</v>
+        <v>0.763836119554206</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>0.7778673779542231</v>
+        <v>0.02304927883029251</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>1.297710126659702</v>
+        <v>0.8454142415383785</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>1.66989213649429</v>
+        <v>0.7560493188162027</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>0.8224679197477727</v>
+        <v>0.1886048174354684</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>2.27101220224111</v>
+        <v>1.937150502167121</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>1.6308527683817</v>
+        <v>1.268930884102026</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>2.469654661499888</v>
+        <v>2.626548728718333</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 1.635</t>
+          <t>X &gt; 1.639</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.2317562043410604</v>
+        <v>-0.6468738323576986</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.9453208814787502</v>
+        <v>-0.8927806680615689</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-5.034855082024897</v>
+        <v>-5.236277858756239</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-4.415570364285934</v>
+        <v>-4.670378899263305</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-1.882234781047067</v>
+        <v>-2.629334722760319</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.5948077409281822</v>
+        <v>0.6164019720408476</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.491814395040201</v>
+        <v>-1.898173620150573</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>1.295108259823571</v>
+        <v>0.51008423101446</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.1959716080701384</v>
+        <v>-0.5247775569758559</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-4.800304908627702</v>
+        <v>-5.196798044443248</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-4.143103504013681</v>
+        <v>-4.924563029838914</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-5.188136432365887</v>
+        <v>-5.976338782759825</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-2.863022637153044</v>
+        <v>-2.827665008737732</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-2.31781798869541</v>
+        <v>-1.913108372496424</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-1.443394236467554</v>
+        <v>-1.044875157482252</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.8490073145245631</v>
+        <v>-0.8711680378873936</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.599782689049924</v>
+        <v>-0.9750484496124017</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-1.087765155323218</v>
+        <v>-1.883126353223616</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.4887320119467802</v>
+        <v>-0.5058734284034259</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.3018862019787534</v>
+        <v>-0.6788838825692451</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.8444323699447835</v>
+        <v>-1.246328383949979</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>0.6122887184545505</v>
+        <v>0.2288966909939489</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>0.1204799060323936</v>
+        <v>-0.302662622177273</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>0.4277894152612163</v>
+        <v>0.3103921819828628</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 1.709</t>
+          <t>X &gt; 1.714</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-1.140847113431967</v>
+        <v>-1.542626728110598</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-1.475623911781781</v>
+        <v>-1.288533563814468</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-5.413642960812773</v>
+        <v>-6.043227665706048</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-4.367803010406263</v>
+        <v>-5.135629864514272</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-1.411882402297735</v>
+        <v>-2.411188004613606</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.805386814102668</v>
+        <v>1.245745601384471</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.1945780724231625</v>
+        <v>-1.272954501300504</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>3.588124188407519</v>
+        <v>2.44222555780344</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2.106768730728305</v>
+        <v>1.062616779045335</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-3.234674864089911</v>
+        <v>-4.256047781500634</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-2.45300100873002</v>
+        <v>-3.481300204082231</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-3.746978838573959</v>
+        <v>-4.762907284181672</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.809227199846319</v>
+        <v>-1.857698899119875</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.5226918630949342</v>
+        <v>-1.603420397738908</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>0.8496216921163935</v>
+        <v>-0.2755245283676899</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>1.951622827257339</v>
+        <v>0.7882920532660478</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>2.32531990347784</v>
+        <v>0.6844116415410397</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>0.6976365600627545</v>
+        <v>-0.9560101520627811</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>1.421142154185056</v>
+        <v>0.2634772007111366</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>1.607987964153082</v>
+        <v>-0.02444891704394792</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>1.065441796187052</v>
+        <v>-0.5918934184246822</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>2.00482426117388</v>
+        <v>0.8404817480622384</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>1.771684760457958</v>
+        <v>0.5816036705265546</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>1.188238294036729</v>
+        <v>0.9219772390511523</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 1.784</t>
+          <t>X &gt; 1.788</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-1.439589251796747</v>
+        <v>-1.97029968408544</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-4.919020138196878</v>
+        <v>-4.731929790229565</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-8.243831640058055</v>
+        <v>-8.502347162561392</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-7.06999320667061</v>
+        <v>-7.20795690853943</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-4.563653275587598</v>
+        <v>-4.96779177819851</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.05369265734522344</v>
+        <v>-0.4083424489299858</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.633357211742258</v>
+        <v>-2.751868056417862</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>1.910087394460078</v>
+        <v>0.7406798546038971</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.04074655089707591</v>
+        <v>-1.030125412927184</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-3.916882500935593</v>
+        <v>-4.990733870171837</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-2.368937508455197</v>
+        <v>-3.452676070757377</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-5.195457612540132</v>
+        <v>-6.260903594848934</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.05080707219610048</v>
+        <v>-1.046681788249067</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.8072144794097227</v>
+        <v>-1.927827242087233</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>0.4454702484874247</v>
+        <v>-0.7112474467570991</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>2.313742520748889</v>
+        <v>1.748790749277752</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>2.816768058930649</v>
+        <v>1.644910337552744</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>1.438042004791001</v>
+        <v>0.24620344758101</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>2.927818736033792</v>
+        <v>2.35939985194198</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>3.114664546001819</v>
+        <v>1.941074904595901</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>1.298233027717323</v>
+        <v>0.1078076184050332</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>3.770157766945161</v>
+        <v>3.197202058475071</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>2.770747129108742</v>
+        <v>2.175013758943322</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>2.057972200726233</v>
+        <v>2.645786157058915</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 1.858</t>
+          <t>X &gt; 1.863</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>126</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-1.297097113431967</v>
+        <v>-2.361524365905872</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-3.975623911781781</v>
+        <v>-3.394832776412898</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-7.757392960812773</v>
+        <v>-7.799133177517071</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-8.470346980255513</v>
+        <v>-8.391535376325294</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-3.706481940991765</v>
+        <v>-4.730085642408881</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-2.73211418009123</v>
+        <v>-2.9983488868045</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-3.07911598234179</v>
+        <v>-4.168384029895854</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.6109265411591096</v>
+        <v>-0.5050505050505123</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.9348878642277825</v>
+        <v>-1.964423182667986</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-4.882406714867443</v>
+        <v>-5.935077852490494</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-4.60834707270552</v>
+        <v>-5.66284283788616</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-7.268048857105903</v>
+        <v>-8.320377173309851</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-3.629306162057254</v>
+        <v>-3.879713735205058</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-3.056734244853054</v>
+        <v>-3.334297002987377</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-2.127575955132016</v>
+        <v>-2.429149797570851</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>0.05411255411255667</v>
+        <v>-0.280544191449593</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>1.507497004436672</v>
+        <v>0.4092261904761898</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.1846452866860986</v>
+        <v>-1.310959501986993</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>0.03124609423822733</v>
+        <v>-0.3028464811904286</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>1.011742697857045</v>
+        <v>-0.08826003613144451</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.324454263759776</v>
+        <v>-1.44935533116297</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>3.567953743085084</v>
+        <v>3.237386908786497</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>1.461476074614765</v>
+        <v>1.100069013112495</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>0.591993027740692</v>
+        <v>1.73158081247383</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 1.932</t>
+          <t>X &gt; 1.937</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.004483477068326636</v>
+        <v>-0.2715986907274228</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-3.975623911781781</v>
+        <v>-3.321243844188302</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-5.413642960812773</v>
+        <v>-5.510517385332214</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-7.03568788934642</v>
+        <v>-7.037499023392776</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-3.251378278490854</v>
+        <v>-4.509318845735109</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.3121185144118357</v>
+        <v>-0.6140674827276769</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.5658884691142845</v>
+        <v>-2.775751505187863</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>4.711455641688204</v>
+        <v>2.579705409894082</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>2.901090971751053</v>
+        <v>0.8208418667480046</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.6496024820632158</v>
+        <v>-2.805398307716622</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.3755428399012928</v>
+        <v>-2.533163293112288</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-3.432070021127068</v>
+        <v>-5.639933926828867</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.8515283842794759</v>
+        <v>-2.981241138619261</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.1466813348001494</v>
+        <v>-2.286078973637274</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>1.972953145397078</v>
+        <v>-0.1380446762770475</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>2.567340067340069</v>
+        <v>0.4232593425426145</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>3.35934885628852</v>
+        <v>1.262775157232703</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>2.328582226541414</v>
+        <v>0.1864948256560055</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>4.396325459317588</v>
+        <v>2.287749505631965</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>4.583171269285614</v>
+        <v>2.502335950690949</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>2.188773249467737</v>
+        <v>0.04809899648002869</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>6.742556917688255</v>
+        <v>5.633313833015315</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>4.239253852392537</v>
+        <v>2.103363412633307</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>4.163421599169261</v>
+        <v>3.828016871174036</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 2.007</t>
+          <t>X &gt; 2.012</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.3799775482145691</v>
+        <v>-0.9110477807421802</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.7147543465643835</v>
+        <v>-1.15695461644605</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-4.32668643907364</v>
+        <v>-5.569543455179733</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-9.387466545472904</v>
+        <v>-10.37247196977743</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-4.81403580445113</v>
+        <v>-6.437503794087291</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.8674358761517311</v>
+        <v>0.03521928559499798</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.7304078271820131</v>
+        <v>-1.230187474678026</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>4.896640826873387</v>
+        <v>2.720211230849522</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>2.71590578656587</v>
+        <v>0.7204805660655538</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-1.390343222803956</v>
+        <v>-3.267060290855923</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-1.116283580642033</v>
+        <v>-2.994825276251589</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-4.728366317423358</v>
+        <v>-6.462896592425011</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-1.40708393983504</v>
+        <v>-3.322469560939609</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.5940594059405981</v>
+        <v>-1.443044047904628</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>2.158138330582261</v>
+        <v>0.002461144678392202</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>2.752525252525253</v>
+        <v>0.5637651634980543</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>4.840830337770001</v>
+        <v>2.58754432624113</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>3.624878522837705</v>
+        <v>1.390830433845494</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>4.951881014873145</v>
+        <v>2.669122448225302</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>6.249837935952286</v>
+        <v>3.947538680518328</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>2.37395843465292</v>
+        <v>0.1886048174354684</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>7.853668028799383</v>
+        <v>6.49642101888444</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>5.905920519059208</v>
+        <v>3.548566142460686</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>5.830088265835933</v>
+        <v>5.514086722639313</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 2.081</t>
+          <t>X &gt; 2.086</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-1.009268166063549</v>
+        <v>-1.643892550895409</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-1.344044964413364</v>
+        <v>-1.889799386599279</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-1.466274539760143</v>
+        <v>-3.144493488490859</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-6.126596980255513</v>
+        <v>-7.534364041729461</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-3.129054119469451</v>
+        <v>-5.278276612208543</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.2754212667054006</v>
+        <v>-1.323874651780081</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>2.412089508863701</v>
+        <v>-0.1390800005918322</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>6.187932118164674</v>
+        <v>3.402153402153395</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>3.526716597376684</v>
+        <v>0.9659797477349343</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.05109821863748465</v>
+        <v>-2.394174311586958</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.3251578607994077</v>
+        <v>-2.121939296982625</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-4.007645596702638</v>
+        <v>-6.244675097607775</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-1.076753609504706</v>
+        <v>-3.513413368904693</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>1.404870216751412</v>
+        <v>-1.197544866235248</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>3.449429621873549</v>
+        <v>0.6844033159822658</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>4.04381654381654</v>
+        <v>1.245707334801928</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>6.612602109541768</v>
+        <v>3.705929487179482</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>5.156410054369246</v>
+        <v>2.290994099966603</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>6.723652786644912</v>
+        <v>3.787507609163654</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>6.910498596612939</v>
+        <v>4.002094054222638</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>3.665249725944207</v>
+        <v>0.870546988739342</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>8.994809169940517</v>
+        <v>7.205640877040459</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>5.215229828368521</v>
+        <v>2.321070234113719</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>7.842100277847941</v>
+        <v>7.287136368029373</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 2.155</t>
+          <t>X &gt; 2.161</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-2.916209432272545</v>
+        <v>-1.36871368463234</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-1.801710868303523</v>
+        <v>-1.61462052033621</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-4.689005279653351</v>
+        <v>-5.767865346865463</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-8.300510023733771</v>
+        <v>-7.80954290799253</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-3.521210982214548</v>
+        <v>-3.737274961135348</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-1.86365656082306</v>
+        <v>-0.6817906304995773</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.3309520401479986</v>
+        <v>-2.137571704965893</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>3.868448455397434</v>
+        <v>1.96927255750785</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>2.417398323879297</v>
+        <v>0.626613231897835</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-1.340591979022861</v>
+        <v>-3.110614733909742</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-1.066532336860938</v>
+        <v>-2.838379719305408</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-4.330356367174602</v>
+        <v>-4.585549909070814</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-2.468443807165052</v>
+        <v>-2.759265555933354</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.2955519432540257</v>
+        <v>-0.06632314677822393</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>2.622483272539149</v>
+        <v>2.192698941924952</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>4.709407507914975</v>
+        <v>4.22459119603873</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>7.560564997803169</v>
+        <v>7.061887254901954</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>5.963186980549153</v>
+        <v>3.987826679152121</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>6.179078361473479</v>
+        <v>4.202288906297895</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>6.365924171441506</v>
+        <v>4.416875351356879</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>4.330840690042642</v>
+        <v>2.378842614682029</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>10.22514398236489</v>
+        <v>8.186033033903222</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>6.022006754548428</v>
+        <v>4.017902813299237</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>8.931249128190821</v>
+        <v>8.267528524892136</v>
       </c>
     </row>
   </sheetData>
@@ -5284,2379 +5284,2379 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; 0.07432</t>
+          <t>X &lt; 0.07451</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.9526750704212148</v>
+        <v>-0.3237426079389252</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.6422905784484456</v>
+        <v>0.2887196550696558</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-2.080309627479437</v>
+        <v>-1.180566721500043</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-1.287887302836161</v>
+        <v>-0.7000075469177034</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.5268598590251727</v>
+        <v>1.170357059764072</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.3614427720817588</v>
+        <v>0.03973701769348281</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-1.993606509735542</v>
+        <v>-1.399121818573562</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-2.056764191047755</v>
+        <v>-1.274857712625959</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.9400081919287544</v>
+        <v>-0.2885597042294066</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-2.573138921728685</v>
+        <v>-1.942980298161189</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-2.514133043007618</v>
+        <v>-2.099929832913077</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-3.007936209896478</v>
+        <v>-2.591104062062485</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.6902380616988282</v>
+        <v>-0.2725197846634728</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.1386992147490602</v>
+        <v>0.2499323876936259</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>0.06522645318763409</v>
+        <v>0.6430468230128739</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-1.064524555903866</v>
+        <v>-0.5160792656943443</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-2.060510658398577</v>
+        <v>-1.265120967741936</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-2.380868603599069</v>
+        <v>-1.828112599785257</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-3.673597912329917</v>
+        <v>-2.903972953284651</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-1.331579688568787</v>
+        <v>-0.5388488738170665</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.2370326860574252</v>
+        <v>0.3124125943980474</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.7448440902310978</v>
+        <v>-0.1937844103158568</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-1.766265706042788</v>
+        <v>-0.8122188905547176</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-1.410132516501484</v>
+        <v>-0.7588406434648789</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; 0.1486</t>
+          <t>X &lt; 0.149</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.9526750704212148</v>
+        <v>-0.3237426079389252</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.6422905784484456</v>
+        <v>0.2887196550696558</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-2.080309627479437</v>
+        <v>-1.180566721500043</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-1.287887302836161</v>
+        <v>-0.7000075469177034</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.5268598590251727</v>
+        <v>1.170357059764072</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.3614427720817588</v>
+        <v>0.03973701769348281</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-1.993606509735542</v>
+        <v>-1.399121818573562</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-2.056764191047755</v>
+        <v>-1.274857712625959</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.9400081919287544</v>
+        <v>-0.2885597042294066</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-2.573138921728685</v>
+        <v>-1.942980298161189</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-2.514133043007618</v>
+        <v>-2.099929832913077</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-3.007936209896478</v>
+        <v>-2.591104062062485</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.6902380616988282</v>
+        <v>-0.2725197846634728</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.1386992147490602</v>
+        <v>0.2499323876936259</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>0.06522645318763409</v>
+        <v>0.6430468230128739</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-1.064524555903866</v>
+        <v>-0.5160792656943443</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-2.060510658398577</v>
+        <v>-1.265120967741936</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-2.380868603599069</v>
+        <v>-1.828112599785257</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-3.673597912329917</v>
+        <v>-2.903972953284651</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-1.331579688568787</v>
+        <v>-0.5388488738170665</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.2370326860574252</v>
+        <v>0.3124125943980474</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.7448440902310978</v>
+        <v>-0.1937844103158568</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-1.766265706042788</v>
+        <v>-0.8122188905547176</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-1.410132516501484</v>
+        <v>-0.7588406434648789</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; 0.223</t>
+          <t>X &lt; 0.2235</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.9526750704212148</v>
+        <v>-0.3237426079389252</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.6422905784484456</v>
+        <v>0.2887196550696558</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-2.080309627479437</v>
+        <v>-1.180566721500043</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-1.287887302836161</v>
+        <v>-0.7000075469177034</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.5268598590251727</v>
+        <v>1.170357059764072</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.3614427720817588</v>
+        <v>0.03973701769348281</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-1.993606509735542</v>
+        <v>-1.399121818573562</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-2.056764191047755</v>
+        <v>-1.274857712625959</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.9400081919287544</v>
+        <v>-0.2885597042294066</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-2.573138921728685</v>
+        <v>-1.942980298161189</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-2.514133043007618</v>
+        <v>-2.099929832913077</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-3.007936209896478</v>
+        <v>-2.591104062062485</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.6902380616988282</v>
+        <v>-0.2725197846634728</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.1386992147490602</v>
+        <v>0.2499323876936259</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.06522645318763409</v>
+        <v>0.6430468230128739</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-1.064524555903866</v>
+        <v>-0.5160792656943443</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-2.060510658398577</v>
+        <v>-1.265120967741936</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-2.380868603599069</v>
+        <v>-1.828112599785257</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-3.673597912329917</v>
+        <v>-2.903972953284651</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-1.331579688568787</v>
+        <v>-0.5388488738170665</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.2370326860574252</v>
+        <v>0.3124125943980474</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.7448440902310978</v>
+        <v>-0.1937844103158568</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-1.766265706042788</v>
+        <v>-0.8122188905547176</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-1.410132516501484</v>
+        <v>-0.7588406434648789</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; 0.2973</t>
+          <t>X &lt; 0.2981</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.9526750704212148</v>
+        <v>-0.3237426079389252</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.6422905784484456</v>
+        <v>0.2887196550696558</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-2.080309627479437</v>
+        <v>-1.180566721500043</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-1.287887302836161</v>
+        <v>-0.7000075469177034</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.5268598590251727</v>
+        <v>1.170357059764072</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.3614427720817588</v>
+        <v>0.03973701769348281</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-1.993606509735542</v>
+        <v>-1.399121818573562</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-2.056764191047755</v>
+        <v>-1.274857712625959</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.9400081919287544</v>
+        <v>-0.2885597042294066</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-2.573138921728685</v>
+        <v>-1.942980298161189</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-2.514133043007618</v>
+        <v>-2.099929832913077</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-3.007936209896478</v>
+        <v>-2.591104062062485</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.6902380616988282</v>
+        <v>-0.2725197846634728</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.1386992147490602</v>
+        <v>0.2499323876936259</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>0.06522645318763409</v>
+        <v>0.6430468230128739</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-1.064524555903866</v>
+        <v>-0.5160792656943443</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-2.060510658398577</v>
+        <v>-1.265120967741936</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-2.380868603599069</v>
+        <v>-1.828112599785257</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-3.673597912329917</v>
+        <v>-2.903972953284651</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-1.331579688568787</v>
+        <v>-0.5388488738170665</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.2370326860574252</v>
+        <v>0.3124125943980474</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.7448440902310978</v>
+        <v>-0.1937844103158568</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-1.766265706042788</v>
+        <v>-0.8122188905547176</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-1.410132516501484</v>
+        <v>-0.7588406434648789</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; 0.3716</t>
+          <t>X &lt; 0.3726</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.9526750704212148</v>
+        <v>-0.3237426079389252</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.6422905784484456</v>
+        <v>0.2887196550696558</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-2.080309627479437</v>
+        <v>-1.180566721500043</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-1.287887302836161</v>
+        <v>-0.7000075469177034</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.5268598590251727</v>
+        <v>1.170357059764072</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.3614427720817588</v>
+        <v>0.03973701769348281</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.993606509735542</v>
+        <v>-1.399121818573562</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-2.056764191047755</v>
+        <v>-1.274857712625959</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.9400081919287544</v>
+        <v>-0.2885597042294066</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-2.573138921728685</v>
+        <v>-1.942980298161189</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-2.514133043007618</v>
+        <v>-2.099929832913077</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-3.007936209896478</v>
+        <v>-2.591104062062485</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.6902380616988282</v>
+        <v>-0.2725197846634728</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.1386992147490602</v>
+        <v>0.2499323876936259</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.06522645318763409</v>
+        <v>0.6430468230128739</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-1.064524555903866</v>
+        <v>-0.5160792656943443</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-2.060510658398577</v>
+        <v>-1.265120967741936</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-2.380868603599069</v>
+        <v>-1.828112599785257</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-3.673597912329917</v>
+        <v>-2.903972953284651</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-1.331579688568787</v>
+        <v>-0.5388488738170665</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.2370326860574252</v>
+        <v>0.3124125943980474</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.7448440902310978</v>
+        <v>-0.1937844103158568</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-1.766265706042788</v>
+        <v>-0.8122188905547176</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-1.410132516501484</v>
+        <v>-0.7588406434648789</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; 0.4459</t>
+          <t>X &lt; 0.4471</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.9526750704212148</v>
+        <v>-0.3237426079389252</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.6422905784484456</v>
+        <v>0.2887196550696558</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-2.080309627479437</v>
+        <v>-1.180566721500043</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.287887302836161</v>
+        <v>-0.7000075469177034</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.5268598590251727</v>
+        <v>1.170357059764072</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.3614427720817588</v>
+        <v>0.03973701769348281</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.993606509735542</v>
+        <v>-1.399121818573562</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-2.056764191047755</v>
+        <v>-1.274857712625959</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.9400081919287544</v>
+        <v>-0.2885597042294066</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.573138921728685</v>
+        <v>-1.942980298161189</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.514133043007618</v>
+        <v>-2.099929832913077</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-3.007936209896478</v>
+        <v>-2.591104062062485</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.6902380616988282</v>
+        <v>-0.2725197846634728</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.1386992147490602</v>
+        <v>0.2499323876936259</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.06522645318763409</v>
+        <v>0.6430468230128739</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-1.064524555903866</v>
+        <v>-0.5160792656943443</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-2.060510658398577</v>
+        <v>-1.265120967741936</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-2.380868603599069</v>
+        <v>-1.828112599785257</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-3.673597912329917</v>
+        <v>-2.903972953284651</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-1.331579688568787</v>
+        <v>-0.5388488738170665</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.2370326860574252</v>
+        <v>0.3124125943980474</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.7448440902310978</v>
+        <v>-0.1937844103158568</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-1.766265706042788</v>
+        <v>-0.8122188905547176</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-1.410132516501484</v>
+        <v>-0.7588406434648789</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; 0.5202</t>
+          <t>X &lt; 0.5216</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.9526750704212148</v>
+        <v>-0.3237426079389252</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.6422905784484456</v>
+        <v>0.2887196550696558</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-2.080309627479437</v>
+        <v>-1.180566721500043</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.287887302836161</v>
+        <v>-0.7000075469177034</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.5268598590251727</v>
+        <v>1.170357059764072</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.3614427720817588</v>
+        <v>0.03973701769348281</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.993606509735542</v>
+        <v>-1.399121818573562</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-2.056764191047755</v>
+        <v>-1.274857712625959</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.9400081919287544</v>
+        <v>-0.2885597042294066</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-2.573138921728685</v>
+        <v>-1.942980298161189</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-2.514133043007618</v>
+        <v>-2.099929832913077</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-3.007936209896478</v>
+        <v>-2.591104062062485</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.6902380616988282</v>
+        <v>-0.2725197846634728</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.1386992147490602</v>
+        <v>0.2499323876936259</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.06522645318763409</v>
+        <v>0.6430468230128739</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-1.064524555903866</v>
+        <v>-0.5160792656943443</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-2.060510658398577</v>
+        <v>-1.265120967741936</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-2.380868603599069</v>
+        <v>-1.828112599785257</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-3.673597912329917</v>
+        <v>-2.903972953284651</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-1.331579688568787</v>
+        <v>-0.5388488738170665</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.2370326860574252</v>
+        <v>0.3124125943980474</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.7448440902310978</v>
+        <v>-0.1937844103158568</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-1.766265706042788</v>
+        <v>-0.8122188905547176</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-1.410132516501484</v>
+        <v>-0.7588406434648789</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; 0.5945</t>
+          <t>X &lt; 0.5961</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.7746050752154048</v>
+        <v>-0.2931508371252747</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.2601249733529087</v>
+        <v>0.5091603565209653</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.910458247436978</v>
+        <v>-0.9551773512406427</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.137212691508168</v>
+        <v>-0.4993615206987627</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.4378248614222642</v>
+        <v>1.111872792032088</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.4367800777457518</v>
+        <v>-0.1986988430599652</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-2.270299886901491</v>
+        <v>-1.622711672902746</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.123882881548411</v>
+        <v>-1.298701298701303</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.020824574368312</v>
+        <v>-0.3321979655371194</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.64299715061712</v>
+        <v>-1.757180278366519</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.581251733508275</v>
+        <v>-1.694588869632199</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-3.072315362009348</v>
+        <v>-2.180814429973516</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.5861356029631324</v>
+        <v>0.2682347523660695</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.04423846639982543</v>
+        <v>0.7740129876755546</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.1486820658068524</v>
+        <v>1.142278773857718</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.9590586718246286</v>
+        <v>0.0229105237698235</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-1.944039638589338</v>
+        <v>-0.7112219887955149</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-2.474412257304138</v>
+        <v>-1.47435819479746</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-3.747882578507465</v>
+        <v>-2.730484202945803</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-1.433377194071362</v>
+        <v>-0.4150574217523584</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.3599908664605564</v>
+        <v>0.6141367323290865</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.8622760602790436</v>
+        <v>0.1179215787948564</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-1.867119045025134</v>
+        <v>-0.4805491990846704</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-1.516512065839024</v>
+        <v>-0.6426881933741342</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; 0.6689</t>
+          <t>X &lt; 0.6706</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>488</v>
+        <v>499</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.191867521595235</v>
+        <v>-0.6484151512642953</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.3021545240266761</v>
+        <v>0.7024844002573829</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.53609194040461</v>
+        <v>-0.5522097016341974</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.6163928986228626</v>
+        <v>-0.1466079084264464</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.088632955360481</v>
+        <v>1.573841935506152</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.05110934553948709</v>
+        <v>0.1339691542786881</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.741247501616172</v>
+        <v>-1.259915253163612</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.815377313716183</v>
+        <v>-1.165634099765846</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.7534819685361711</v>
+        <v>-0.2393019964689529</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.954969073144099</v>
+        <v>-2.232958282107461</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.680909430982176</v>
+        <v>-1.960723267503127</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.755577201777108</v>
+        <v>-1.838103625168038</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.6134331461842351</v>
+        <v>0.2406170318322935</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.1012371175767797</v>
+        <v>0.7101474414570603</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.0586154948631048</v>
+        <v>1.027993059572012</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.9829894032347966</v>
+        <v>-0.01070292160832764</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-2.548399382748059</v>
+        <v>-1.314583333333339</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-2.857739064074359</v>
+        <v>-1.847467438494938</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-4.073340525685822</v>
+        <v>-2.83300521134916</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-1.84150494066666</v>
+        <v>-0.6184187662901834</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.6269523121594673</v>
+        <v>0.1331748084813924</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-1.112634339142339</v>
+        <v>-0.1423885150770943</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-2.272585856168483</v>
+        <v>-0.9007580378147537</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-2.143500076604873</v>
+        <v>-1.062897032104217</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; 0.7432</t>
+          <t>X &lt; 0.7451</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.603810076394929</v>
+        <v>-1.44790905962244</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.08673502289289559</v>
+        <v>0.491976454400465</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.9691985163683299</v>
+        <v>-0.3984189225366421</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.5400696864111509</v>
+        <v>1.012821865904677</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>2.056131065715725</v>
+        <v>2.55875735057765</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.9468009555168138</v>
+        <v>1.076346694280652</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.380703283929094</v>
+        <v>-0.08303404290652594</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.6589147286821699</v>
+        <v>-0.02365576136068626</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.493683564343641</v>
+        <v>1.015019960709587</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.945898778359506</v>
+        <v>-1.238226434327615</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.301468765827224</v>
+        <v>-0.6016926947688077</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.024662613719656</v>
+        <v>-0.1496771993311867</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.8151382823871884</v>
+        <v>1.649820482853748</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.07643417402965</v>
+        <v>1.876570799121303</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>1.716992175150395</v>
+        <v>2.836752183659598</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.08503401360543705</v>
+        <v>1.208275180581452</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-1.904170692945321</v>
+        <v>-0.5379409975669063</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-2.009011396766503</v>
+        <v>-0.8533068545533382</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-3.277350071500791</v>
+        <v>-1.916216890181275</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-1.420745448916819</v>
+        <v>-0.05929467869894012</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.368709884223577</v>
+        <v>0.7603890175210424</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.4445558456326779</v>
+        <v>0.6852264955657574</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-2.028817192630179</v>
+        <v>-0.5336618710754308</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-1.918775839905493</v>
+        <v>-0.6958008653648946</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; 0.8175</t>
+          <t>X &lt; 0.8197</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>689</v>
+        <v>710</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.253003408656284</v>
+        <v>-0.6674514125425759</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.1406022041117438</v>
+        <v>0.3489138415151274</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.144467852274424</v>
+        <v>-0.2045179882866961</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.7474985334926743</v>
+        <v>1.306866629174372</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.569450463260893</v>
+        <v>2.433833033254558</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.177545448200519</v>
+        <v>1.608999458326977</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.6074278377158748</v>
+        <v>0.1126551740044945</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.740921482179516</v>
+        <v>0.0882396394317837</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.8924615029189766</v>
+        <v>1.758945547713367</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.1195458268824865</v>
+        <v>1.243398961329923</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.9724766702021554</v>
+        <v>1.936391339188127</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.8384450670435939</v>
+        <v>2.080566747970678</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.886050004529004</v>
+        <v>3.069461446789191</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>2.188262304491317</v>
+        <v>3.329248565052573</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>1.675046543142649</v>
+        <v>3.068442497774264</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.3853754940711411</v>
+        <v>1.803903819964702</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.6181068602976296</v>
+        <v>0.9977762172284628</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-1.30265770904635</v>
+        <v>0.1626449210556231</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-2.246186617977095</v>
+        <v>-0.746488357416581</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-1.044848054385881</v>
+        <v>0.310794716855888</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>0.2388189410228634</v>
+        <v>1.373630403215166</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.1273027823601112</v>
+        <v>0.8765269529898276</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-1.594482641721314</v>
+        <v>-0.1456613465419139</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-1.525177013957645</v>
+        <v>-0.08375565074996416</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; 0.8918</t>
+          <t>X &lt; 0.8942</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1020</v>
+        <v>1051</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.1774324792856206</v>
+        <v>-0.03219029547302199</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.3170873264159226</v>
+        <v>0.1962861705308754</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.0009911855286972582</v>
+        <v>0.8391252754704226</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.516840882694531</v>
+        <v>0.2467230766621995</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.3648264771930272</v>
+        <v>0.5404248986122084</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.543713949632235</v>
+        <v>-0.8206680608546151</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-2.510784584742098</v>
+        <v>-1.710626733428889</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.247456395348834</v>
+        <v>-1.256533894105054</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.2528442134341304</v>
+        <v>0.5791749017270504</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.2030096608715155</v>
+        <v>0.9216433306063934</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.414701416096399</v>
+        <v>2.142644948626284</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.8424099382844048</v>
+        <v>1.581433013130322</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.480500317612233</v>
+        <v>2.269197442169116</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.122952647860288</v>
+        <v>1.793908125217747</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>1.738070858604893</v>
+        <v>2.536255167834121</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.7653666933784464</v>
+        <v>1.578091000518931</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.2396767846086121</v>
+        <v>1.189310303893635</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>0.0368928878393362</v>
+        <v>0.7715259138317521</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.7266476607172407</v>
+        <v>0.1312872862766596</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.3439154648530263</v>
+        <v>0.4408404929690732</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>0.3478146438032468</v>
+        <v>1.070410496587634</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>0.5660863294529648</v>
+        <v>1.185362043073425</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.7280664090453683</v>
+        <v>0.1932550834848783</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>0.0784542789078273</v>
+        <v>0.9439711285748942</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 0.9661</t>
+          <t>X &lt; 0.9687</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1428</v>
+        <v>1460</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.339591883306447</v>
+        <v>-1.122722160966774</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.628343577053748</v>
+        <v>-0.1416351316399656</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.02568758312028052</v>
+        <v>0.6184367271998141</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.0596513735609534</v>
+        <v>0.3370663812195147</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.3257068391347175</v>
+        <v>0.2662863981167689</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.975560736719352</v>
+        <v>-0.464152009537024</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.538304399689203</v>
+        <v>-0.9861964791076261</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.987130592836628</v>
+        <v>-1.4276356938473</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.06148430415289852</v>
+        <v>0.4067778574750278</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.6720403898589851</v>
+        <v>0.9759140755662656</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.847378194340493</v>
+        <v>1.08318890814558</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.1493415791524626</v>
+        <v>0.4650768990294694</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.563565955343158</v>
+        <v>0.9212230329448161</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.4541992660804581</v>
+        <v>0.7820544817851669</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>0.5652867377306663</v>
+        <v>1.125190598874816</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>0.2505827505827511</v>
+        <v>0.8662622185147129</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.1166656136052779</v>
+        <v>0.8307345067213419</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>0.123595574388915</v>
+        <v>0.8345558014230434</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.4302821139659869</v>
+        <v>0.2971383293206884</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.1034782914017285</v>
+        <v>0.5800774743113237</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>0.5158818706940025</v>
+        <v>1.147652464203233</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>0.4400359092849015</v>
+        <v>0.9770303363149324</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.6860496023226759</v>
+        <v>0.193970776418773</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-0.341713788319062</v>
+        <v>0.3464970986229901</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 1.04</t>
+          <t>X &lt; 1.043</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1891</v>
+        <v>1926</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.219794481853022</v>
+        <v>-0.9653071404817268</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.2387818065186238</v>
+        <v>0.1052261061184794</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.0600412497135494</v>
+        <v>0.3747289906406976</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.7681398618497539</v>
+        <v>0.9983401922745827</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.06392833667089093</v>
+        <v>0.5679033738066224</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.3280528456527705</v>
+        <v>0.105322266330262</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.1000015295431211</v>
+        <v>0.2911385504320876</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.9274771299459843</v>
+        <v>-0.5526039616948779</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.2198552336432797</v>
+        <v>0.6083827992288988</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.636351543616847</v>
+        <v>0.9789125498719926</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.3087735270718994</v>
+        <v>0.7643333410997286</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.07540550210092078</v>
+        <v>0.4360450784588394</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.4355916297777966</v>
+        <v>0.8723422060959649</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.140472908050306</v>
+        <v>0.6031634787048716</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>0.3580796967505364</v>
+        <v>0.9352394363836041</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.2136803390101534</v>
+        <v>0.8236656084123695</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.290844996227932</v>
+        <v>0.9061313222855105</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>0.2704258653227427</v>
+        <v>0.856159504510245</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.2000607896557725</v>
+        <v>0.500673545127519</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.1979782621285153</v>
+        <v>0.8188869331916919</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>0.5320848653625561</v>
+        <v>1.111803917399065</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>0.06531942649728251</v>
+        <v>0.7049493141082408</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.7701424360735132</v>
+        <v>0.04571196498274332</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.4446634822103732</v>
+        <v>0.0181851738445431</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 1.115</t>
+          <t>X &lt; 1.118</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2280</v>
+        <v>2301</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.2114019408675318</v>
+        <v>-0.1546250017402926</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.3277427409648368</v>
+        <v>-0.1184126657142954</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.1930226025777344</v>
+        <v>-0.01083025749870359</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.2735777685430918</v>
+        <v>0.5009302046300661</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.1495871033051941</v>
+        <v>0.2496420861775732</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.486867313013839</v>
+        <v>-0.1554649476859922</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.4287592035446437</v>
+        <v>-0.08586905243925003</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.7259310456984807</v>
+        <v>-0.3663675809004516</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.2036746330145434</v>
+        <v>0.3052601125453833</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.01032723339776709</v>
+        <v>0.4862785688659201</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.2151462228117609</v>
+        <v>0.3938573071639127</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.1001948388581795</v>
+        <v>0.5503632695397371</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.348466267044131</v>
+        <v>0.3449557774679164</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.6313235262256995</v>
+        <v>0.03562404457665025</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.3005112121303242</v>
+        <v>0.4193237921251054</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-0.1439526614657893</v>
+        <v>0.5905107758342396</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.1161757357073441</v>
+        <v>0.8593975860075176</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.1377145564439317</v>
+        <v>0.5789967697480094</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-0.272239294661091</v>
+        <v>0.4897713613189509</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.2167995293711229</v>
+        <v>0.5742059625601499</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-0.1199552862546724</v>
+        <v>0.6835811767735294</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.169616105839431</v>
+        <v>0.5476585351675496</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.5089072855099417</v>
+        <v>0.3395157330109981</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-0.5149409739301589</v>
+        <v>0.1163410616408598</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 1.189</t>
+          <t>X &lt; 1.192</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2503</v>
+        <v>2526</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.3022143630345155</v>
+        <v>-0.1438055100359463</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.6157829575074274</v>
+        <v>-0.2901058908584986</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.2645375930195328</v>
+        <v>0.1278301400352078</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.01654417282599496</v>
+        <v>0.4225920080270313</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.2397234368982097</v>
+        <v>0.09038617877875765</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.410610133504612</v>
+        <v>-0.1068714785053331</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.3078073263412904</v>
+        <v>0.003201959871944382</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.4043403452294996</v>
+        <v>-0.08260331094977147</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.114473805658946</v>
+        <v>0.5009268801614013</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.3194326095345588</v>
+        <v>0.7124511354640148</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.01959752339194409</v>
+        <v>0.4558074865189852</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.1963073767622703</v>
+        <v>0.3597089515712284</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.363674939436784</v>
+        <v>0.2700534271803932</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.4417971677645767</v>
+        <v>0.1634018793268837</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-0.2394525644179595</v>
+        <v>0.4122077399192889</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-0.05980861244019309</v>
+        <v>0.6024040661532126</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-0.01047489646303035</v>
+        <v>0.6405509478672897</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-0.1314396468882819</v>
+        <v>0.4522559909795802</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>0.004643274339308334</v>
+        <v>0.6903149467536025</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.04793629478283634</v>
+        <v>0.6282215499153523</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>0.03197573338877646</v>
+        <v>0.7564854867774784</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.1397647010550784</v>
+        <v>0.4677716787282336</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-0.2247149087008253</v>
+        <v>0.4976858622528937</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.3567097987088417</v>
+        <v>0.1612456316873363</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 1.263</t>
+          <t>X &lt; 1.267</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2663</v>
+        <v>2686</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.3747030298186829</v>
+        <v>-0.3078762660033902</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.4655417609229318</v>
+        <v>-0.2382377058263074</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.02154568319171091</v>
+        <v>0.3026842839794881</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.05636911324019422</v>
+        <v>0.3229193582836558</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.2053833437254653</v>
+        <v>0.1421255829465551</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.2425486481024919</v>
+        <v>0.0769192407772934</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.4541686058068137</v>
+        <v>-0.1257895763425054</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.4870163729273074</v>
+        <v>-0.187590187590196</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.1465755288302475</v>
+        <v>0.2206894692842312</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.1112144095948011</v>
+        <v>0.4835508789625393</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.1539300528434779</v>
+        <v>0.2581981777043509</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.2988863323878164</v>
+        <v>0.1513151633676486</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.4119473891429308</v>
+        <v>0.1120907017032309</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.4239046659156855</v>
+        <v>0.07118640249602493</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.5732564861738396</v>
+        <v>-0.0322890488169989</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-0.480932924753148</v>
+        <v>0.06839102566237187</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-0.5552813977947153</v>
+        <v>-0.05069031698860726</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-0.4505837460278528</v>
+        <v>0.024178789673023</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-0.5124359455068017</v>
+        <v>0.03762675891105971</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.588057327139822</v>
+        <v>-0.008009844357090401</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-0.4334100741409372</v>
+        <v>0.1901873087515469</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-0.6745787921303759</v>
+        <v>-0.1976329324833372</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-0.6781635650248816</v>
+        <v>-0.08080775391982797</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-0.7694027009100139</v>
+        <v>-0.3326203954355051</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 1.338</t>
+          <t>X &lt; 1.341</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2797</v>
+        <v>2820</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.4425528703616024</v>
+        <v>-0.3548845653772474</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.4384749604842426</v>
+        <v>-0.159217143800376</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.0628861999269148</v>
+        <v>0.4026658838181021</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.02560785615985139</v>
+        <v>0.4292502483207059</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.02568759505029306</v>
+        <v>0.3498349230759885</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.01653079728861684</v>
+        <v>0.2245815802204589</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.1128038055032974</v>
+        <v>0.1349669401217781</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.3707610467184494</v>
+        <v>-0.114666169712045</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.0824538292704915</v>
+        <v>0.3862735379546081</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.4335561482652253</v>
+        <v>0.7403324246146923</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.2654828011243495</v>
+        <v>0.6092692095702859</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.2211646171449857</v>
+        <v>0.6358177899522559</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.0826173285853784</v>
+        <v>0.4043178986498859</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.1400817202176299</v>
+        <v>0.3890445782545271</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-0.1710357632977164</v>
+        <v>0.3997045164319744</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-0.2328924047896948</v>
+        <v>0.3101318856078024</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.4527043671096891</v>
+        <v>0.1210854564755763</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.2152356813021896</v>
+        <v>0.2923555703546228</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.3708211946551998</v>
+        <v>0.2446151852513978</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-0.4338861308492596</v>
+        <v>0.1759155113302171</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.2411209304264403</v>
+        <v>0.3732582342773725</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-0.5100332931013085</v>
+        <v>0.0003491217841471439</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-0.3930231708780454</v>
+        <v>0.1941648814019175</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-0.5906800176423985</v>
+        <v>-0.1596721426089118</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 1.412</t>
+          <t>X &lt; 1.416</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2875</v>
+        <v>2904</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.3052093671478318</v>
+        <v>-0.3096469128523012</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.3103403709795671</v>
+        <v>-0.05821186634697995</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.1034791422657477</v>
+        <v>0.4514659323767987</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.08232726740966001</v>
+        <v>0.4945071217871018</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.2534632051376136</v>
+        <v>0.1354032937762497</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.1854558687815313</v>
+        <v>0.1210453615763214</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.0577505734331325</v>
+        <v>0.25093765561288</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.3854637075675882</v>
+        <v>-0.03451730662149544</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.02199996939135218</v>
+        <v>0.3871448013991383</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.4119890713883976</v>
+        <v>0.7766603407291797</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.2212077568493029</v>
+        <v>0.6229259007127581</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.1012119610284046</v>
+        <v>0.5377897493732107</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.05141284412927405</v>
+        <v>0.4524103292457013</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.0786174317847852</v>
+        <v>0.3961069333897811</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-0.1612049460971221</v>
+        <v>0.3524436090225578</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-0.3093916261855156</v>
+        <v>0.2129315682577015</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.4574842906383481</v>
+        <v>0.06067439862543011</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.2987325882733955</v>
+        <v>0.2231410180193265</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.4095484938297247</v>
+        <v>0.2173386676054392</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.4311083802840656</v>
+        <v>0.1568219489780489</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-0.3277634401057909</v>
+        <v>0.2632595393466275</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-0.4871962974664044</v>
+        <v>0.002153838728922608</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-0.5049896957453015</v>
+        <v>0.05971712938711704</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-0.6298151158065863</v>
+        <v>-0.219750684312217</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 1.486</t>
+          <t>X &lt; 1.49</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2974</v>
+        <v>3004</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.3320235840202059</v>
+        <v>-0.2842740982726824</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.2812073286991961</v>
+        <v>-0.1154693679177115</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.07130687196314511</v>
+        <v>0.3357859059589643</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.1610284378046885</v>
+        <v>0.4901979500552684</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.1078724026355644</v>
+        <v>0.2001071262244167</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.3035243112018975</v>
+        <v>0.02580522377599692</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.1052488398563867</v>
+        <v>0.1913061860381404</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.3978705519753447</v>
+        <v>-0.06167898812034167</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.2034112539430026</v>
+        <v>0.151365128015911</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.2149258104623968</v>
+        <v>0.5678062366004824</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.02750636121154315</v>
+        <v>0.3617958733197</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.01470785594571566</v>
+        <v>0.4692922003011333</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.20362847364499</v>
+        <v>0.2833980921403452</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.2373184016356618</v>
+        <v>0.2538580289114307</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.2049289620624961</v>
+        <v>0.2885508284963123</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-0.362014983786203</v>
+        <v>0.172292760889178</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.442540281171091</v>
+        <v>0.08807447397563095</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.2925434308380233</v>
+        <v>0.2075009895542479</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-0.3924962704040738</v>
+        <v>0.2090160652465869</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-0.4407075457281948</v>
+        <v>0.1244003826459874</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.3252540462189515</v>
+        <v>0.2749282188605164</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-0.4819054479031308</v>
+        <v>0.05327893425936026</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-0.4899711709501275</v>
+        <v>0.1170512913260566</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.545911136390778</v>
+        <v>-0.09191378731904365</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 1.561</t>
+          <t>X &lt; 1.565</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3073</v>
+        <v>3097</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.1630082263404091</v>
+        <v>-0.1109397492780175</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.2215786043384185</v>
+        <v>0.01319887121922392</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.008823856927598683</v>
+        <v>0.2841150814056377</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.07282030689243157</v>
+        <v>0.4157345014568392</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.1334784207535833</v>
+        <v>0.2224022330228692</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.3168720439074804</v>
+        <v>-0.03813365359304299</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.1820849765024946</v>
+        <v>0.09806243308239715</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.409481622106199</v>
+        <v>-0.1244142586898818</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.2199334875754175</v>
+        <v>0.08601138704678135</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.09534019156665607</v>
+        <v>0.4011178279674681</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.03157634153696165</v>
+        <v>0.3704343529472922</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.03106713484174151</v>
+        <v>0.4018680236860703</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.2163245784626326</v>
+        <v>0.2386903831990637</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.3209308601204057</v>
+        <v>0.1381487288725793</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-0.3107570497055221</v>
+        <v>0.1833053583485764</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.4112554112554108</v>
+        <v>0.0875257418377231</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.4610353473369955</v>
+        <v>0.03490120274913977</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.3842182932766462</v>
+        <v>0.08221351542062649</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.4415397051644092</v>
+        <v>0.09014114583974475</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-0.4821882078385613</v>
+        <v>0.0335644649255542</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-0.3879256861388711</v>
+        <v>0.1625238291032787</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-0.5419959278401834</v>
+        <v>-0.08703417942935943</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-0.4759200072185337</v>
+        <v>0.04665001263087731</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-0.5324962516460872</v>
+        <v>-0.1609316547883992</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 1.635</t>
+          <t>X &lt; 1.639</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3140</v>
+        <v>3168</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.09654331596361487</v>
+        <v>-0.06300290365918926</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.1611256528390825</v>
+        <v>0.05279600658377603</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.1278389897888701</v>
+        <v>0.4147397119602019</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.04819719327203842</v>
+        <v>0.4045332983348047</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.1609308346900562</v>
+        <v>0.2407266218772861</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.3679141396860928</v>
+        <v>-0.08706444571128458</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.189593580624269</v>
+        <v>0.0911659439398278</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.4181035753234781</v>
+        <v>-0.1017442914427846</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.2951877158113163</v>
+        <v>0.04401449966224646</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.09137311623641864</v>
+        <v>0.3971680146390852</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.03500091031895636</v>
+        <v>0.4046811013762124</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.1235795370605715</v>
+        <v>0.5235880857497506</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.06077412637193191</v>
+        <v>0.3391930788574626</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.1043532924721049</v>
+        <v>0.2668497699655603</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.1720546760159536</v>
+        <v>0.232840399830117</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.2257325478418224</v>
+        <v>0.2147378844370067</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.245495263331577</v>
+        <v>0.1925032808398939</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.2043225790906646</v>
+        <v>0.2358343888522683</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.2556794868050005</v>
+        <v>0.2169159988619924</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.2726387391961538</v>
+        <v>0.1664488251347933</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.2237012676838432</v>
+        <v>0.2798573252019949</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.3442243256811395</v>
+        <v>0.09733383182490485</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.3054771250031934</v>
+        <v>0.2019838928752833</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.2987156973629368</v>
+        <v>0.09016667105968423</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 1.709</t>
+          <t>X &lt; 1.714</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3204</v>
+        <v>3227</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.04283222509450013</v>
+        <v>-0.01846544771662906</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.1437902164668543</v>
+        <v>0.05998860367321868</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.04880272509660699</v>
+        <v>0.3617615551131763</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.04341883003824876</v>
+        <v>0.3409567035695247</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.2240261865085671</v>
+        <v>0.175098590147563</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.4232014591922137</v>
+        <v>-0.1130706748177417</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.2948086342343785</v>
+        <v>0.01663152996557216</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.5243391593239934</v>
+        <v>-0.2091751397949366</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.4341408117565848</v>
+        <v>-0.06377396554745474</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.1017581803345067</v>
+        <v>0.2375711927287369</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.1516167067429564</v>
+        <v>0.2189913772813838</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.07040611841838995</v>
+        <v>0.3306370041013622</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.2424044858865244</v>
+        <v>0.2218774880662124</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.2584608180793211</v>
+        <v>0.2080776237245985</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.3379712243508308</v>
+        <v>0.1622328617969728</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.4099211290992102</v>
+        <v>0.09285194701609356</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.4320164735383472</v>
+        <v>0.06909013605442027</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.3315077699971809</v>
+        <v>0.1400982899306698</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.3775743363958597</v>
+        <v>0.1563512242944043</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.390505649528464</v>
+        <v>0.1107053438924268</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.353408782892032</v>
+        <v>0.2116599521433287</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.4106973971381009</v>
+        <v>0.06204636893681936</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.3984649896944745</v>
+        <v>0.1382468616992654</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.3309604233026491</v>
+        <v>0.05647837815229906</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 1.784</t>
+          <t>X &lt; 1.788</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3244</v>
+        <v>3268</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.04207222828648582</v>
+        <v>-0.01679086184920209</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.007219225473114932</v>
+        <v>0.2096421734917087</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.1180763159264302</v>
+        <v>0.4008112637343402</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.03526690693025358</v>
+        <v>0.3728885413269154</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.08593129093890184</v>
+        <v>0.2665356715884641</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.3109931771623238</v>
+        <v>-0.01605044123348165</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.2243095396788632</v>
+        <v>0.07166815536179882</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.3930660579255161</v>
+        <v>-0.09420813318499199</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.3034252965884718</v>
+        <v>0.05100985621920984</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.1073475199187541</v>
+        <v>0.2168039849489247</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.1839327465411174</v>
+        <v>0.1713734047421482</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.04572913478617835</v>
+        <v>0.3391272788775268</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.2908525010229539</v>
+        <v>0.1567956535458634</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.2479811595172947</v>
+        <v>0.2010565323661595</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.3038625574868732</v>
+        <v>0.1777641917050587</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.39835625628983</v>
+        <v>0.05523114432573806</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.4218238882801018</v>
+        <v>0.0304548346055995</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.3546086566494679</v>
+        <v>0.06835418642869939</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.4282359441911794</v>
+        <v>0.05651510640213786</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.4387225457116486</v>
+        <v>0.01409957111813043</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.3471858694910779</v>
+        <v>0.1677900493575208</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.4663155407220856</v>
+        <v>-0.04206554497787351</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.4200510611496568</v>
+        <v>0.0667934616356618</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.3543205572905208</v>
+        <v>-0.01600520683802387</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 1.858</t>
+          <t>X &lt; 1.863</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3275</v>
+        <v>3300</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.06075002605332713</v>
+        <v>-0.02065201408289852</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.07577565685006959</v>
+        <v>0.1108943193532497</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.02047968642462905</v>
+        <v>0.2880976354987652</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.02281085454557541</v>
+        <v>0.3450872189446059</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.1611423875127826</v>
+        <v>0.2069554553020083</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.2000871233275205</v>
+        <v>0.07933016574986596</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.1822423685787555</v>
+        <v>0.09823669738209162</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.32163122822638</v>
+        <v>-0.03881656475143558</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.2628176176894428</v>
+        <v>0.07608532842875348</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.1062649822039745</v>
+        <v>0.2024244226098375</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.118716670666366</v>
+        <v>0.2204260547398036</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.01484841863013031</v>
+        <v>0.3537084029496356</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.1465172258294913</v>
+        <v>0.2529752812048827</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.1669756016697477</v>
+        <v>0.2340145109434673</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.1980668392648042</v>
+        <v>0.2345811526514936</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.2860235003092129</v>
+        <v>0.1489101376419768</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.3409693778505556</v>
+        <v>0.09315782179215404</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.2753551457592565</v>
+        <v>0.1294230636224256</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.2852463564005703</v>
+        <v>0.1803079505267817</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.324320852296168</v>
+        <v>0.1101526622812514</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.2692521951348823</v>
+        <v>0.2266102412603601</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.4184643415936051</v>
+        <v>-0.01220689198839864</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.33950072636204</v>
+        <v>0.1282615281271831</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.275085610330315</v>
+        <v>0.04471212560513749</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 1.932</t>
+          <t>X &lt; 1.937</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3293</v>
+        <v>3320</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.1103703481935909</v>
+        <v>-0.1015734665905512</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.09696408684969526</v>
+        <v>0.08755144067520604</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.09963329897702522</v>
+        <v>0.1663531726173062</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.07102464561341293</v>
+        <v>0.2493656431227436</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.1953986276744288</v>
+        <v>0.1702979150988</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.2935481549229308</v>
+        <v>-0.01556695480371673</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.2799983493872986</v>
+        <v>0.02842804824675227</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.4503925165334834</v>
+        <v>-0.1396285568947491</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.3917121094438087</v>
+        <v>-0.02467876916045952</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.2704964331658104</v>
+        <v>0.0661028637471972</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.2814378456148106</v>
+        <v>0.08558914816958207</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.1797026764753014</v>
+        <v>0.2163708592365055</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.256290289041381</v>
+        <v>0.1995703350726998</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.2778751989640398</v>
+        <v>0.1792165105261319</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.3427029104164561</v>
+        <v>0.1456259823716479</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.3663949400089948</v>
+        <v>0.1239124630070592</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.3914928945532239</v>
+        <v>0.0678633152990642</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.3571362291073257</v>
+        <v>0.07303767274979833</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.4264627625003428</v>
+        <v>0.09481433752301882</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.4340160727424944</v>
+        <v>0.02634657667011453</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.3519045642683238</v>
+        <v>0.1687560522207505</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.5007410084624695</v>
+        <v>-0.06909321888568343</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.4207340043166212</v>
+        <v>0.1020907793619088</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.3874776146512957</v>
+        <v>-0.01206041911920863</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 2.007</t>
+          <t>X &lt; 2.012</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3311</v>
+        <v>3332</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.0994305468053156</v>
+        <v>-0.08406978118156161</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.2079865656394873</v>
+        <v>0.01403130346856329</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.1583877055575229</v>
+        <v>0.1477031218834526</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.04368920014137245</v>
+        <v>0.3178168678044386</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.1692063173266618</v>
+        <v>0.2082149804610225</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.3259020359361813</v>
+        <v>-0.03612958523839893</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.3166007198265319</v>
+        <v>-0.02500078827433327</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.4274749931847168</v>
+        <v>-0.133826746729973</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.3688807438009363</v>
+        <v>-0.01882869151030775</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.2524986112751293</v>
+        <v>0.06877417646612827</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.2618912822064061</v>
+        <v>0.08916798138922388</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.1622112366730377</v>
+        <v>0.2184889313457319</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.2444643666194324</v>
+        <v>0.1977473419568767</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.2972383959263141</v>
+        <v>0.1466525282314493</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.3351682289893532</v>
+        <v>0.1406539395480664</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.3555059483049874</v>
+        <v>0.1210336053377858</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.4113295979342411</v>
+        <v>0.03486260856543311</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.3777342798956767</v>
+        <v>0.03953076402153499</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.4153619820441605</v>
+        <v>0.09195732985551075</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.4520222953197077</v>
+        <v>-0.005469126002410007</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.3431340350044252</v>
+        <v>0.1643616198853124</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.4915712642213919</v>
+        <v>-0.07290341410129741</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.4406978384287115</v>
+        <v>0.06853728851146457</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.4080405304323946</v>
+        <v>-0.0457968052399309</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 2.081</t>
+          <t>X &lt; 2.086</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3327</v>
+        <v>3348</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.08648630100663723</v>
+        <v>-0.07081663908981994</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.1961198783189815</v>
+        <v>0.0256546225909986</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.2432903009203642</v>
+        <v>0.06366069533907392</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.1624714197173986</v>
+        <v>0.2004259715415628</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.2292035963005432</v>
+        <v>0.1494180559924487</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.2945600226862624</v>
+        <v>-0.003882927590261431</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.3488053572943244</v>
+        <v>-0.05602288930292332</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.430576908361104</v>
+        <v>-0.1360642264328433</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.3720654881199508</v>
+        <v>-0.02100531596733646</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.2898743013233656</v>
+        <v>0.03264732998780318</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.2979203071889387</v>
+        <v>0.05422927311632009</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.2000644306309098</v>
+        <v>0.1816069536742759</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.2573602197098737</v>
+        <v>0.1854133576088444</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.3109450891148455</v>
+        <v>0.1333755534284791</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.3518536758126274</v>
+        <v>0.1241503428606663</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.3692471945845313</v>
+        <v>0.1072946946014426</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.4254497395478722</v>
+        <v>0.02103514654744743</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.3925232173363042</v>
+        <v>0.02504299680619226</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.4289379793912289</v>
+        <v>0.07823845104272209</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.4345077727104467</v>
+        <v>0.012130159724137</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.3587742980798154</v>
+        <v>0.148604055516202</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.4768282830727273</v>
+        <v>-0.05804071499932917</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.3948273441886627</v>
+        <v>0.1137523206148572</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.4227922070625709</v>
+        <v>-0.06053388286667882</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 2.155</t>
+          <t>X &lt; 2.161</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3334</v>
+        <v>3358</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.04919286604001627</v>
+        <v>-0.08108826657213797</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.1891003578163648</v>
+        <v>0.0143667025365275</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.1795242611408412</v>
+        <v>0.1077492437078007</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.130176932522815</v>
+        <v>0.1831441953021269</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.2273039205832248</v>
+        <v>0.1018451707418464</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.2622908578722161</v>
+        <v>-0.02092106528218807</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.288193585331662</v>
+        <v>-0.01600307751490249</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.3703575147518166</v>
+        <v>-0.09669905935466971</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.3417233564618982</v>
+        <v>-0.01123752061781147</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.2613109647394367</v>
+        <v>0.03989814027908523</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.2687584337443099</v>
+        <v>0.06222579136520068</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.2015681504578311</v>
+        <v>0.1290599704893083</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.2311995352510792</v>
+        <v>0.1592126100436388</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.2851271969302118</v>
+        <v>0.1065844960888995</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.3273205054598805</v>
+        <v>0.09535272693167229</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.3733474783744057</v>
+        <v>0.05049731606250418</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.4297140767432808</v>
+        <v>-0.03583147597820613</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.3970775649866454</v>
+        <v>-0.002520946223825149</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.4030156607782516</v>
+        <v>0.08088119959344198</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.4081741804181291</v>
+        <v>0.01560859837370998</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.3636968112432655</v>
+        <v>0.1202361075150478</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.4816637058129416</v>
+        <v>-0.05626388486429335</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.399260223902651</v>
+        <v>0.08597279210945885</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.4273269177940122</v>
+        <v>-0.058505879340089</v>
       </c>
     </row>
   </sheetData>
